--- a/美股回撤分析报告.xlsx
+++ b/美股回撤分析报告.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>82.06%</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>540.9400000000001</v>
+        <v>530.33</v>
       </c>
       <c r="F2" t="n">
-        <v>56.62</v>
+        <v>55.51</v>
       </c>
       <c r="G2" t="n">
         <v>309.44</v>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>76.78%</t>
+          <t>77.84%</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>261.83</v>
+        <v>249.95</v>
       </c>
       <c r="F3" t="n">
-        <v>191.69</v>
+        <v>182.99</v>
       </c>
       <c r="G3" t="n">
         <v>825.62</v>
@@ -530,7 +530,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>72.73%</t>
+          <t>72.29%</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>346.81</v>
+        <v>352.36</v>
       </c>
       <c r="F4" t="n">
-        <v>131.75</v>
+        <v>133.86</v>
       </c>
       <c r="G4" t="n">
         <v>483.13</v>
@@ -561,74 +561,74 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.24%</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Citigroup Inc.</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2032.43</v>
+        <v>467.52</v>
       </c>
       <c r="F5" t="n">
-        <v>113.59</v>
+        <v>161.58</v>
       </c>
       <c r="G5" t="n">
-        <v>382.43</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>69.96%</t>
+          <t>69.98%</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Citigroup Inc.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>471.95</v>
+        <v>2053.9</v>
       </c>
       <c r="F6" t="n">
-        <v>163.11</v>
+        <v>114.79</v>
       </c>
       <c r="G6" t="n">
-        <v>543</v>
+        <v>382.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>64.22%</t>
+          <t>64.08%</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -638,28 +638,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Kraft Heinz Company</t>
+          <t>Warner Bros. Discovery, Inc.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>274.61</v>
+        <v>695.99</v>
       </c>
       <c r="F7" t="n">
-        <v>23.2</v>
+        <v>28.07</v>
       </c>
       <c r="G7" t="n">
-        <v>64.84</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>63.42%</t>
+          <t>63.45%</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -669,23 +669,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery, Inc.</t>
+          <t>The Kraft Heinz Company</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>708.64</v>
+        <v>280.53</v>
       </c>
       <c r="F8" t="n">
-        <v>28.58</v>
+        <v>23.7</v>
       </c>
       <c r="G8" t="n">
-        <v>78.14</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>56.96%</t>
+          <t>57.48%</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1260.28</v>
+        <v>1245</v>
       </c>
       <c r="F9" t="n">
-        <v>301.07</v>
+        <v>297.42</v>
       </c>
       <c r="G9" t="n">
         <v>699.54</v>
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>56.66%</t>
+          <t>56.22%</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2766.51</v>
+        <v>2794.5</v>
       </c>
       <c r="F10" t="n">
-        <v>62.26</v>
+        <v>62.89</v>
       </c>
       <c r="G10" t="n">
         <v>143.64</v>
@@ -747,7 +747,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>55.81%</t>
+          <t>55.31%</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>285.72</v>
+        <v>288.9</v>
       </c>
       <c r="F11" t="n">
-        <v>72.86</v>
+        <v>73.67</v>
       </c>
       <c r="G11" t="n">
         <v>164.86</v>
@@ -778,12 +778,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>49.96%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -793,28 +793,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc.</t>
+          <t>UnitedHealth Group Incorporated</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1510.15</v>
+        <v>2560.81</v>
       </c>
       <c r="F12" t="n">
-        <v>106.38</v>
+        <v>282.7</v>
       </c>
       <c r="G12" t="n">
-        <v>212.6</v>
+        <v>613.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>48.53%</t>
+          <t>49.71%</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -824,28 +824,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>PDD Holdings Inc.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5090.04</v>
+        <v>1517.74</v>
       </c>
       <c r="F13" t="n">
-        <v>177.16</v>
+        <v>106.91</v>
       </c>
       <c r="G13" t="n">
-        <v>344.21</v>
+        <v>212.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.19%</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -855,28 +855,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1458.38</v>
+        <v>5025.1</v>
       </c>
       <c r="F14" t="n">
-        <v>25.65</v>
+        <v>174.9</v>
       </c>
       <c r="G14" t="n">
-        <v>49.42</v>
+        <v>344.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>44.45%</t>
+          <t>46.38%</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -886,28 +886,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1404.5</v>
+        <v>1506.71</v>
       </c>
       <c r="F15" t="n">
-        <v>133.11</v>
+        <v>26.5</v>
       </c>
       <c r="G15" t="n">
-        <v>239.62</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>44.27%</t>
+          <t>45.14%</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -917,28 +917,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zscaler, Inc.</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>334.28</v>
+        <v>537.46</v>
       </c>
       <c r="F16" t="n">
-        <v>209.62</v>
+        <v>118.9</v>
       </c>
       <c r="G16" t="n">
-        <v>376.11</v>
+        <v>216.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>44.05%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -948,28 +948,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1981.31</v>
+        <v>1390.68</v>
       </c>
       <c r="F17" t="n">
-        <v>110.98</v>
+        <v>131.8</v>
       </c>
       <c r="G17" t="n">
-        <v>198.35</v>
+        <v>239.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>43.06%</t>
+          <t>44.23%</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -979,28 +979,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>557.8099999999999</v>
+        <v>1974.71</v>
       </c>
       <c r="F18" t="n">
-        <v>123.4</v>
+        <v>110.61</v>
       </c>
       <c r="G18" t="n">
-        <v>216.72</v>
+        <v>198.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>42.88%</t>
+          <t>43.85%</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1010,28 +1010,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Limited</t>
+          <t>The Boeing Company</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4135.56</v>
+        <v>1915.08</v>
       </c>
       <c r="F19" t="n">
-        <v>173.23</v>
+        <v>244.56</v>
       </c>
       <c r="G19" t="n">
-        <v>303.26</v>
+        <v>435.56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>42.11%</t>
+          <t>43.12%</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1041,28 +1041,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>The Boeing Company</t>
+          <t>Comcast Corporation</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1974.51</v>
+        <v>1131.11</v>
       </c>
       <c r="F20" t="n">
-        <v>252.15</v>
+        <v>28.7</v>
       </c>
       <c r="G20" t="n">
-        <v>435.56</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>41.93%</t>
+          <t>43.04%</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1072,28 +1072,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Comcast Corporation</t>
+          <t>Alibaba Group Holding Limited</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1155.55</v>
+        <v>4123.39</v>
       </c>
       <c r="F21" t="n">
-        <v>29.3</v>
+        <v>172.72</v>
       </c>
       <c r="G21" t="n">
-        <v>50.46</v>
+        <v>303.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.59%</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1103,23 +1103,23 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UnitedHealth Group Incorporated</t>
+          <t>Zscaler, Inc.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3227.14</v>
+        <v>350.31</v>
       </c>
       <c r="F22" t="n">
-        <v>356.26</v>
+        <v>219.67</v>
       </c>
       <c r="G22" t="n">
-        <v>613.22</v>
+        <v>376.11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>39.92%</t>
+          <t>39.88%</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>809.0700000000001</v>
+        <v>809.5</v>
       </c>
       <c r="F23" t="n">
-        <v>132.15</v>
+        <v>132.22</v>
       </c>
       <c r="G23" t="n">
         <v>219.94</v>
@@ -1150,12 +1150,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>39.83%</t>
+          <t>39.42%</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1165,28 +1165,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mizuho Financial Group, Inc.</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1048.07</v>
+        <v>503.51</v>
       </c>
       <c r="F24" t="n">
-        <v>8.470000000000001</v>
+        <v>188.58</v>
       </c>
       <c r="G24" t="n">
-        <v>14.08</v>
+        <v>311.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.14%</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1196,28 +1196,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>505.32</v>
+        <v>1218.88</v>
       </c>
       <c r="F25" t="n">
-        <v>189.26</v>
+        <v>114.88</v>
       </c>
       <c r="G25" t="n">
-        <v>311.28</v>
+        <v>188.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>38.51%</t>
+          <t>38.34%</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1227,23 +1227,23 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Mizuho Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1231.5</v>
+        <v>1074.05</v>
       </c>
       <c r="F26" t="n">
-        <v>116.07</v>
+        <v>8.68</v>
       </c>
       <c r="G26" t="n">
-        <v>188.75</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>38.24%</t>
+          <t>37.91%</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1359.84</v>
+        <v>1367.04</v>
       </c>
       <c r="F27" t="n">
-        <v>69.88</v>
+        <v>70.25</v>
       </c>
       <c r="G27" t="n">
         <v>113.15</v>
@@ -1274,7 +1274,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>37.72%</t>
+          <t>37.59%</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2171.04</v>
+        <v>2175.61</v>
       </c>
       <c r="F28" t="n">
-        <v>228.05</v>
+        <v>228.53</v>
       </c>
       <c r="G28" t="n">
         <v>366.19</v>
@@ -1305,12 +1305,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>37.44%</t>
+          <t>37.55%</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1320,28 +1320,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
+          <t>Roper Technologies, Inc.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>798.67</v>
+        <v>397.47</v>
       </c>
       <c r="F29" t="n">
-        <v>753.55</v>
+        <v>369.27</v>
       </c>
       <c r="G29" t="n">
-        <v>1204.52</v>
+        <v>591.26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>36.85%</t>
+          <t>37.29%</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1351,23 +1351,23 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Copart, Inc.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>691.66</v>
+        <v>390.79</v>
       </c>
       <c r="F30" t="n">
-        <v>80.23</v>
+        <v>40.37</v>
       </c>
       <c r="G30" t="n">
-        <v>127.06</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>35.79%</t>
+          <t>36.19%</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3647.7</v>
+        <v>3626.3</v>
       </c>
       <c r="F31" t="n">
-        <v>86.12</v>
+        <v>85.58</v>
       </c>
       <c r="G31" t="n">
         <v>134.12</v>
@@ -1398,12 +1398,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>35.69%</t>
+          <t>35.97%</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1413,28 +1413,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Copart, Inc.</t>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>400.76</v>
+        <v>817.4299999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>41.4</v>
+        <v>771.25</v>
       </c>
       <c r="G32" t="n">
-        <v>64.38</v>
+        <v>1204.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>35.48%</t>
+          <t>34.82%</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1444,28 +1444,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Spotify Technology S.A.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>456.33</v>
+        <v>1053.56</v>
       </c>
       <c r="F33" t="n">
-        <v>130.13</v>
+        <v>511.7</v>
       </c>
       <c r="G33" t="n">
-        <v>201.69</v>
+        <v>785</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35.08%</t>
+          <t>34.73%</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1475,28 +1475,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CoStar Group, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>278.03</v>
+        <v>714.9400000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>65.59999999999999</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>101.05</v>
+        <v>127.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34.62%</t>
+          <t>34.47%</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1506,23 +1506,23 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Spotify Technology S.A.</t>
+          <t>CoStar Group, Inc.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1056.67</v>
+        <v>280.66</v>
       </c>
       <c r="F35" t="n">
-        <v>513.21</v>
+        <v>66.22</v>
       </c>
       <c r="G35" t="n">
-        <v>785</v>
+        <v>101.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>32.72%</t>
+          <t>33.79%</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>382.77</v>
+        <v>376.7</v>
       </c>
       <c r="F36" t="n">
-        <v>106.63</v>
+        <v>104.94</v>
       </c>
       <c r="G36" t="n">
         <v>158.49</v>
@@ -1553,12 +1553,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>32.12%</t>
+          <t>32.73%</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1568,28 +1568,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>304.63</v>
+        <v>1518.39</v>
       </c>
       <c r="F37" t="n">
-        <v>218.04</v>
+        <v>545.4</v>
       </c>
       <c r="G37" t="n">
-        <v>321.24</v>
+        <v>810.72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.67%</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1599,28 +1599,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T-Mobile US, Inc.</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2093.62</v>
+        <v>302.18</v>
       </c>
       <c r="F38" t="n">
-        <v>186.03</v>
+        <v>216.28</v>
       </c>
       <c r="G38" t="n">
-        <v>273.15</v>
+        <v>321.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>31.06%</t>
+          <t>32.46%</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1630,59 +1630,59 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Roper Technologies, Inc.</t>
+          <t>T-Mobile US, Inc.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>438.74</v>
+        <v>2076.29</v>
       </c>
       <c r="F39" t="n">
-        <v>407.61</v>
+        <v>184.49</v>
       </c>
       <c r="G39" t="n">
-        <v>591.26</v>
+        <v>273.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>30.79%</t>
+          <t>31.54%</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>KKR &amp; Co. Inc.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>487.06</v>
+        <v>1074.07</v>
       </c>
       <c r="F40" t="n">
-        <v>613.14</v>
+        <v>116</v>
       </c>
       <c r="G40" t="n">
-        <v>885.92</v>
+        <v>169.44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>30.44%</t>
+          <t>31.47%</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1692,23 +1692,23 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1570.08</v>
+        <v>484.66</v>
       </c>
       <c r="F41" t="n">
-        <v>563.97</v>
+        <v>138.21</v>
       </c>
       <c r="G41" t="n">
-        <v>810.72</v>
+        <v>201.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.45%</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1668.83</v>
+        <v>1639.06</v>
       </c>
       <c r="F42" t="n">
-        <v>155.82</v>
+        <v>153.04</v>
       </c>
       <c r="G42" t="n">
         <v>223.25</v>
@@ -1739,43 +1739,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>29.88%</t>
+          <t>31.12%</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Constellation Energy Corporation</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1046.84</v>
+        <v>484.74</v>
       </c>
       <c r="F43" t="n">
-        <v>289.06</v>
+        <v>610.22</v>
       </c>
       <c r="G43" t="n">
-        <v>412.23</v>
+        <v>885.92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>29.67%</t>
+          <t>30.07%</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1785,28 +1785,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AppLovin Corporation</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1773.82</v>
+        <v>1710.34</v>
       </c>
       <c r="F44" t="n">
-        <v>524.41</v>
+        <v>275.8</v>
       </c>
       <c r="G44" t="n">
-        <v>745.61</v>
+        <v>394.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.95%</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1816,28 +1816,28 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Constellation Energy Corporation</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>625.58</v>
+        <v>1046.15</v>
       </c>
       <c r="F45" t="n">
-        <v>81.64</v>
+        <v>288.76</v>
       </c>
       <c r="G45" t="n">
-        <v>114.82</v>
+        <v>412.23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28.74%</t>
+          <t>29.48%</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1847,28 +1847,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1743.02</v>
+        <v>2194.3</v>
       </c>
       <c r="F46" t="n">
-        <v>281.07</v>
+        <v>43.93</v>
       </c>
       <c r="G46" t="n">
-        <v>394.41</v>
+        <v>62.29</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28.44%</t>
+          <t>28.84%</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1878,23 +1878,23 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1122.68</v>
+        <v>626.12</v>
       </c>
       <c r="F47" t="n">
-        <v>121.25</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>169.44</v>
+        <v>114.82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27.76%</t>
+          <t>28.41%</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>472.94</v>
+        <v>468.67</v>
       </c>
       <c r="F48" t="n">
-        <v>357.98</v>
+        <v>354.75</v>
       </c>
       <c r="G48" t="n">
         <v>495.55</v>
@@ -1925,12 +1925,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27.65%</t>
+          <t>27.37%</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1940,28 +1940,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2252</v>
+        <v>893.72</v>
       </c>
       <c r="F49" t="n">
-        <v>45.07</v>
+        <v>207.36</v>
       </c>
       <c r="G49" t="n">
-        <v>62.29</v>
+        <v>285.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27.42%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1971,59 +1971,59 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>AppLovin Corporation</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>893.16</v>
+        <v>1838.59</v>
       </c>
       <c r="F50" t="n">
-        <v>207.23</v>
+        <v>543.5599999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>285.5</v>
+        <v>745.61</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26.58%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Insmed Incorporated</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>333.15</v>
+        <v>374.83</v>
       </c>
       <c r="F51" t="n">
-        <v>156.21</v>
+        <v>27.59</v>
       </c>
       <c r="G51" t="n">
-        <v>212.75</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26.24%</t>
+          <t>25.51%</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2033,28 +2033,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Sony Group Corporation</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2696.11</v>
+        <v>1357.64</v>
       </c>
       <c r="F52" t="n">
-        <v>231.07</v>
+        <v>22.6</v>
       </c>
       <c r="G52" t="n">
-        <v>313.28</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>26.15%</t>
+          <t>25.33%</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2064,28 +2064,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>377.21</v>
+        <v>2729.6</v>
       </c>
       <c r="F53" t="n">
-        <v>27.76</v>
+        <v>233.94</v>
       </c>
       <c r="G53" t="n">
-        <v>37.59</v>
+        <v>313.28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25.13%</t>
+          <t>24.59%</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2095,28 +2095,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>The Progressive Corporation</t>
+          <t>Old Dominion Freight Line, Inc.</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1207.75</v>
+        <v>366.62</v>
       </c>
       <c r="F54" t="n">
-        <v>206.03</v>
+        <v>174.44</v>
       </c>
       <c r="G54" t="n">
-        <v>275.18</v>
+        <v>231.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.53%</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2126,28 +2126,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Diamondback Energy, Inc.</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>445.87</v>
+        <v>1790.03</v>
       </c>
       <c r="F55" t="n">
-        <v>154.02</v>
+        <v>137.5</v>
       </c>
       <c r="G55" t="n">
-        <v>205.08</v>
+        <v>182.19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>24.65%</t>
+          <t>24.38%</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2157,28 +2157,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Old Dominion Freight Line, Inc.</t>
+          <t>The Progressive Corporation</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>366.32</v>
+        <v>1219.76</v>
       </c>
       <c r="F56" t="n">
-        <v>174.3</v>
+        <v>208.08</v>
       </c>
       <c r="G56" t="n">
-        <v>231.32</v>
+        <v>275.18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>24.32%</t>
+          <t>23.87%</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2188,59 +2188,59 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1795.11</v>
+        <v>1821.08</v>
       </c>
       <c r="F57" t="n">
-        <v>137.89</v>
+        <v>148.41</v>
       </c>
       <c r="G57" t="n">
-        <v>182.19</v>
+        <v>194.94</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.55%</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sony Group Corporation</t>
+          <t>Insmed Incorporated</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1387.07</v>
+        <v>346.87</v>
       </c>
       <c r="F58" t="n">
-        <v>23.09</v>
+        <v>162.64</v>
       </c>
       <c r="G58" t="n">
-        <v>30.34</v>
+        <v>212.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>23.17%</t>
+          <t>22.87%</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2250,28 +2250,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1228.33</v>
+        <v>961.76</v>
       </c>
       <c r="F59" t="n">
-        <v>98.34999999999999</v>
+        <v>502.7</v>
       </c>
       <c r="G59" t="n">
-        <v>128.01</v>
+        <v>651.73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23.07%</t>
+          <t>22.41%</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2281,28 +2281,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>Diamondback Energy, Inc.</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>959.25</v>
+        <v>460.63</v>
       </c>
       <c r="F60" t="n">
-        <v>501.39</v>
+        <v>159.12</v>
       </c>
       <c r="G60" t="n">
-        <v>651.73</v>
+        <v>205.08</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>22.81%</t>
+          <t>22.16%</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2312,28 +2312,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1846.48</v>
+        <v>571.03</v>
       </c>
       <c r="F61" t="n">
-        <v>150.48</v>
+        <v>268.09</v>
       </c>
       <c r="G61" t="n">
-        <v>194.94</v>
+        <v>344.39</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22.66%</t>
+          <t>21.98%</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2343,28 +2343,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>15169.94</v>
+        <v>1247.32</v>
       </c>
       <c r="F62" t="n">
-        <v>320.05</v>
+        <v>99.87</v>
       </c>
       <c r="G62" t="n">
-        <v>413.82</v>
+        <v>128.01</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22.51%</t>
+          <t>21.95%</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2374,28 +2374,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Microchip Technology Incorporated</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1869.6</v>
+        <v>406.2</v>
       </c>
       <c r="F63" t="n">
-        <v>107.42</v>
+        <v>75.16</v>
       </c>
       <c r="G63" t="n">
-        <v>138.63</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22.45%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2405,28 +2405,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Company</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1112.54</v>
+        <v>1884.39</v>
       </c>
       <c r="F64" t="n">
-        <v>54.65</v>
+        <v>108.27</v>
       </c>
       <c r="G64" t="n">
-        <v>70.48</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22.42%</t>
+          <t>21.57%</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2436,28 +2436,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Microchip Technology Incorporated</t>
+          <t>Automatic Data Processing, Inc.</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>403.77</v>
+        <v>1030.99</v>
       </c>
       <c r="F65" t="n">
-        <v>74.70999999999999</v>
+        <v>254.51</v>
       </c>
       <c r="G65" t="n">
-        <v>96.3</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.16%</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2467,28 +2467,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>Bristol-Myers Squibb Company</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>575.1</v>
+        <v>1131.06</v>
       </c>
       <c r="F66" t="n">
-        <v>270</v>
+        <v>55.56</v>
       </c>
       <c r="G66" t="n">
-        <v>344.39</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20.53%</t>
+          <t>21.05%</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2498,28 +2498,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Automatic Data Processing, Inc.</t>
+          <t>AT&amp;T Inc.</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1044.6</v>
+        <v>1644.59</v>
       </c>
       <c r="F67" t="n">
-        <v>257.87</v>
+        <v>23</v>
       </c>
       <c r="G67" t="n">
-        <v>324.5</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20.18%</t>
+          <t>20.35%</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2529,28 +2529,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>NXP Semiconductors N.V.</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1140.72</v>
+        <v>578.4</v>
       </c>
       <c r="F68" t="n">
-        <v>452.49</v>
+        <v>229.42</v>
       </c>
       <c r="G68" t="n">
-        <v>566.9</v>
+        <v>288.03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>19.89%</t>
+          <t>20.35%</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2560,59 +2560,59 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mondelez International, Inc.</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>755.66</v>
+        <v>1694.19</v>
       </c>
       <c r="F69" t="n">
-        <v>58.4</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>72.90000000000001</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>19.47%</t>
+          <t>20.15%</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PepsiCo, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1979.41</v>
+        <v>3949.35</v>
       </c>
       <c r="F70" t="n">
-        <v>144.58</v>
+        <v>165.7</v>
       </c>
       <c r="G70" t="n">
-        <v>179.53</v>
+        <v>207.52</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>19.42%</t>
+          <t>19.58%</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2622,28 +2622,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1255.85</v>
+        <v>15778.49</v>
       </c>
       <c r="F71" t="n">
-        <v>180.18</v>
+        <v>332.79</v>
       </c>
       <c r="G71" t="n">
-        <v>223.61</v>
+        <v>413.82</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.04%</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2653,28 +2653,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>Mondelez International, Inc.</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1716.51</v>
+        <v>763.6900000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>82.31</v>
+        <v>59.02</v>
       </c>
       <c r="G72" t="n">
-        <v>101.99</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>19.29%</t>
+          <t>18.75%</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2684,28 +2684,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NXP Semiconductors N.V.</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>586.1</v>
+        <v>1688.09</v>
       </c>
       <c r="F73" t="n">
-        <v>232.48</v>
+        <v>235.75</v>
       </c>
       <c r="G73" t="n">
-        <v>288.03</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>17.94%</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2715,28 +2715,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>MercadoLibre, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1083.55</v>
+        <v>1255.11</v>
       </c>
       <c r="F74" t="n">
-        <v>2137.29</v>
+        <v>183.5</v>
       </c>
       <c r="G74" t="n">
-        <v>2645.22</v>
+        <v>223.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>19.02%</t>
+          <t>17.54%</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2746,28 +2746,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc.</t>
+          <t>HDFC Bank Limited</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1686.78</v>
+        <v>1663.83</v>
       </c>
       <c r="F75" t="n">
-        <v>23.59</v>
+        <v>32.44</v>
       </c>
       <c r="G75" t="n">
-        <v>29.13</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>17.51%</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2777,28 +2777,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Sanofi</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1682.79</v>
+        <v>1153.48</v>
       </c>
       <c r="F76" t="n">
-        <v>235.01</v>
+        <v>47.49</v>
       </c>
       <c r="G76" t="n">
-        <v>290.14</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>18.82%</t>
+          <t>17.27%</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2808,28 +2808,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Financial Group, Inc.</t>
+          <t>Prologis, Inc.</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1342.91</v>
+        <v>1195.45</v>
       </c>
       <c r="F77" t="n">
-        <v>20.92</v>
+        <v>128.7</v>
       </c>
       <c r="G77" t="n">
-        <v>25.77</v>
+        <v>155.57</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>17.16%</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2839,59 +2839,59 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>HDFC Bank Limited</t>
+          <t>Sumitomo Mitsui Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1644.34</v>
+        <v>1370.51</v>
       </c>
       <c r="F78" t="n">
-        <v>32.06</v>
+        <v>21.35</v>
       </c>
       <c r="G78" t="n">
-        <v>39.34</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>18.27%</t>
+          <t>17.13%</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4042.31</v>
+        <v>2036.91</v>
       </c>
       <c r="F79" t="n">
-        <v>169.6</v>
+        <v>148.78</v>
       </c>
       <c r="G79" t="n">
-        <v>207.52</v>
+        <v>179.53</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>18.27%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2901,28 +2901,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Prologis, Inc.</t>
+          <t>Starbucks Corporation</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1181.05</v>
+        <v>1088.43</v>
       </c>
       <c r="F80" t="n">
-        <v>127.15</v>
+        <v>95.72</v>
       </c>
       <c r="G80" t="n">
-        <v>155.57</v>
+        <v>115.04</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>18.01%</t>
+          <t>16.38%</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2932,28 +2932,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>Capital One Financial Corporation</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1146.44</v>
+        <v>1380.24</v>
       </c>
       <c r="F81" t="n">
-        <v>47.2</v>
+        <v>217.11</v>
       </c>
       <c r="G81" t="n">
-        <v>57.57</v>
+        <v>259.64</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17.34%</t>
+          <t>16.22%</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2963,28 +2963,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1716.91</v>
+        <v>768.41</v>
       </c>
       <c r="F82" t="n">
-        <v>136.34</v>
+        <v>191.21</v>
       </c>
       <c r="G82" t="n">
-        <v>164.94</v>
+        <v>228.23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>17.14%</t>
+          <t>15.92%</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2994,28 +2994,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>16604.23</v>
+        <v>1201.65</v>
       </c>
       <c r="F83" t="n">
-        <v>658.76</v>
+        <v>476.66</v>
       </c>
       <c r="G83" t="n">
-        <v>795.0599999999999</v>
+        <v>566.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>16.86%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3025,28 +3025,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Eaton Corporation plc</t>
+          <t>Merck &amp; Co., Inc.</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1289.44</v>
+        <v>2695.61</v>
       </c>
       <c r="F84" t="n">
-        <v>331.22</v>
+        <v>107.92</v>
       </c>
       <c r="G84" t="n">
-        <v>398.4</v>
+        <v>127.87</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>16.31%</t>
+          <t>15.43%</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3056,28 +3056,28 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Capital One Financial Corporation</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1381.45</v>
+        <v>1291.47</v>
       </c>
       <c r="F85" t="n">
-        <v>217.3</v>
+        <v>100.69</v>
       </c>
       <c r="G85" t="n">
-        <v>259.64</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>15.82%</t>
+          <t>15.43%</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Cadence Design Systems, Inc.</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>34634.84</v>
+        <v>867.53</v>
       </c>
       <c r="F86" t="n">
-        <v>465.95</v>
+        <v>318.37</v>
       </c>
       <c r="G86" t="n">
-        <v>553.5</v>
+        <v>376.45</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.36%</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3118,28 +3118,28 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>GE HealthCare Technologies Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>364.2</v>
+        <v>16962.39</v>
       </c>
       <c r="F87" t="n">
-        <v>79.77</v>
+        <v>672.97</v>
       </c>
       <c r="G87" t="n">
-        <v>94.63</v>
+        <v>795.0599999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>15.52%</t>
+          <t>15.32%</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3149,28 +3149,28 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Boston Scientific Corporation</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1371.94</v>
+        <v>3471.88</v>
       </c>
       <c r="F88" t="n">
-        <v>92.51000000000001</v>
+        <v>148.34</v>
       </c>
       <c r="G88" t="n">
-        <v>109.5</v>
+        <v>175.18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>15.45%</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>GE HealthCare Technologies Inc.</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>775.4400000000001</v>
+        <v>366.71</v>
       </c>
       <c r="F89" t="n">
-        <v>192.96</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>228.23</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>15.44%</t>
+          <t>14.77%</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3211,28 +3211,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cadence Design Systems, Inc.</t>
+          <t>Intuitive Surgical, Inc.</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>867.39</v>
+        <v>1882.14</v>
       </c>
       <c r="F90" t="n">
-        <v>318.32</v>
+        <v>525.04</v>
       </c>
       <c r="G90" t="n">
-        <v>376.45</v>
+        <v>616</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.51%</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3242,28 +3242,28 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Merck &amp; Co., Inc.</t>
+          <t>Boston Scientific Corporation</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2702.1</v>
+        <v>1388.25</v>
       </c>
       <c r="F91" t="n">
-        <v>108.18</v>
+        <v>93.61</v>
       </c>
       <c r="G91" t="n">
-        <v>127.87</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>15.27%</t>
+          <t>14.36%</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3273,28 +3273,28 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>Eaton Corporation plc</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1293.9</v>
+        <v>1328.25</v>
       </c>
       <c r="F92" t="n">
-        <v>100.88</v>
+        <v>341.19</v>
       </c>
       <c r="G92" t="n">
-        <v>119.06</v>
+        <v>398.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>15.14%</t>
+          <t>13.62%</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3304,28 +3304,28 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Starbucks Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1110.04</v>
+        <v>14330.96</v>
       </c>
       <c r="F93" t="n">
-        <v>97.62</v>
+        <v>430.9</v>
       </c>
       <c r="G93" t="n">
-        <v>115.04</v>
+        <v>498.83</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>15.01%</t>
+          <t>13.28%</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IBN</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3335,28 +3335,28 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1042.43</v>
+        <v>4704.57</v>
       </c>
       <c r="F94" t="n">
-        <v>29.15</v>
+        <v>520.41</v>
       </c>
       <c r="G94" t="n">
-        <v>34.3</v>
+        <v>600.08</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>14.94%</t>
+          <t>13.26%</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>IBN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3366,28 +3366,28 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Intuitive Surgical, Inc.</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1878.38</v>
+        <v>1063.89</v>
       </c>
       <c r="F95" t="n">
-        <v>523.99</v>
+        <v>29.75</v>
       </c>
       <c r="G95" t="n">
-        <v>616</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>13.24%</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3397,28 +3397,28 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>MercadoLibre, Inc.</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3508.61</v>
+        <v>1163.5</v>
       </c>
       <c r="F96" t="n">
-        <v>150.15</v>
+        <v>2295</v>
       </c>
       <c r="G96" t="n">
-        <v>175.18</v>
+        <v>2645.22</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>14.19%</t>
+          <t>13.17%</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3428,28 +3428,28 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1053.76</v>
+        <v>35722.31</v>
       </c>
       <c r="F97" t="n">
-        <v>83.01000000000001</v>
+        <v>480.58</v>
       </c>
       <c r="G97" t="n">
-        <v>96.73</v>
+        <v>553.5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14.06%</t>
+          <t>13.06%</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3459,28 +3459,28 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>36651.26</v>
+        <v>6277.18</v>
       </c>
       <c r="F98" t="n">
-        <v>248.04</v>
+        <v>325.26</v>
       </c>
       <c r="G98" t="n">
-        <v>288.62</v>
+        <v>374.11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12.86%</t>
+          <t>12.87%</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3490,28 +3490,28 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Verizon Communications Inc.</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>503.88</v>
+        <v>1657.9</v>
       </c>
       <c r="F99" t="n">
-        <v>43.89</v>
+        <v>39.32</v>
       </c>
       <c r="G99" t="n">
-        <v>50.37</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12.81%</t>
+          <t>12.74%</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3521,28 +3521,28 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6294.94</v>
+        <v>504.57</v>
       </c>
       <c r="F100" t="n">
-        <v>326.18</v>
+        <v>43.95</v>
       </c>
       <c r="G100" t="n">
-        <v>374.11</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>12.55%</t>
+          <t>12.23%</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3552,28 +3552,28 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4743.71</v>
+        <v>1259.34</v>
       </c>
       <c r="F101" t="n">
-        <v>524.74</v>
+        <v>183.49</v>
       </c>
       <c r="G101" t="n">
-        <v>600.08</v>
+        <v>209.05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>12.43%</t>
+          <t>12.01%</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3583,23 +3583,23 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc.</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1666.33</v>
+        <v>1355.96</v>
       </c>
       <c r="F102" t="n">
-        <v>39.52</v>
+        <v>354.57</v>
       </c>
       <c r="G102" t="n">
-        <v>45.13</v>
+        <v>402.95</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12.37%</t>
+          <t>11.43%</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1652.42</v>
+        <v>1670.21</v>
       </c>
       <c r="F103" t="n">
-        <v>5098.5</v>
+        <v>5153.41</v>
       </c>
       <c r="G103" t="n">
         <v>5818.24</v>
@@ -3630,12 +3630,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>12.14%</t>
+          <t>11.15%</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3645,28 +3645,28 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1260.65</v>
+        <v>45898.97</v>
       </c>
       <c r="F104" t="n">
-        <v>183.68</v>
+        <v>188.52</v>
       </c>
       <c r="G104" t="n">
-        <v>209.05</v>
+        <v>212.18</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>11.89%</t>
+          <t>11.06%</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3676,28 +3676,28 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1357.76</v>
+        <v>1847.25</v>
       </c>
       <c r="F105" t="n">
-        <v>355.04</v>
+        <v>146.69</v>
       </c>
       <c r="G105" t="n">
-        <v>402.95</v>
+        <v>164.94</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>10.81%</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3707,28 +3707,28 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>The Home Depot, Inc.</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3099.78</v>
+        <v>3786.53</v>
       </c>
       <c r="F106" t="n">
-        <v>293.87</v>
+        <v>380.36</v>
       </c>
       <c r="G106" t="n">
-        <v>332.79</v>
+        <v>426.44</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>11.55%</t>
+          <t>10.61%</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3738,28 +3738,28 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>45694.45</v>
+        <v>3137.75</v>
       </c>
       <c r="F107" t="n">
-        <v>187.67</v>
+        <v>297.47</v>
       </c>
       <c r="G107" t="n">
-        <v>212.18</v>
+        <v>332.79</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>11.39%</t>
+          <t>10.59%</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3769,28 +3769,28 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1757.45</v>
+        <v>8175.23</v>
       </c>
       <c r="F108" t="n">
-        <v>193.31</v>
+        <v>300.31</v>
       </c>
       <c r="G108" t="n">
-        <v>218.15</v>
+        <v>335.87</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>11.36%</t>
+          <t>10.52%</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3800,28 +3800,28 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>8104.72</v>
+        <v>38162.88</v>
       </c>
       <c r="F109" t="n">
-        <v>297.72</v>
+        <v>258.27</v>
       </c>
       <c r="G109" t="n">
-        <v>335.87</v>
+        <v>288.62</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>11.05%</t>
+          <t>9.87%</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3831,28 +3831,28 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2729.75</v>
+        <v>1787.64</v>
       </c>
       <c r="F110" t="n">
-        <v>86.95999999999999</v>
+        <v>196.63</v>
       </c>
       <c r="G110" t="n">
-        <v>97.76000000000001</v>
+        <v>218.15</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10.13%</t>
+          <t>9.77%</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3862,28 +3862,28 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>IDEXX Laboratories, Inc.</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3776.85</v>
+        <v>555.83</v>
       </c>
       <c r="F111" t="n">
-        <v>51.72</v>
+        <v>694.75</v>
       </c>
       <c r="G111" t="n">
-        <v>57.55</v>
+        <v>769.98</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10.09%</t>
+          <t>9.64%</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3893,28 +3893,28 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1362.19</v>
+        <v>4307.63</v>
       </c>
       <c r="F112" t="n">
-        <v>229.65</v>
+        <v>970.28</v>
       </c>
       <c r="G112" t="n">
-        <v>255.44</v>
+        <v>1073.82</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>10.01%</t>
+          <t>9.55%</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3924,28 +3924,28 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>The Home Depot, Inc.</t>
+          <t>International Business Machines Corporation</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3820.47</v>
+        <v>2746.81</v>
       </c>
       <c r="F113" t="n">
-        <v>383.77</v>
+        <v>293.86</v>
       </c>
       <c r="G113" t="n">
-        <v>426.44</v>
+        <v>324.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9.99%</t>
+          <t>9.35%</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3955,28 +3955,28 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2733.54</v>
+        <v>3809.71</v>
       </c>
       <c r="F114" t="n">
-        <v>292.44</v>
+        <v>52.17</v>
       </c>
       <c r="G114" t="n">
-        <v>324.9</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>9.98%</t>
+          <t>9.26%</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3986,28 +3986,28 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>14934.92</v>
+        <v>2784.68</v>
       </c>
       <c r="F115" t="n">
-        <v>449.06</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="G115" t="n">
-        <v>498.83</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9.95%</t>
+          <t>8.96%</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4017,28 +4017,28 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1790.63</v>
+        <v>1379.4</v>
       </c>
       <c r="F116" t="n">
-        <v>657.78</v>
+        <v>232.55</v>
       </c>
       <c r="G116" t="n">
-        <v>730.46</v>
+        <v>255.44</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.84%</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4048,28 +4048,28 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals Incorporated</t>
+          <t>BlackRock, Inc.</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1200.96</v>
+        <v>1717.04</v>
       </c>
       <c r="F117" t="n">
-        <v>468.41</v>
+        <v>1106.69</v>
       </c>
       <c r="G117" t="n">
-        <v>519.88</v>
+        <v>1214.03</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>9.89%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4079,28 +4079,28 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories, Inc.</t>
+          <t>Toyota Motor Corporation</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>555.11</v>
+        <v>2934.83</v>
       </c>
       <c r="F118" t="n">
-        <v>693.85</v>
+        <v>224.12</v>
       </c>
       <c r="G118" t="n">
-        <v>769.98</v>
+        <v>245.75</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>9.33%</t>
+          <t>8.79%</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4110,28 +4110,28 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Coca-Cola Europacific Partners PLC</t>
+          <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>409.98</v>
+        <v>1215.73</v>
       </c>
       <c r="F119" t="n">
-        <v>89.84999999999999</v>
+        <v>474.17</v>
       </c>
       <c r="G119" t="n">
-        <v>99.09999999999999</v>
+        <v>519.88</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>9.31%</t>
+          <t>8.71%</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4141,28 +4141,28 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>HCA Healthcare, Inc.</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1101.83</v>
+        <v>1607.92</v>
       </c>
       <c r="F120" t="n">
-        <v>470.88</v>
+        <v>526.67</v>
       </c>
       <c r="G120" t="n">
-        <v>519.23</v>
+        <v>576.91</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>9.07%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4172,28 +4172,28 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Coca-Cola Europacific Partners PLC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3875.17</v>
+        <v>414.17</v>
       </c>
       <c r="F121" t="n">
-        <v>219.26</v>
+        <v>90.77</v>
       </c>
       <c r="G121" t="n">
-        <v>241.12</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8.94%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4203,23 +4203,23 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Xcel Energy Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>443.6</v>
+        <v>9318.76</v>
       </c>
       <c r="F122" t="n">
-        <v>75.01000000000001</v>
+        <v>1039.51</v>
       </c>
       <c r="G122" t="n">
-        <v>82.37</v>
+        <v>1133.95</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8.73%</t>
+          <t>7.45%</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>839.52</v>
+        <v>851.28</v>
       </c>
       <c r="F123" t="n">
-        <v>99.23</v>
+        <v>100.62</v>
       </c>
       <c r="G123" t="n">
         <v>108.72</v>
@@ -4250,12 +4250,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8.43%</t>
+          <t>7.34%</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4265,28 +4265,28 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>Xcel Energy Inc.</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4365.21</v>
+        <v>451.52</v>
       </c>
       <c r="F124" t="n">
-        <v>983.25</v>
+        <v>76.33</v>
       </c>
       <c r="G124" t="n">
-        <v>1073.82</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8.38%</t>
+          <t>7.28%</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4296,28 +4296,28 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Exelon Corporation</t>
+          <t>Take-Two Interactive Software, Inc.</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>445</v>
+        <v>453.67</v>
       </c>
       <c r="F125" t="n">
-        <v>44.06</v>
+        <v>245.52</v>
       </c>
       <c r="G125" t="n">
-        <v>48.09</v>
+        <v>264.79</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>7.19%</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4327,28 +4327,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>The TJX Companies, Inc.</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1020.24</v>
+        <v>1647.26</v>
       </c>
       <c r="F126" t="n">
-        <v>820.23</v>
+        <v>148.01</v>
       </c>
       <c r="G126" t="n">
-        <v>894.75</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>7.92%</t>
+          <t>7.13%</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4358,28 +4358,28 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Toyota Motor Corporation</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2963.11</v>
+        <v>3957.7</v>
       </c>
       <c r="F127" t="n">
-        <v>226.28</v>
+        <v>223.93</v>
       </c>
       <c r="G127" t="n">
-        <v>245.75</v>
+        <v>241.12</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>7.03%</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4389,23 +4389,23 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>American Express Company</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2748.29</v>
+        <v>2501.35</v>
       </c>
       <c r="F128" t="n">
-        <v>217.94</v>
+        <v>359.45</v>
       </c>
       <c r="G128" t="n">
-        <v>236.1</v>
+        <v>386.63</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7.68%</t>
+          <t>6.91%</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1461.89</v>
+        <v>1474.11</v>
       </c>
       <c r="F129" t="n">
-        <v>67</v>
+        <v>67.56</v>
       </c>
       <c r="G129" t="n">
         <v>72.58</v>
@@ -4436,12 +4436,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7.52%</t>
+          <t>6.78%</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4451,28 +4451,28 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Exelon Corporation</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>25566.72</v>
+        <v>452.78</v>
       </c>
       <c r="F130" t="n">
-        <v>239.16</v>
+        <v>44.83</v>
       </c>
       <c r="G130" t="n">
-        <v>258.6</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>6.77%</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4482,28 +4482,28 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1629.11</v>
+        <v>1037.59</v>
       </c>
       <c r="F131" t="n">
-        <v>533.61</v>
+        <v>834.1799999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>576.91</v>
+        <v>894.75</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>6.22%</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4513,28 +4513,28 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc.</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2947.12</v>
+        <v>2124.3</v>
       </c>
       <c r="F132" t="n">
-        <v>74.59</v>
+        <v>453.03</v>
       </c>
       <c r="G132" t="n">
-        <v>80.39</v>
+        <v>483.05</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4544,28 +4544,28 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software, Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>454.06</v>
+        <v>2344.08</v>
       </c>
       <c r="F133" t="n">
-        <v>245.73</v>
+        <v>623.91</v>
       </c>
       <c r="G133" t="n">
-        <v>264.79</v>
+        <v>664.9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>5.64%</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4575,28 +4575,28 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2844.86</v>
+        <v>4103.15</v>
       </c>
       <c r="F134" t="n">
-        <v>179</v>
+        <v>252.03</v>
       </c>
       <c r="G134" t="n">
-        <v>192.68</v>
+        <v>267.08</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>5.58%</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4606,28 +4606,28 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>BlackRock, Inc.</t>
+          <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1753.07</v>
+        <v>2814.46</v>
       </c>
       <c r="F135" t="n">
-        <v>1129.91</v>
+        <v>929.72</v>
       </c>
       <c r="G135" t="n">
-        <v>1214.03</v>
+        <v>984.7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6.68%</t>
+          <t>5.38%</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4637,28 +4637,28 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2781.64</v>
+        <v>26156.82</v>
       </c>
       <c r="F136" t="n">
-        <v>918.88</v>
+        <v>244.68</v>
       </c>
       <c r="G136" t="n">
-        <v>984.7</v>
+        <v>258.6</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4668,28 +4668,28 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Altria Group, Inc.</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1040.02</v>
+        <v>413.43</v>
       </c>
       <c r="F137" t="n">
-        <v>61.91</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="G137" t="n">
-        <v>66.3</v>
+        <v>89.37</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>6.55%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4699,28 +4699,28 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>American Electric Power Company, Inc.</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>624.28</v>
+        <v>2903.03</v>
       </c>
       <c r="F138" t="n">
-        <v>116.63</v>
+        <v>182.66</v>
       </c>
       <c r="G138" t="n">
-        <v>124.8</v>
+        <v>192.68</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>6.52%</t>
+          <t>5.18%</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4730,28 +4730,28 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Marriott International, Inc.</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2117.45</v>
+        <v>852.24</v>
       </c>
       <c r="F139" t="n">
-        <v>451.57</v>
+        <v>313.95</v>
       </c>
       <c r="G139" t="n">
-        <v>483.05</v>
+        <v>331.09</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>5.17%</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4761,28 +4761,28 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>American Express Company</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2516.94</v>
+        <v>1885.7</v>
       </c>
       <c r="F140" t="n">
-        <v>361.69</v>
+        <v>692.7</v>
       </c>
       <c r="G140" t="n">
-        <v>386.63</v>
+        <v>730.46</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>ENB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4792,28 +4792,28 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Enbridge Inc.</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>9540.9</v>
+        <v>1048.28</v>
       </c>
       <c r="F141" t="n">
-        <v>1064.29</v>
+        <v>48.02</v>
       </c>
       <c r="G141" t="n">
-        <v>1133.95</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5.94%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4823,28 +4823,28 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>683.0700000000001</v>
+        <v>1201.93</v>
       </c>
       <c r="F142" t="n">
-        <v>36.64</v>
+        <v>301.47</v>
       </c>
       <c r="G142" t="n">
-        <v>38.95</v>
+        <v>316.94</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>4.58%</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4854,28 +4854,28 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Ross Stores, Inc.</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2351.86</v>
+        <v>604.92</v>
       </c>
       <c r="F143" t="n">
-        <v>625.98</v>
+        <v>186</v>
       </c>
       <c r="G143" t="n">
-        <v>664.9</v>
+        <v>194.92</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>SATA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4885,28 +4885,28 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>Strive Asset Management, LLC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>411.13</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>84.18000000000001</v>
+        <v>96.89</v>
       </c>
       <c r="G144" t="n">
-        <v>89.37</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>BN</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4916,59 +4916,59 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mitsubishi UFJ Financial Group, Inc.</t>
+          <t>Brookfield Corporation</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2047.85</v>
+        <v>1065.65</v>
       </c>
       <c r="F145" t="n">
-        <v>17.88</v>
+        <v>47.42</v>
       </c>
       <c r="G145" t="n">
-        <v>18.9</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5.15%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>American Electric Power Company, Inc.</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>509.61</v>
+        <v>639.27</v>
       </c>
       <c r="F146" t="n">
-        <v>1063.74</v>
+        <v>119.43</v>
       </c>
       <c r="G146" t="n">
-        <v>1121.48</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4978,28 +4978,28 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>HCA Healthcare, Inc.</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1199.7</v>
+        <v>1183.63</v>
       </c>
       <c r="F147" t="n">
-        <v>300.91</v>
+        <v>505.84</v>
       </c>
       <c r="G147" t="n">
-        <v>316.94</v>
+        <v>527.55</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5009,28 +5009,28 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Strive Asset Management, LLC</t>
+          <t>Altria Group, Inc.</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1068.75</v>
       </c>
       <c r="F148" t="n">
-        <v>96.34999999999999</v>
+        <v>63.62</v>
       </c>
       <c r="G148" t="n">
-        <v>101.35</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>3.97%</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5040,28 +5040,28 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc.</t>
+          <t>Mitsubishi UFJ Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2693.3</v>
+        <v>2078.78</v>
       </c>
       <c r="F149" t="n">
-        <v>173.02</v>
+        <v>18.15</v>
       </c>
       <c r="G149" t="n">
-        <v>181.91</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5071,23 +5071,23 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Brookfield Corporation</t>
+          <t>Walmart Inc.</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1060.03</v>
+        <v>9323.450000000001</v>
       </c>
       <c r="F150" t="n">
-        <v>47.17</v>
+        <v>116.94</v>
       </c>
       <c r="G150" t="n">
-        <v>49.57</v>
+        <v>121.62</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>17368.05</v>
+        <v>17548.02</v>
       </c>
       <c r="F151" t="n">
-        <v>334.87</v>
+        <v>338.34</v>
       </c>
       <c r="G151" t="n">
         <v>351.33</v>
@@ -5118,43 +5118,43 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TBB</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>810.33</v>
+        <v>1386.36</v>
       </c>
       <c r="F152" t="n">
-        <v>236.39</v>
+        <v>22.58</v>
       </c>
       <c r="G152" t="n">
-        <v>247.94</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ENB</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5164,28 +5164,28 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Enbridge Inc.</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1052.21</v>
+        <v>2372.1</v>
       </c>
       <c r="F153" t="n">
-        <v>48.2</v>
+        <v>168.84</v>
       </c>
       <c r="G153" t="n">
-        <v>50.54</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5195,28 +5195,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>GSK plc</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>993.34</v>
+        <v>702.27</v>
       </c>
       <c r="F154" t="n">
-        <v>49.15</v>
+        <v>37.67</v>
       </c>
       <c r="G154" t="n">
-        <v>51.46</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5226,59 +5226,59 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Agnico Eagle Mines Limited</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2935.58</v>
+        <v>1085.22</v>
       </c>
       <c r="F155" t="n">
-        <v>626.62</v>
+        <v>216.16</v>
       </c>
       <c r="G155" t="n">
-        <v>655.78</v>
+        <v>223.44</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Seagate Technology Holdings plc</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1992.1</v>
+        <v>809.96</v>
       </c>
       <c r="F156" t="n">
-        <v>1512.78</v>
+        <v>371.76</v>
       </c>
       <c r="G156" t="n">
-        <v>1581.34</v>
+        <v>383.88</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5288,28 +5288,28 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1848.2</v>
+        <v>1487.72</v>
       </c>
       <c r="F157" t="n">
-        <v>150.99</v>
+        <v>303.83</v>
       </c>
       <c r="G157" t="n">
-        <v>157.54</v>
+        <v>313.54</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5319,28 +5319,28 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>The TJX Companies, Inc.</t>
+          <t>PACCAR Inc</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1705.47</v>
+        <v>634.5</v>
       </c>
       <c r="F158" t="n">
-        <v>153.24</v>
+        <v>120.81</v>
       </c>
       <c r="G158" t="n">
-        <v>159.48</v>
+        <v>124.53</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5350,28 +5350,28 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>McDonald's Corporation</t>
+          <t>Parker-Hannifin Corporation</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2206.82</v>
+        <v>1171.76</v>
       </c>
       <c r="F159" t="n">
-        <v>309.25</v>
+        <v>925.97</v>
       </c>
       <c r="G159" t="n">
-        <v>321.79</v>
+        <v>954.3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>CCZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5381,28 +5381,28 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Shell plc</t>
+          <t>Comcast Holdings Corp.</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2088.48</v>
+        <v>615.7</v>
       </c>
       <c r="F160" t="n">
-        <v>73.75</v>
+        <v>65</v>
       </c>
       <c r="G160" t="n">
-        <v>76.73999999999999</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5412,28 +5412,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>39648.73</v>
+        <v>1536.67</v>
       </c>
       <c r="F161" t="n">
-        <v>328.43</v>
+        <v>273.94</v>
       </c>
       <c r="G161" t="n">
-        <v>341.2</v>
+        <v>281.36</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5443,28 +5443,28 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>39719.89</v>
+        <v>2993.16</v>
       </c>
       <c r="F162" t="n">
-        <v>327.93</v>
+        <v>638.91</v>
       </c>
       <c r="G162" t="n">
-        <v>340.49</v>
+        <v>655.78</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5474,28 +5474,28 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>AstraZeneca PLC</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2881.98</v>
+        <v>1407.39</v>
       </c>
       <c r="F163" t="n">
-        <v>92.95</v>
+        <v>519.1900000000001</v>
       </c>
       <c r="G163" t="n">
-        <v>96.51000000000001</v>
+        <v>532.61</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SCCO</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5505,59 +5505,59 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Southern Copper Corporation</t>
+          <t>McDonald's Corporation</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1509.59</v>
+        <v>2241.65</v>
       </c>
       <c r="F164" t="n">
-        <v>184.3</v>
+        <v>314.13</v>
       </c>
       <c r="G164" t="n">
-        <v>191.22</v>
+        <v>321.79</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2626.97</v>
+        <v>524.8200000000001</v>
       </c>
       <c r="F165" t="n">
-        <v>195.93</v>
+        <v>1095.49</v>
       </c>
       <c r="G165" t="n">
-        <v>203.03</v>
+        <v>1121.48</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TBB</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5567,28 +5567,28 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1386.98</v>
+        <v>795.39</v>
       </c>
       <c r="F166" t="n">
-        <v>22.59</v>
+        <v>81.41</v>
       </c>
       <c r="G166" t="n">
-        <v>23.41</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5598,28 +5598,28 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Marriott International, Inc.</t>
+          <t>Cisco Systems, Inc.</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>867.85</v>
+        <v>3108.72</v>
       </c>
       <c r="F167" t="n">
-        <v>319.7</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="G167" t="n">
-        <v>331.09</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5629,28 +5629,28 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation</t>
+          <t>NextEra Energy, Inc.</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1854.79</v>
+        <v>1814.99</v>
       </c>
       <c r="F168" t="n">
-        <v>102.18</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="G168" t="n">
-        <v>105.81</v>
+        <v>88.95999999999999</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5660,28 +5660,28 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>The Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1394.49</v>
+        <v>1882.75</v>
       </c>
       <c r="F169" t="n">
-        <v>514.4299999999999</v>
+        <v>103.72</v>
       </c>
       <c r="G169" t="n">
-        <v>532.61</v>
+        <v>105.81</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5691,28 +5691,28 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Ross Stores, Inc.</t>
+          <t>Honeywell International Inc.</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>613.21</v>
+        <v>1488.65</v>
       </c>
       <c r="F170" t="n">
-        <v>188.55</v>
+        <v>220.91</v>
       </c>
       <c r="G170" t="n">
-        <v>194.92</v>
+        <v>225.29</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5722,28 +5722,28 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>Carvana Co.</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>9386.440000000001</v>
+        <v>1035.71</v>
       </c>
       <c r="F171" t="n">
-        <v>117.73</v>
+        <v>477.72</v>
       </c>
       <c r="G171" t="n">
-        <v>121.62</v>
+        <v>486.89</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5753,28 +5753,28 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>Baker Hughes Company</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2568.14</v>
+        <v>557.53</v>
       </c>
       <c r="F172" t="n">
-        <v>322.38</v>
+        <v>56.5</v>
       </c>
       <c r="G172" t="n">
-        <v>333.03</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5784,28 +5784,28 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4498.1</v>
+        <v>40440.64</v>
       </c>
       <c r="F173" t="n">
-        <v>399.65</v>
+        <v>335</v>
       </c>
       <c r="G173" t="n">
-        <v>412.43</v>
+        <v>341.2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CCZ</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5815,28 +5815,28 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Comcast Holdings Corp.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>615.7</v>
+        <v>40521.1</v>
       </c>
       <c r="F174" t="n">
-        <v>65</v>
+        <v>334.55</v>
       </c>
       <c r="G174" t="n">
-        <v>66.90000000000001</v>
+        <v>340.49</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5846,28 +5846,28 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2384.46</v>
+        <v>1395.03</v>
       </c>
       <c r="F175" t="n">
-        <v>169.72</v>
+        <v>127</v>
       </c>
       <c r="G175" t="n">
-        <v>174.61</v>
+        <v>129.25</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5877,28 +5877,28 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Carvana Co.</t>
+          <t>Shell plc</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1026.15</v>
+        <v>2136.62</v>
       </c>
       <c r="F176" t="n">
-        <v>473.31</v>
+        <v>75.45</v>
       </c>
       <c r="G176" t="n">
-        <v>486.89</v>
+        <v>76.73999999999999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5908,59 +5908,59 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Philip Morris International Inc.</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4227.7</v>
+        <v>2784.52</v>
       </c>
       <c r="F177" t="n">
-        <v>259.68</v>
+        <v>178.88</v>
       </c>
       <c r="G177" t="n">
-        <v>267.08</v>
+        <v>181.91</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Parker-Hannifin Corporation</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1174.32</v>
+        <v>866.11</v>
       </c>
       <c r="F178" t="n">
-        <v>927.99</v>
+        <v>252.66</v>
       </c>
       <c r="G178" t="n">
-        <v>954.3</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5970,28 +5970,28 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1496.38</v>
+        <v>4617.29</v>
       </c>
       <c r="F179" t="n">
-        <v>305.6</v>
+        <v>410.24</v>
       </c>
       <c r="G179" t="n">
-        <v>313.54</v>
+        <v>416.45</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6001,28 +6001,28 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Baker Hughes Company</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>530.88</v>
+        <v>5645.96</v>
       </c>
       <c r="F180" t="n">
-        <v>53.92</v>
+        <v>1454.59</v>
       </c>
       <c r="G180" t="n">
-        <v>55.31</v>
+        <v>1473.59</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6032,59 +6032,59 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NextEra Energy, Inc.</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1766.26</v>
+        <v>1026.69</v>
       </c>
       <c r="F181" t="n">
-        <v>84.81</v>
+        <v>50.8</v>
       </c>
       <c r="G181" t="n">
-        <v>86.94</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FER</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Ferrovial SE</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>479.33</v>
+        <v>2650.51</v>
       </c>
       <c r="F182" t="n">
-        <v>67.04000000000001</v>
+        <v>332.71</v>
       </c>
       <c r="G182" t="n">
-        <v>68.54000000000001</v>
+        <v>336.4</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6094,28 +6094,28 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PACCAR Inc</t>
+          <t>AstraZeneca PLC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>640.75</v>
+        <v>2964.14</v>
       </c>
       <c r="F183" t="n">
-        <v>122</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G183" t="n">
-        <v>124.53</v>
+        <v>96.51000000000001</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6125,28 +6125,28 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>UBS Group AG</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1498.4</v>
+        <v>2698.71</v>
       </c>
       <c r="F184" t="n">
-        <v>47.55</v>
+        <v>201.28</v>
       </c>
       <c r="G184" t="n">
-        <v>48.43</v>
+        <v>203.03</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6156,28 +6156,28 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Honeywell International Inc.</t>
+          <t>CME Group Inc.</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1492.35</v>
+        <v>1022.74</v>
       </c>
       <c r="F185" t="n">
-        <v>221.46</v>
+        <v>284.48</v>
       </c>
       <c r="G185" t="n">
-        <v>225.29</v>
+        <v>286.76</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6187,28 +6187,28 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1552.32</v>
+        <v>1891.79</v>
       </c>
       <c r="F186" t="n">
-        <v>276.73</v>
+        <v>351.32</v>
       </c>
       <c r="G186" t="n">
-        <v>281.36</v>
+        <v>353.25</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6218,28 +6218,28 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>3359.11</v>
+        <v>1749.17</v>
       </c>
       <c r="F187" t="n">
-        <v>166.72</v>
+        <v>140.97</v>
       </c>
       <c r="G187" t="n">
-        <v>169.37</v>
+        <v>141.71</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6249,28 +6249,28 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1856.41</v>
+        <v>2034.99</v>
       </c>
       <c r="F188" t="n">
-        <v>344.75</v>
+        <v>166.25</v>
       </c>
       <c r="G188" t="n">
-        <v>349.98</v>
+        <v>167.04</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6280,28 +6280,28 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>CME Group Inc.</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1016.47</v>
+        <v>5407.42</v>
       </c>
       <c r="F189" t="n">
-        <v>282.74</v>
+        <v>224.44</v>
       </c>
       <c r="G189" t="n">
-        <v>286.76</v>
+        <v>225.5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6311,59 +6311,59 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1602.05</v>
+        <v>3007.06</v>
       </c>
       <c r="F190" t="n">
-        <v>95.11</v>
+        <v>238.46</v>
       </c>
       <c r="G190" t="n">
-        <v>96.44</v>
+        <v>239.5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings plc</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>754.0599999999999</v>
+        <v>1389</v>
       </c>
       <c r="F191" t="n">
-        <v>346.1</v>
+        <v>594.95</v>
       </c>
       <c r="G191" t="n">
-        <v>350.05</v>
+        <v>597.48</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6373,28 +6373,28 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1379.36</v>
+        <v>1618.22</v>
       </c>
       <c r="F192" t="n">
-        <v>590.8200000000001</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="G192" t="n">
-        <v>597.48</v>
+        <v>96.44</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6404,28 +6404,28 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Electronic Arts Inc.</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5303.82</v>
+        <v>511.14</v>
       </c>
       <c r="F193" t="n">
-        <v>220.14</v>
+        <v>204.37</v>
       </c>
       <c r="G193" t="n">
-        <v>222.17</v>
+        <v>204.89</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6435,28 +6435,28 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corporation</t>
+          <t>UBS Group AG</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5754.1</v>
+        <v>1551.97</v>
       </c>
       <c r="F194" t="n">
-        <v>134.97</v>
+        <v>49.25</v>
       </c>
       <c r="G194" t="n">
-        <v>135.98</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6466,28 +6466,28 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5391.53</v>
+        <v>3406.06</v>
       </c>
       <c r="F195" t="n">
-        <v>1389.04</v>
+        <v>169.05</v>
       </c>
       <c r="G195" t="n">
-        <v>1398.8</v>
+        <v>169.37</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6497,28 +6497,28 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Agnico Eagle Mines Limited</t>
+          <t>Novartis AG</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1077.09</v>
+        <v>2920.79</v>
       </c>
       <c r="F196" t="n">
-        <v>214.54</v>
+        <v>152.22</v>
       </c>
       <c r="G196" t="n">
-        <v>215.95</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6528,28 +6528,28 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Novartis AG</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2823.31</v>
+        <v>2128.46</v>
       </c>
       <c r="F197" t="n">
-        <v>147.14</v>
+        <v>1616.33</v>
       </c>
       <c r="G197" t="n">
-        <v>148.1</v>
+        <v>1618.19</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6559,28 +6559,28 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Banco Santander, S.A.</t>
+          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1833.65</v>
+        <v>1484.15</v>
       </c>
       <c r="F198" t="n">
-        <v>12.4</v>
+        <v>26.11</v>
       </c>
       <c r="G198" t="n">
-        <v>12.48</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6590,28 +6590,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Electronic Arts Inc.</t>
+          <t>Exxon Mobil Corporation</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>510.22</v>
+        <v>5833.4</v>
       </c>
       <c r="F199" t="n">
-        <v>204</v>
+        <v>136.83</v>
       </c>
       <c r="G199" t="n">
-        <v>204.89</v>
+        <v>136.94</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>SCCO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6621,59 +6621,59 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
+          <t>Southern Copper Corporation</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1419.35</v>
+        <v>1595.93</v>
       </c>
       <c r="F200" t="n">
-        <v>24.97</v>
+        <v>194.84</v>
       </c>
       <c r="G200" t="n">
-        <v>25.06</v>
+        <v>194.98</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>FER</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc</t>
+          <t>Ferrovial SE</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2881.82</v>
+        <v>498.49</v>
       </c>
       <c r="F201" t="n">
-        <v>83.94</v>
+        <v>69.72</v>
       </c>
       <c r="G201" t="n">
-        <v>84.23999999999999</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6683,28 +6683,28 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc.</t>
+          <t>BHP Group Limited</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1686.63</v>
+        <v>1810.79</v>
       </c>
       <c r="F202" t="n">
-        <v>135.93</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="G202" t="n">
-        <v>136.3</v>
+        <v>70.54000000000001</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6714,28 +6714,28 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1365.48</v>
+        <v>1538.11</v>
       </c>
       <c r="F203" t="n">
-        <v>124.31</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G203" t="n">
-        <v>124.64</v>
+        <v>71.84</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6745,28 +6745,28 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>British American Tobacco p.l.c.</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3136.51</v>
+        <v>1309.69</v>
       </c>
       <c r="F204" t="n">
-        <v>72.88</v>
+        <v>60.34</v>
       </c>
       <c r="G204" t="n">
-        <v>73.06</v>
+        <v>60.38</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6776,28 +6776,28 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>HSBC Holdings plc</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>801.16</v>
+        <v>3038.03</v>
       </c>
       <c r="F205" t="n">
-        <v>82</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="G205" t="n">
-        <v>82.19</v>
+        <v>88.54000000000001</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6807,28 +6807,28 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>British American Tobacco p.l.c.</t>
+          <t>Rio Tinto Group</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1284.08</v>
+        <v>1854.33</v>
       </c>
       <c r="F206" t="n">
-        <v>59.16</v>
+        <v>92.91</v>
       </c>
       <c r="G206" t="n">
-        <v>59.24</v>
+        <v>92.94</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6838,28 +6838,28 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1734.5</v>
+        <v>3165.35</v>
       </c>
       <c r="F207" t="n">
-        <v>67.52</v>
+        <v>73.55</v>
       </c>
       <c r="G207" t="n">
-        <v>67.56</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6869,48 +6869,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Rio Tinto Group</t>
+          <t>Banco Santander, S.A.</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1804.84</v>
+        <v>1929.77</v>
       </c>
       <c r="F208" t="n">
-        <v>90.43000000000001</v>
+        <v>13.05</v>
       </c>
       <c r="G208" t="n">
-        <v>90.44</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>TTE</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>常规</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>TotalEnergies SE</t>
-        </is>
-      </c>
-      <c r="E209" t="n">
-        <v>1482.83</v>
-      </c>
-      <c r="F209" t="n">
-        <v>69.20999999999999</v>
-      </c>
-      <c r="G209" t="n">
-        <v>69.20999999999999</v>
+        <v>13.05</v>
       </c>
     </row>
   </sheetData>

--- a/美股回撤分析报告.xlsx
+++ b/美股回撤分析报告.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>82.06%</t>
+          <t>82.52%</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>530.33</v>
+        <v>516.67</v>
       </c>
       <c r="F2" t="n">
-        <v>55.51</v>
+        <v>54.08</v>
       </c>
       <c r="G2" t="n">
         <v>309.44</v>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>77.84%</t>
+          <t>77.86%</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>249.95</v>
+        <v>249.7</v>
       </c>
       <c r="F3" t="n">
-        <v>182.99</v>
+        <v>182.81</v>
       </c>
       <c r="G3" t="n">
         <v>825.62</v>
@@ -530,7 +530,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>72.29%</t>
+          <t>72.11%</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>352.36</v>
+        <v>354.73</v>
       </c>
       <c r="F4" t="n">
-        <v>133.86</v>
+        <v>134.76</v>
       </c>
       <c r="G4" t="n">
         <v>483.13</v>
@@ -561,7 +561,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>70.24%</t>
+          <t>70.82%</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>467.52</v>
+        <v>458.47</v>
       </c>
       <c r="F5" t="n">
-        <v>161.58</v>
+        <v>158.45</v>
       </c>
       <c r="G5" t="n">
         <v>543</v>
@@ -592,7 +592,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>69.98%</t>
+          <t>70.14%</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2053.9</v>
+        <v>2043.34</v>
       </c>
       <c r="F6" t="n">
-        <v>114.79</v>
+        <v>114.2</v>
       </c>
       <c r="G6" t="n">
         <v>382.43</v>
@@ -623,12 +623,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>64.08%</t>
+          <t>64.23%</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -638,28 +638,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery, Inc.</t>
+          <t>The Kraft Heinz Company</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>695.99</v>
+        <v>274.49</v>
       </c>
       <c r="F7" t="n">
-        <v>28.07</v>
+        <v>23.19</v>
       </c>
       <c r="G7" t="n">
-        <v>78.14</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>63.45%</t>
+          <t>64.19%</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -669,28 +669,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Kraft Heinz Company</t>
+          <t>Warner Bros. Discovery, Inc.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>280.53</v>
+        <v>693.76</v>
       </c>
       <c r="F8" t="n">
-        <v>23.7</v>
+        <v>27.98</v>
       </c>
       <c r="G8" t="n">
-        <v>64.84</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>57.48%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -700,28 +700,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Adobe Inc.</t>
+          <t>Novo Nordisk A/S</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1245</v>
+        <v>2680.75</v>
       </c>
       <c r="F9" t="n">
-        <v>297.42</v>
+        <v>60.33</v>
       </c>
       <c r="G9" t="n">
-        <v>699.54</v>
+        <v>143.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>56.22%</t>
+          <t>57.17%</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -731,23 +731,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Novo Nordisk A/S</t>
+          <t>Adobe Inc.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2794.5</v>
+        <v>1254.04</v>
       </c>
       <c r="F10" t="n">
-        <v>62.89</v>
+        <v>299.58</v>
       </c>
       <c r="G10" t="n">
-        <v>143.64</v>
+        <v>699.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>55.31%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>288.9</v>
+        <v>287.69</v>
       </c>
       <c r="F11" t="n">
-        <v>73.67</v>
+        <v>73.36</v>
       </c>
       <c r="G11" t="n">
         <v>164.86</v>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>52.05%</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2560.81</v>
+        <v>2663.35</v>
       </c>
       <c r="F12" t="n">
-        <v>282.7</v>
+        <v>294.02</v>
       </c>
       <c r="G12" t="n">
         <v>613.22</v>
@@ -809,7 +809,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49.71%</t>
+          <t>51.64%</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1517.74</v>
+        <v>1459.54</v>
       </c>
       <c r="F13" t="n">
-        <v>106.91</v>
+        <v>102.81</v>
       </c>
       <c r="G13" t="n">
         <v>212.6</v>
@@ -840,7 +840,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49.19%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5025.1</v>
+        <v>4964.77</v>
       </c>
       <c r="F14" t="n">
-        <v>174.9</v>
+        <v>172.8</v>
       </c>
       <c r="G14" t="n">
         <v>344.21</v>
@@ -871,7 +871,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>46.38%</t>
+          <t>47.67%</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1506.71</v>
+        <v>1470.32</v>
       </c>
       <c r="F15" t="n">
-        <v>26.5</v>
+        <v>25.86</v>
       </c>
       <c r="G15" t="n">
         <v>49.42</v>
@@ -902,12 +902,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>45.14%</t>
+          <t>45.91%</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -917,28 +917,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>537.46</v>
+        <v>1367.68</v>
       </c>
       <c r="F16" t="n">
-        <v>118.9</v>
+        <v>129.62</v>
       </c>
       <c r="G16" t="n">
-        <v>216.72</v>
+        <v>239.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.89%</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -948,23 +948,23 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1390.68</v>
+        <v>530.14</v>
       </c>
       <c r="F17" t="n">
-        <v>131.8</v>
+        <v>117.28</v>
       </c>
       <c r="G17" t="n">
-        <v>239.62</v>
+        <v>216.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>44.23%</t>
+          <t>44.76%</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1974.71</v>
+        <v>1955.96</v>
       </c>
       <c r="F18" t="n">
-        <v>110.61</v>
+        <v>109.56</v>
       </c>
       <c r="G18" t="n">
         <v>198.35</v>
@@ -995,7 +995,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>43.85%</t>
+          <t>44.53%</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1915.08</v>
+        <v>1891.82</v>
       </c>
       <c r="F19" t="n">
-        <v>244.56</v>
+        <v>241.59</v>
       </c>
       <c r="G19" t="n">
         <v>435.56</v>
@@ -1026,7 +1026,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>43.12%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1131.11</v>
+        <v>1119.68</v>
       </c>
       <c r="F20" t="n">
-        <v>28.7</v>
+        <v>28.41</v>
       </c>
       <c r="G20" t="n">
         <v>50.46</v>
@@ -1057,12 +1057,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>43.04%</t>
+          <t>43.12%</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1072,28 +1072,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Limited</t>
+          <t>Zscaler, Inc.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4123.39</v>
+        <v>341.19</v>
       </c>
       <c r="F21" t="n">
-        <v>172.72</v>
+        <v>213.95</v>
       </c>
       <c r="G21" t="n">
-        <v>303.26</v>
+        <v>376.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>41.59%</t>
+          <t>42.08%</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1103,28 +1103,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Zscaler, Inc.</t>
+          <t>Alibaba Group Holding Limited</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>350.31</v>
+        <v>4193.57</v>
       </c>
       <c r="F22" t="n">
-        <v>219.67</v>
+        <v>175.66</v>
       </c>
       <c r="G22" t="n">
-        <v>376.11</v>
+        <v>303.26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>39.88%</t>
+          <t>41.74%</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1134,28 +1134,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Airbnb, Inc.</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>809.5</v>
+        <v>1166.67</v>
       </c>
       <c r="F23" t="n">
-        <v>132.22</v>
+        <v>109.96</v>
       </c>
       <c r="G23" t="n">
-        <v>219.94</v>
+        <v>188.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>39.42%</t>
+          <t>40.19%</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1165,28 +1165,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Airbnb, Inc.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>503.51</v>
+        <v>805.4</v>
       </c>
       <c r="F24" t="n">
-        <v>188.58</v>
+        <v>131.55</v>
       </c>
       <c r="G24" t="n">
-        <v>311.28</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>39.14%</t>
+          <t>39.24%</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1196,28 +1196,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1218.88</v>
+        <v>504.95</v>
       </c>
       <c r="F25" t="n">
-        <v>114.88</v>
+        <v>189.12</v>
       </c>
       <c r="G25" t="n">
-        <v>188.75</v>
+        <v>311.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>38.34%</t>
+          <t>39.05%</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1227,28 +1227,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mizuho Financial Group, Inc.</t>
+          <t>Roper Technologies, Inc.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1074.05</v>
+        <v>387.89</v>
       </c>
       <c r="F26" t="n">
-        <v>8.68</v>
+        <v>360.37</v>
       </c>
       <c r="G26" t="n">
-        <v>14.08</v>
+        <v>591.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>37.91%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1258,28 +1258,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Anheuser-Busch InBev SA/NV</t>
+          <t>Mizuho Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1367.04</v>
+        <v>1067.87</v>
       </c>
       <c r="F27" t="n">
-        <v>70.25</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>113.15</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>37.59%</t>
+          <t>38.29%</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1289,59 +1289,59 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Anheuser-Busch InBev SA/NV</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2175.61</v>
+        <v>1358.67</v>
       </c>
       <c r="F28" t="n">
-        <v>228.53</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>366.19</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>37.55%</t>
+          <t>37.93%</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Roper Technologies, Inc.</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>397.47</v>
+        <v>436.79</v>
       </c>
       <c r="F29" t="n">
-        <v>369.27</v>
+        <v>549.86</v>
       </c>
       <c r="G29" t="n">
-        <v>591.26</v>
+        <v>885.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>37.29%</t>
+          <t>37.75%</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1351,28 +1351,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Copart, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>390.79</v>
+        <v>2170.18</v>
       </c>
       <c r="F30" t="n">
-        <v>40.37</v>
+        <v>227.96</v>
       </c>
       <c r="G30" t="n">
-        <v>64.38</v>
+        <v>366.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>36.19%</t>
+          <t>37.64%</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3626.3</v>
+        <v>796.1</v>
       </c>
       <c r="F31" t="n">
-        <v>85.58</v>
+        <v>751.13</v>
       </c>
       <c r="G31" t="n">
-        <v>134.12</v>
+        <v>1204.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>35.97%</t>
+          <t>36.91%</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1413,28 +1413,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
+          <t>Copart, Inc.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>817.4299999999999</v>
+        <v>393.21</v>
       </c>
       <c r="F32" t="n">
-        <v>771.25</v>
+        <v>40.62</v>
       </c>
       <c r="G32" t="n">
-        <v>1204.52</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>34.82%</t>
+          <t>36.89%</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1444,28 +1444,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Spotify Technology S.A.</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1053.56</v>
+        <v>3590.34</v>
       </c>
       <c r="F33" t="n">
-        <v>511.7</v>
+        <v>84.64</v>
       </c>
       <c r="G33" t="n">
-        <v>785</v>
+        <v>134.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>34.73%</t>
+          <t>35.48%</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1475,28 +1475,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>CoStar Group, Inc.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>714.9400000000001</v>
+        <v>276.33</v>
       </c>
       <c r="F34" t="n">
-        <v>82.93000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="G34" t="n">
-        <v>127.06</v>
+        <v>101.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34.47%</t>
+          <t>35.36%</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1506,28 +1506,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CoStar Group, Inc.</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>280.66</v>
+        <v>367.76</v>
       </c>
       <c r="F35" t="n">
-        <v>66.22</v>
+        <v>102.45</v>
       </c>
       <c r="G35" t="n">
-        <v>101.05</v>
+        <v>158.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>33.79%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1537,28 +1537,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Spotify Technology S.A.</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>376.7</v>
+        <v>1047.38</v>
       </c>
       <c r="F36" t="n">
-        <v>104.94</v>
+        <v>508.7</v>
       </c>
       <c r="G36" t="n">
-        <v>158.49</v>
+        <v>785</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>32.73%</t>
+          <t>34.19%</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1568,28 +1568,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1518.39</v>
+        <v>720.89</v>
       </c>
       <c r="F37" t="n">
-        <v>545.4</v>
+        <v>83.62</v>
       </c>
       <c r="G37" t="n">
-        <v>810.72</v>
+        <v>127.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>32.67%</t>
+          <t>33.55%</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1599,28 +1599,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>302.18</v>
+        <v>1499.74</v>
       </c>
       <c r="F38" t="n">
-        <v>216.28</v>
+        <v>538.7</v>
       </c>
       <c r="G38" t="n">
-        <v>321.24</v>
+        <v>810.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>32.46%</t>
+          <t>31.82%</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1630,28 +1630,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T-Mobile US, Inc.</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2076.29</v>
+        <v>306.02</v>
       </c>
       <c r="F39" t="n">
-        <v>184.49</v>
+        <v>219.03</v>
       </c>
       <c r="G39" t="n">
-        <v>273.15</v>
+        <v>321.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>31.54%</t>
+          <t>31.81%</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1661,28 +1661,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc.</t>
+          <t>T-Mobile US, Inc.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1074.07</v>
+        <v>2096.09</v>
       </c>
       <c r="F40" t="n">
-        <v>116</v>
+        <v>186.25</v>
       </c>
       <c r="G40" t="n">
-        <v>169.44</v>
+        <v>273.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>31.47%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1692,28 +1692,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>QUALCOMM Incorporated</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>484.66</v>
+        <v>1635.42</v>
       </c>
       <c r="F41" t="n">
-        <v>138.21</v>
+        <v>152.7</v>
       </c>
       <c r="G41" t="n">
-        <v>201.69</v>
+        <v>223.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>31.45%</t>
+          <t>31.43%</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1723,59 +1723,59 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>QUALCOMM Incorporated</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1639.06</v>
+        <v>1677.04</v>
       </c>
       <c r="F42" t="n">
-        <v>153.04</v>
+        <v>270.43</v>
       </c>
       <c r="G42" t="n">
-        <v>223.25</v>
+        <v>394.41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>31.12%</t>
+          <t>31.08%</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>KKR &amp; Co. Inc.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>484.74</v>
+        <v>1081.2</v>
       </c>
       <c r="F43" t="n">
-        <v>610.22</v>
+        <v>116.77</v>
       </c>
       <c r="G43" t="n">
-        <v>885.92</v>
+        <v>169.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>30.07%</t>
+          <t>30.31%</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1785,23 +1785,23 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1710.34</v>
+        <v>492.9</v>
       </c>
       <c r="F44" t="n">
-        <v>275.8</v>
+        <v>140.56</v>
       </c>
       <c r="G44" t="n">
-        <v>394.41</v>
+        <v>201.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29.95%</t>
+          <t>30.15%</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1046.15</v>
+        <v>1043.21</v>
       </c>
       <c r="F45" t="n">
-        <v>288.76</v>
+        <v>287.95</v>
       </c>
       <c r="G45" t="n">
         <v>412.23</v>
@@ -1832,43 +1832,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>29.48%</t>
+          <t>29.46%</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>ALNY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Alnylam Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2194.3</v>
+        <v>461.84</v>
       </c>
       <c r="F46" t="n">
-        <v>43.93</v>
+        <v>349.58</v>
       </c>
       <c r="G46" t="n">
-        <v>62.29</v>
+        <v>495.55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28.84%</t>
+          <t>28.94%</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1878,54 +1878,54 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>626.12</v>
+        <v>362.88</v>
       </c>
       <c r="F47" t="n">
-        <v>81.70999999999999</v>
+        <v>26.71</v>
       </c>
       <c r="G47" t="n">
-        <v>114.82</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28.41%</t>
+          <t>28.51%</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ALNY</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Alnylam Pharmaceuticals, Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>468.67</v>
+        <v>628.95</v>
       </c>
       <c r="F48" t="n">
-        <v>354.75</v>
+        <v>82.08</v>
       </c>
       <c r="G48" t="n">
-        <v>495.55</v>
+        <v>114.82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27.37%</t>
+          <t>27.61%</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>893.72</v>
+        <v>890.7</v>
       </c>
       <c r="F49" t="n">
-        <v>207.36</v>
+        <v>206.66</v>
       </c>
       <c r="G49" t="n">
         <v>285.5</v>
@@ -1956,7 +1956,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.26%</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1838.59</v>
+        <v>1834.53</v>
       </c>
       <c r="F50" t="n">
-        <v>543.5599999999999</v>
+        <v>542.36</v>
       </c>
       <c r="G50" t="n">
         <v>745.61</v>
@@ -1987,38 +1987,38 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.73%</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>Insmed Incorporated</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>374.83</v>
+        <v>332.47</v>
       </c>
       <c r="F51" t="n">
-        <v>27.59</v>
+        <v>155.89</v>
       </c>
       <c r="G51" t="n">
-        <v>37.59</v>
+        <v>212.75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25.51%</t>
+          <t>26.57%</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1357.64</v>
+        <v>1338.41</v>
       </c>
       <c r="F52" t="n">
-        <v>22.6</v>
+        <v>22.28</v>
       </c>
       <c r="G52" t="n">
         <v>30.34</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2064,28 +2064,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Old Dominion Freight Line, Inc.</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2729.6</v>
+        <v>363</v>
       </c>
       <c r="F53" t="n">
-        <v>233.94</v>
+        <v>172.72</v>
       </c>
       <c r="G53" t="n">
-        <v>313.28</v>
+        <v>231.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>24.59%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2095,28 +2095,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Old Dominion Freight Line, Inc.</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>366.62</v>
+        <v>1801.2</v>
       </c>
       <c r="F54" t="n">
-        <v>174.44</v>
+        <v>146.79</v>
       </c>
       <c r="G54" t="n">
-        <v>231.32</v>
+        <v>194.94</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>24.53%</t>
+          <t>24.63%</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2126,59 +2126,59 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1790.03</v>
+        <v>2754.92</v>
       </c>
       <c r="F55" t="n">
-        <v>137.5</v>
+        <v>236.11</v>
       </c>
       <c r="G55" t="n">
-        <v>182.19</v>
+        <v>313.28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>24.38%</t>
+          <t>24.18%</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>The Progressive Corporation</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1219.76</v>
+        <v>3750.34</v>
       </c>
       <c r="F56" t="n">
-        <v>208.08</v>
+        <v>157.35</v>
       </c>
       <c r="G56" t="n">
-        <v>275.18</v>
+        <v>207.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>23.87%</t>
+          <t>23.75%</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2188,59 +2188,59 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1821.08</v>
+        <v>1808.52</v>
       </c>
       <c r="F57" t="n">
-        <v>148.41</v>
+        <v>138.92</v>
       </c>
       <c r="G57" t="n">
-        <v>194.94</v>
+        <v>182.19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>23.55%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Insmed Incorporated</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>346.87</v>
+        <v>1845.76</v>
       </c>
       <c r="F58" t="n">
-        <v>162.64</v>
+        <v>106.05</v>
       </c>
       <c r="G58" t="n">
-        <v>212.75</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22.87%</t>
+          <t>22.74%</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2250,28 +2250,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>Automatic Data Processing, Inc.</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>961.76</v>
+        <v>1015.52</v>
       </c>
       <c r="F59" t="n">
-        <v>502.7</v>
+        <v>250.69</v>
       </c>
       <c r="G59" t="n">
-        <v>651.73</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>22.41%</t>
+          <t>22.69%</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2281,28 +2281,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Diamondback Energy, Inc.</t>
+          <t>The Progressive Corporation</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>460.63</v>
+        <v>1247.08</v>
       </c>
       <c r="F60" t="n">
-        <v>159.12</v>
+        <v>212.74</v>
       </c>
       <c r="G60" t="n">
-        <v>205.08</v>
+        <v>275.18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>22.16%</t>
+          <t>22.61%</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2312,28 +2312,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>571.03</v>
+        <v>1607.82</v>
       </c>
       <c r="F61" t="n">
-        <v>268.09</v>
+        <v>224.54</v>
       </c>
       <c r="G61" t="n">
-        <v>344.39</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21.98%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2343,28 +2343,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Bristol-Myers Squibb Company</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1247.32</v>
+        <v>1111.93</v>
       </c>
       <c r="F62" t="n">
-        <v>99.87</v>
+        <v>54.62</v>
       </c>
       <c r="G62" t="n">
-        <v>128.01</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21.95%</t>
+          <t>22.09%</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2374,28 +2374,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Microchip Technology Incorporated</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>406.2</v>
+        <v>571.54</v>
       </c>
       <c r="F63" t="n">
-        <v>75.16</v>
+        <v>268.33</v>
       </c>
       <c r="G63" t="n">
-        <v>96.3</v>
+        <v>344.39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.85%</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2405,28 +2405,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Diamondback Energy, Inc.</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1884.39</v>
+        <v>463.96</v>
       </c>
       <c r="F64" t="n">
-        <v>108.27</v>
+        <v>160.27</v>
       </c>
       <c r="G64" t="n">
-        <v>138.63</v>
+        <v>205.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21.57%</t>
+          <t>21.78%</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2436,28 +2436,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Automatic Data Processing, Inc.</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1030.99</v>
+        <v>1663.75</v>
       </c>
       <c r="F65" t="n">
-        <v>254.51</v>
+        <v>79.78</v>
       </c>
       <c r="G65" t="n">
-        <v>324.5</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21.16%</t>
+          <t>21.69%</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2467,28 +2467,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Company</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1131.06</v>
+        <v>2436.65</v>
       </c>
       <c r="F66" t="n">
-        <v>55.56</v>
+        <v>48.78</v>
       </c>
       <c r="G66" t="n">
-        <v>70.48</v>
+        <v>62.29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21.05%</t>
+          <t>21.54%</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2498,28 +2498,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc.</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1644.59</v>
+        <v>978.3099999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>23</v>
+        <v>511.35</v>
       </c>
       <c r="G67" t="n">
-        <v>29.13</v>
+        <v>651.73</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20.35%</t>
+          <t>20.81%</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2529,28 +2529,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NXP Semiconductors N.V.</t>
+          <t>Mondelez International, Inc.</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>578.4</v>
+        <v>746.99</v>
       </c>
       <c r="F68" t="n">
-        <v>229.42</v>
+        <v>57.73</v>
       </c>
       <c r="G68" t="n">
-        <v>288.03</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20.35%</t>
+          <t>20.79%</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2560,54 +2560,54 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1694.19</v>
+        <v>1266.3</v>
       </c>
       <c r="F69" t="n">
-        <v>81.23999999999999</v>
+        <v>101.39</v>
       </c>
       <c r="G69" t="n">
-        <v>101.99</v>
+        <v>128.01</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20.15%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Sanofi</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3949.35</v>
+        <v>1111.7</v>
       </c>
       <c r="F70" t="n">
-        <v>165.7</v>
+        <v>45.77</v>
       </c>
       <c r="G70" t="n">
-        <v>207.52</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>19.58%</t>
+          <t>19.47%</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>15778.49</v>
+        <v>15799.82</v>
       </c>
       <c r="F71" t="n">
-        <v>332.79</v>
+        <v>333.24</v>
       </c>
       <c r="G71" t="n">
         <v>413.82</v>
@@ -2638,12 +2638,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>19.04%</t>
+          <t>18.71%</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2653,28 +2653,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mondelez International, Inc.</t>
+          <t>Sumitomo Mitsui Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>763.6900000000001</v>
+        <v>1344.83</v>
       </c>
       <c r="F72" t="n">
-        <v>59.02</v>
+        <v>20.95</v>
       </c>
       <c r="G72" t="n">
-        <v>72.90000000000001</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>18.75%</t>
+          <t>18.28%</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2684,28 +2684,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Prologis, Inc.</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1688.09</v>
+        <v>1180.87</v>
       </c>
       <c r="F73" t="n">
-        <v>235.75</v>
+        <v>127.13</v>
       </c>
       <c r="G73" t="n">
-        <v>290.14</v>
+        <v>155.57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>17.94%</t>
+          <t>17.87%</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2715,28 +2715,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>HDFC Bank Limited</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1255.11</v>
+        <v>1657.16</v>
       </c>
       <c r="F74" t="n">
-        <v>183.5</v>
+        <v>32.31</v>
       </c>
       <c r="G74" t="n">
-        <v>223.61</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>17.54%</t>
+          <t>17.83%</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2746,28 +2746,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>HDFC Bank Limited</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1663.83</v>
+        <v>1280.67</v>
       </c>
       <c r="F75" t="n">
-        <v>32.44</v>
+        <v>183.74</v>
       </c>
       <c r="G75" t="n">
-        <v>39.34</v>
+        <v>223.61</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>17.51%</t>
+          <t>17.37%</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2777,28 +2777,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>AT&amp;T Inc.</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1153.48</v>
+        <v>1721.1</v>
       </c>
       <c r="F76" t="n">
-        <v>47.49</v>
+        <v>24.07</v>
       </c>
       <c r="G76" t="n">
-        <v>57.57</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>17.27%</t>
+          <t>17.28%</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2808,28 +2808,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Prologis, Inc.</t>
+          <t>Starbucks Corporation</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1195.45</v>
+        <v>1084.12</v>
       </c>
       <c r="F77" t="n">
-        <v>128.7</v>
+        <v>95.16</v>
       </c>
       <c r="G77" t="n">
-        <v>155.57</v>
+        <v>115.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>17.16%</t>
+          <t>17.28%</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2839,28 +2839,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Financial Group, Inc.</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1370.51</v>
+        <v>2033.08</v>
       </c>
       <c r="F78" t="n">
-        <v>21.35</v>
+        <v>148.5</v>
       </c>
       <c r="G78" t="n">
-        <v>25.77</v>
+        <v>179.53</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>17.13%</t>
+          <t>17.24%</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2870,28 +2870,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PepsiCo, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2036.91</v>
+        <v>1182.82</v>
       </c>
       <c r="F79" t="n">
-        <v>148.78</v>
+        <v>469.19</v>
       </c>
       <c r="G79" t="n">
-        <v>179.53</v>
+        <v>566.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.12%</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2901,28 +2901,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Starbucks Corporation</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1088.43</v>
+        <v>760.17</v>
       </c>
       <c r="F80" t="n">
-        <v>95.72</v>
+        <v>189.16</v>
       </c>
       <c r="G80" t="n">
-        <v>115.04</v>
+        <v>228.23</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>16.38%</t>
+          <t>16.67%</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2932,28 +2932,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Capital One Financial Corporation</t>
+          <t>NXP Semiconductors N.V.</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1380.24</v>
+        <v>605.15</v>
       </c>
       <c r="F81" t="n">
-        <v>217.11</v>
+        <v>240.03</v>
       </c>
       <c r="G81" t="n">
-        <v>259.64</v>
+        <v>288.03</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>16.22%</t>
+          <t>16.63%</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2963,28 +2963,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Microchip Technology Incorporated</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>768.41</v>
+        <v>433.87</v>
       </c>
       <c r="F82" t="n">
-        <v>191.21</v>
+        <v>80.28</v>
       </c>
       <c r="G82" t="n">
-        <v>228.23</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>15.92%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2994,28 +2994,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Merck &amp; Co., Inc.</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1201.65</v>
+        <v>2670.13</v>
       </c>
       <c r="F83" t="n">
-        <v>476.66</v>
+        <v>106.9</v>
       </c>
       <c r="G83" t="n">
-        <v>566.9</v>
+        <v>127.87</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.24%</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3025,28 +3025,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Merck &amp; Co., Inc.</t>
+          <t>GE HealthCare Technologies Inc.</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2695.61</v>
+        <v>361.87</v>
       </c>
       <c r="F84" t="n">
-        <v>107.92</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>127.87</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>15.43%</t>
+          <t>15.89%</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3056,28 +3056,28 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1291.47</v>
+        <v>3442.94</v>
       </c>
       <c r="F85" t="n">
-        <v>100.69</v>
+        <v>147.34</v>
       </c>
       <c r="G85" t="n">
-        <v>119.06</v>
+        <v>175.18</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>15.43%</t>
+          <t>15.89%</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cadence Design Systems, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>867.53</v>
+        <v>16855.52</v>
       </c>
       <c r="F86" t="n">
-        <v>318.37</v>
+        <v>668.73</v>
       </c>
       <c r="G86" t="n">
-        <v>376.45</v>
+        <v>795.0599999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>15.36%</t>
+          <t>15.88%</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3118,28 +3118,28 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Capital One Financial Corporation</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>16962.39</v>
+        <v>1388.51</v>
       </c>
       <c r="F87" t="n">
-        <v>672.97</v>
+        <v>218.41</v>
       </c>
       <c r="G87" t="n">
-        <v>795.0599999999999</v>
+        <v>259.64</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>15.32%</t>
+          <t>15.35%</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3149,28 +3149,28 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3471.88</v>
+        <v>1292.75</v>
       </c>
       <c r="F88" t="n">
-        <v>148.34</v>
+        <v>100.79</v>
       </c>
       <c r="G88" t="n">
-        <v>175.18</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>15.12%</t>
+          <t>15.25%</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>GE HealthCare Technologies Inc.</t>
+          <t>Intuitive Surgical, Inc.</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>366.71</v>
+        <v>1871.39</v>
       </c>
       <c r="F89" t="n">
-        <v>80.31999999999999</v>
+        <v>522.04</v>
       </c>
       <c r="G89" t="n">
-        <v>94.63</v>
+        <v>616</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14.77%</t>
+          <t>14.87%</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3211,23 +3211,23 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Intuitive Surgical, Inc.</t>
+          <t>Cadence Design Systems, Inc.</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1882.14</v>
+        <v>873.3</v>
       </c>
       <c r="F90" t="n">
-        <v>525.04</v>
+        <v>320.49</v>
       </c>
       <c r="G90" t="n">
-        <v>616</v>
+        <v>376.45</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>14.51%</t>
+          <t>14.35%</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1388.25</v>
+        <v>1390.92</v>
       </c>
       <c r="F91" t="n">
-        <v>93.61</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="G91" t="n">
         <v>109.5</v>
@@ -3258,12 +3258,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14.36%</t>
+          <t>14.24%</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3273,28 +3273,28 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Eaton Corporation plc</t>
+          <t>MercadoLibre, Inc.</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1328.25</v>
+        <v>1150.12</v>
       </c>
       <c r="F92" t="n">
-        <v>341.19</v>
+        <v>2268.6</v>
       </c>
       <c r="G92" t="n">
-        <v>398.4</v>
+        <v>2645.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>13.62%</t>
+          <t>13.76%</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>IBN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3304,28 +3304,28 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>14330.96</v>
+        <v>1057.81</v>
       </c>
       <c r="F93" t="n">
-        <v>430.9</v>
+        <v>29.58</v>
       </c>
       <c r="G93" t="n">
-        <v>498.83</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>13.28%</t>
+          <t>13.51%</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3335,28 +3335,28 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4704.57</v>
+        <v>14349.58</v>
       </c>
       <c r="F94" t="n">
-        <v>520.41</v>
+        <v>431.46</v>
       </c>
       <c r="G94" t="n">
-        <v>600.08</v>
+        <v>498.83</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13.26%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IBN</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3366,28 +3366,28 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1063.89</v>
+        <v>500.78</v>
       </c>
       <c r="F95" t="n">
-        <v>29.75</v>
+        <v>43.62</v>
       </c>
       <c r="G95" t="n">
-        <v>34.3</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13.24%</t>
+          <t>13.12%</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MercadoLibre, Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1163.5</v>
+        <v>4713.25</v>
       </c>
       <c r="F96" t="n">
-        <v>2295</v>
+        <v>521.37</v>
       </c>
       <c r="G96" t="n">
-        <v>2645.22</v>
+        <v>600.08</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>13.17%</t>
+          <t>12.99%</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>35722.31</v>
+        <v>35800.36</v>
       </c>
       <c r="F97" t="n">
-        <v>480.58</v>
+        <v>481.63</v>
       </c>
       <c r="G97" t="n">
         <v>553.5</v>
@@ -3444,12 +3444,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>13.06%</t>
+          <t>12.82%</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3459,23 +3459,23 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Eaton Corporation plc</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6277.18</v>
+        <v>1352.12</v>
       </c>
       <c r="F98" t="n">
-        <v>325.26</v>
+        <v>347.32</v>
       </c>
       <c r="G98" t="n">
-        <v>374.11</v>
+        <v>398.4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12.87%</t>
+          <t>12.67%</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1657.9</v>
+        <v>1661.69</v>
       </c>
       <c r="F99" t="n">
-        <v>39.32</v>
+        <v>39.41</v>
       </c>
       <c r="G99" t="n">
         <v>45.13</v>
@@ -3506,12 +3506,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12.74%</t>
+          <t>12.62%</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3521,28 +3521,28 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>504.57</v>
+        <v>1786.63</v>
       </c>
       <c r="F100" t="n">
-        <v>43.95</v>
+        <v>145.96</v>
       </c>
       <c r="G100" t="n">
-        <v>50.37</v>
+        <v>167.04</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>12.23%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3552,28 +3552,28 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>Booking Holdings Inc.</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1259.34</v>
+        <v>1648.11</v>
       </c>
       <c r="F101" t="n">
-        <v>183.49</v>
+        <v>5085.22</v>
       </c>
       <c r="G101" t="n">
-        <v>209.05</v>
+        <v>5818.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>12.01%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3583,28 +3583,28 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1355.96</v>
+        <v>6310.38</v>
       </c>
       <c r="F102" t="n">
-        <v>354.57</v>
+        <v>326.98</v>
       </c>
       <c r="G102" t="n">
-        <v>402.95</v>
+        <v>374.11</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>11.43%</t>
+          <t>12.11%</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3614,28 +3614,28 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc.</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1670.21</v>
+        <v>3085.12</v>
       </c>
       <c r="F103" t="n">
-        <v>5153.41</v>
+        <v>292.48</v>
       </c>
       <c r="G103" t="n">
-        <v>5818.24</v>
+        <v>332.79</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>11.15%</t>
+          <t>12.01%</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3645,28 +3645,28 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>45898.97</v>
+        <v>1262.43</v>
       </c>
       <c r="F104" t="n">
-        <v>188.52</v>
+        <v>183.94</v>
       </c>
       <c r="G104" t="n">
-        <v>212.18</v>
+        <v>209.05</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>11.06%</t>
+          <t>11.99%</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3676,28 +3676,28 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>The Home Depot, Inc.</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1847.25</v>
+        <v>3736.15</v>
       </c>
       <c r="F105" t="n">
-        <v>146.69</v>
+        <v>375.3</v>
       </c>
       <c r="G105" t="n">
-        <v>164.94</v>
+        <v>426.44</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10.81%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3707,28 +3707,28 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>The Home Depot, Inc.</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3786.53</v>
+        <v>1368.43</v>
       </c>
       <c r="F106" t="n">
-        <v>380.36</v>
+        <v>357.83</v>
       </c>
       <c r="G106" t="n">
-        <v>426.44</v>
+        <v>402.95</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10.61%</t>
+          <t>11.15%</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3738,28 +3738,28 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3137.75</v>
+        <v>37892.48</v>
       </c>
       <c r="F107" t="n">
-        <v>297.47</v>
+        <v>256.44</v>
       </c>
       <c r="G107" t="n">
-        <v>332.79</v>
+        <v>288.62</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10.59%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3769,28 +3769,28 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Toyota Motor Corporation</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>8175.23</v>
+        <v>2866.34</v>
       </c>
       <c r="F108" t="n">
-        <v>300.31</v>
+        <v>218.89</v>
       </c>
       <c r="G108" t="n">
-        <v>335.87</v>
+        <v>245.75</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10.52%</t>
+          <t>10.85%</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3800,28 +3800,28 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>38162.88</v>
+        <v>1350.69</v>
       </c>
       <c r="F109" t="n">
-        <v>258.27</v>
+        <v>227.71</v>
       </c>
       <c r="G109" t="n">
-        <v>288.62</v>
+        <v>255.44</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9.87%</t>
+          <t>10.68%</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3831,28 +3831,28 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>IDEXX Laboratories, Inc.</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1787.64</v>
+        <v>550.22</v>
       </c>
       <c r="F110" t="n">
-        <v>196.63</v>
+        <v>687.74</v>
       </c>
       <c r="G110" t="n">
-        <v>218.15</v>
+        <v>769.98</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>10.53%</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3862,28 +3862,28 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories, Inc.</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>555.83</v>
+        <v>4265.46</v>
       </c>
       <c r="F111" t="n">
-        <v>694.75</v>
+        <v>960.78</v>
       </c>
       <c r="G111" t="n">
-        <v>769.98</v>
+        <v>1073.82</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>9.64%</t>
+          <t>10.45%</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3893,28 +3893,28 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4307.63</v>
+        <v>8187.75</v>
       </c>
       <c r="F112" t="n">
-        <v>970.28</v>
+        <v>300.77</v>
       </c>
       <c r="G112" t="n">
-        <v>1073.82</v>
+        <v>335.87</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9.55%</t>
+          <t>9.97%</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3924,28 +3924,28 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2746.81</v>
+        <v>3783.42</v>
       </c>
       <c r="F113" t="n">
-        <v>293.86</v>
+        <v>51.81</v>
       </c>
       <c r="G113" t="n">
-        <v>324.9</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9.35%</t>
+          <t>9.95%</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3955,28 +3955,28 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3809.71</v>
+        <v>2763.34</v>
       </c>
       <c r="F114" t="n">
-        <v>52.17</v>
+        <v>88.03</v>
       </c>
       <c r="G114" t="n">
-        <v>57.55</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>9.26%</t>
+          <t>9.74%</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3986,28 +3986,28 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2784.68</v>
+        <v>46629.38</v>
       </c>
       <c r="F115" t="n">
-        <v>88.70999999999999</v>
+        <v>191.52</v>
       </c>
       <c r="G115" t="n">
-        <v>97.76000000000001</v>
+        <v>212.18</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>9.71%</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4017,28 +4017,28 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1379.4</v>
+        <v>9177.92</v>
       </c>
       <c r="F116" t="n">
-        <v>232.55</v>
+        <v>1023.8</v>
       </c>
       <c r="G116" t="n">
-        <v>255.44</v>
+        <v>1133.95</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8.84%</t>
+          <t>9.46%</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4048,28 +4048,28 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>BlackRock, Inc.</t>
+          <t>International Business Machines Corporation</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1717.04</v>
+        <v>2749.62</v>
       </c>
       <c r="F117" t="n">
-        <v>1106.69</v>
+        <v>294.16</v>
       </c>
       <c r="G117" t="n">
-        <v>1214.03</v>
+        <v>324.9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.31%</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4079,28 +4079,28 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Toyota Motor Corporation</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2934.83</v>
+        <v>3864.74</v>
       </c>
       <c r="F118" t="n">
-        <v>224.12</v>
+        <v>218.67</v>
       </c>
       <c r="G118" t="n">
-        <v>245.75</v>
+        <v>241.12</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8.79%</t>
+          <t>8.97%</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4110,28 +4110,28 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals Incorporated</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1215.73</v>
+        <v>1890.82</v>
       </c>
       <c r="F119" t="n">
-        <v>474.17</v>
+        <v>150.15</v>
       </c>
       <c r="G119" t="n">
-        <v>519.88</v>
+        <v>164.94</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8.71%</t>
+          <t>8.55%</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4141,28 +4141,28 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc.</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1607.92</v>
+        <v>2284.38</v>
       </c>
       <c r="F120" t="n">
-        <v>526.67</v>
+        <v>608.02</v>
       </c>
       <c r="G120" t="n">
-        <v>576.91</v>
+        <v>664.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.46%</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Coca-Cola Europacific Partners PLC</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>414.17</v>
+        <v>1612.35</v>
       </c>
       <c r="F121" t="n">
-        <v>90.77</v>
+        <v>528.12</v>
       </c>
       <c r="G121" t="n">
-        <v>99.09999999999999</v>
+        <v>576.91</v>
       </c>
     </row>
     <row r="122">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4203,28 +4203,28 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>9318.76</v>
+        <v>1451.64</v>
       </c>
       <c r="F122" t="n">
-        <v>1039.51</v>
+        <v>66.53</v>
       </c>
       <c r="G122" t="n">
-        <v>1133.95</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7.45%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4234,28 +4234,28 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>O'Reilly Automotive, Inc.</t>
+          <t>Take-Two Interactive Software, Inc.</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>851.28</v>
+        <v>449.35</v>
       </c>
       <c r="F123" t="n">
-        <v>100.62</v>
+        <v>243.18</v>
       </c>
       <c r="G123" t="n">
-        <v>108.72</v>
+        <v>264.79</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7.34%</t>
+          <t>8.14%</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4265,28 +4265,28 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Xcel Energy Inc.</t>
+          <t>Coca-Cola Europacific Partners PLC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>451.52</v>
+        <v>415.36</v>
       </c>
       <c r="F124" t="n">
-        <v>76.33</v>
+        <v>91.03</v>
       </c>
       <c r="G124" t="n">
-        <v>82.37</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7.28%</t>
+          <t>8.07%</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4296,28 +4296,28 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software, Inc.</t>
+          <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>453.67</v>
+        <v>1225.32</v>
       </c>
       <c r="F125" t="n">
-        <v>245.52</v>
+        <v>477.91</v>
       </c>
       <c r="G125" t="n">
-        <v>264.79</v>
+        <v>519.88</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>7.19%</t>
+          <t>7.73%</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4327,28 +4327,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>The TJX Companies, Inc.</t>
+          <t>Xcel Energy Inc.</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1647.26</v>
+        <v>449.63</v>
       </c>
       <c r="F126" t="n">
-        <v>148.01</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>159.48</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>7.13%</t>
+          <t>7.67%</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4358,28 +4358,28 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>American Express Company</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3957.7</v>
+        <v>2484.23</v>
       </c>
       <c r="F127" t="n">
-        <v>223.93</v>
+        <v>356.99</v>
       </c>
       <c r="G127" t="n">
-        <v>241.12</v>
+        <v>386.63</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7.03%</t>
+          <t>7.61%</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4389,28 +4389,28 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>American Express Company</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2501.35</v>
+        <v>1028.19</v>
       </c>
       <c r="F128" t="n">
-        <v>359.45</v>
+        <v>826.62</v>
       </c>
       <c r="G128" t="n">
-        <v>386.63</v>
+        <v>894.75</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>7.61%</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4420,28 +4420,28 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>BlackRock, Inc.</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1474.11</v>
+        <v>1740.28</v>
       </c>
       <c r="F129" t="n">
-        <v>67.56</v>
+        <v>1121.67</v>
       </c>
       <c r="G129" t="n">
-        <v>72.58</v>
+        <v>1214.03</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6.78%</t>
+          <t>7.33%</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4451,28 +4451,28 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Exelon Corporation</t>
+          <t>The TJX Companies, Inc.</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>452.78</v>
+        <v>1644.81</v>
       </c>
       <c r="F130" t="n">
-        <v>44.83</v>
+        <v>147.79</v>
       </c>
       <c r="G130" t="n">
-        <v>48.09</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6.77%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4482,28 +4482,28 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Exelon Corporation</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1037.59</v>
+        <v>452.07</v>
       </c>
       <c r="F131" t="n">
-        <v>834.1799999999999</v>
+        <v>44.76</v>
       </c>
       <c r="G131" t="n">
-        <v>894.75</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>6.22%</t>
+          <t>6.88%</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4513,28 +4513,28 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>HCA Healthcare, Inc.</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2124.3</v>
+        <v>1149.45</v>
       </c>
       <c r="F132" t="n">
-        <v>453.03</v>
+        <v>491.23</v>
       </c>
       <c r="G132" t="n">
-        <v>483.05</v>
+        <v>527.55</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4544,28 +4544,28 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2344.08</v>
+        <v>406.83</v>
       </c>
       <c r="F133" t="n">
-        <v>623.91</v>
+        <v>83.3</v>
       </c>
       <c r="G133" t="n">
-        <v>664.9</v>
+        <v>89.37</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5.64%</t>
+          <t>6.76%</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4575,28 +4575,28 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>O'Reilly Automotive, Inc.</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4103.15</v>
+        <v>857.62</v>
       </c>
       <c r="F134" t="n">
-        <v>252.03</v>
+        <v>101.37</v>
       </c>
       <c r="G134" t="n">
-        <v>267.08</v>
+        <v>108.72</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>6.53%</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4606,23 +4606,23 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc.</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2814.46</v>
+        <v>2117.13</v>
       </c>
       <c r="F135" t="n">
-        <v>929.72</v>
+        <v>451.5</v>
       </c>
       <c r="G135" t="n">
-        <v>984.7</v>
+        <v>483.05</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>6.03%</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>26156.82</v>
+        <v>25978.29</v>
       </c>
       <c r="F136" t="n">
-        <v>244.68</v>
+        <v>243.01</v>
       </c>
       <c r="G136" t="n">
         <v>258.6</v>
@@ -4653,12 +4653,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4668,28 +4668,28 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>Marriott International, Inc.</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>413.43</v>
+        <v>847.14</v>
       </c>
       <c r="F137" t="n">
-        <v>84.65000000000001</v>
+        <v>312.07</v>
       </c>
       <c r="G137" t="n">
-        <v>89.37</v>
+        <v>331.09</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4699,28 +4699,28 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2903.03</v>
+        <v>4114.71</v>
       </c>
       <c r="F138" t="n">
-        <v>182.66</v>
+        <v>252.74</v>
       </c>
       <c r="G138" t="n">
-        <v>192.68</v>
+        <v>267.08</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4730,28 +4730,28 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Marriott International, Inc.</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>852.24</v>
+        <v>2897.95</v>
       </c>
       <c r="F139" t="n">
-        <v>313.95</v>
+        <v>182.34</v>
       </c>
       <c r="G139" t="n">
-        <v>331.09</v>
+        <v>192.68</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>5.03%</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4761,28 +4761,28 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>Mitsubishi UFJ Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1885.7</v>
+        <v>2055.87</v>
       </c>
       <c r="F140" t="n">
-        <v>692.7</v>
+        <v>17.95</v>
       </c>
       <c r="G140" t="n">
-        <v>730.46</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ENB</t>
+          <t>BN</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4792,28 +4792,28 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Enbridge Inc.</t>
+          <t>Brookfield Corporation</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1048.28</v>
+        <v>1058.23</v>
       </c>
       <c r="F141" t="n">
-        <v>48.02</v>
+        <v>47.09</v>
       </c>
       <c r="G141" t="n">
-        <v>50.54</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.86%</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4823,28 +4823,28 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1201.93</v>
+        <v>2835.92</v>
       </c>
       <c r="F142" t="n">
-        <v>301.47</v>
+        <v>936.8099999999999</v>
       </c>
       <c r="G142" t="n">
-        <v>316.94</v>
+        <v>984.7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.78%</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4854,28 +4854,28 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Ross Stores, Inc.</t>
+          <t>Altria Group, Inc.</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>604.92</v>
+        <v>1060.52</v>
       </c>
       <c r="F143" t="n">
-        <v>186</v>
+        <v>63.13</v>
       </c>
       <c r="G143" t="n">
-        <v>194.92</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4885,28 +4885,28 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Strive Asset Management, LLC</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>5523.03</v>
       </c>
       <c r="F144" t="n">
-        <v>96.89</v>
+        <v>1422.92</v>
       </c>
       <c r="G144" t="n">
-        <v>101.35</v>
+        <v>1493.47</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Brookfield Corporation</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1065.65</v>
+        <v>2340.34</v>
       </c>
       <c r="F145" t="n">
-        <v>47.42</v>
+        <v>166.58</v>
       </c>
       <c r="G145" t="n">
-        <v>49.57</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.56%</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4947,28 +4947,28 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>American Electric Power Company, Inc.</t>
+          <t>Ross Stores, Inc.</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>639.27</v>
+        <v>605.05</v>
       </c>
       <c r="F146" t="n">
-        <v>119.43</v>
+        <v>186.04</v>
       </c>
       <c r="G146" t="n">
-        <v>124.8</v>
+        <v>194.92</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4978,28 +4978,28 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>HCA Healthcare, Inc.</t>
+          <t>American Electric Power Company, Inc.</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1183.63</v>
+        <v>637.61</v>
       </c>
       <c r="F147" t="n">
-        <v>505.84</v>
+        <v>119.12</v>
       </c>
       <c r="G147" t="n">
-        <v>527.55</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>4.24%</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5009,28 +5009,28 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Altria Group, Inc.</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1068.75</v>
+        <v>1511.32</v>
       </c>
       <c r="F148" t="n">
-        <v>63.62</v>
+        <v>269.42</v>
       </c>
       <c r="G148" t="n">
-        <v>66.3</v>
+        <v>281.36</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5040,23 +5040,23 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mitsubishi UFJ Financial Group, Inc.</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2078.78</v>
+        <v>1210.62</v>
       </c>
       <c r="F149" t="n">
-        <v>18.15</v>
+        <v>303.65</v>
       </c>
       <c r="G149" t="n">
-        <v>18.9</v>
+        <v>316.94</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>9323.450000000001</v>
+        <v>9293.950000000001</v>
       </c>
       <c r="F150" t="n">
-        <v>116.94</v>
+        <v>116.57</v>
       </c>
       <c r="G150" t="n">
         <v>121.62</v>
@@ -5087,12 +5087,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5102,28 +5102,28 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>17548.02</v>
+        <v>696.87</v>
       </c>
       <c r="F151" t="n">
-        <v>338.34</v>
+        <v>37.38</v>
       </c>
       <c r="G151" t="n">
-        <v>351.33</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TBB</t>
+          <t>SATA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5133,28 +5133,28 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
+          <t>Strive Asset Management, LLC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1386.36</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>22.58</v>
+        <v>97.27</v>
       </c>
       <c r="G152" t="n">
-        <v>23.41</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5164,28 +5164,28 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Parker-Hannifin Corporation</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2372.1</v>
+        <v>1159.49</v>
       </c>
       <c r="F153" t="n">
-        <v>168.84</v>
+        <v>916.27</v>
       </c>
       <c r="G153" t="n">
-        <v>174.61</v>
+        <v>954.3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>ENB</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5195,28 +5195,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Enbridge Inc.</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>702.27</v>
+        <v>1060.06</v>
       </c>
       <c r="F154" t="n">
-        <v>37.67</v>
+        <v>48.56</v>
       </c>
       <c r="G154" t="n">
-        <v>38.95</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.84%</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5226,59 +5226,59 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Agnico Eagle Mines Limited</t>
+          <t>Honeywell International Inc.</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1085.22</v>
+        <v>1459.87</v>
       </c>
       <c r="F155" t="n">
-        <v>216.16</v>
+        <v>216.64</v>
       </c>
       <c r="G155" t="n">
-        <v>223.44</v>
+        <v>225.29</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings plc</t>
+          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>809.96</v>
+        <v>1429.02</v>
       </c>
       <c r="F156" t="n">
-        <v>371.76</v>
+        <v>25.14</v>
       </c>
       <c r="G156" t="n">
-        <v>383.88</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>TBB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5288,28 +5288,28 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1487.72</v>
+        <v>1382.68</v>
       </c>
       <c r="F157" t="n">
-        <v>303.83</v>
+        <v>22.52</v>
       </c>
       <c r="G157" t="n">
-        <v>313.54</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.41%</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5319,28 +5319,28 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>PACCAR Inc</t>
+          <t>AstraZeneca PLC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>634.5</v>
+        <v>2890.35</v>
       </c>
       <c r="F158" t="n">
-        <v>120.81</v>
+        <v>93.22</v>
       </c>
       <c r="G158" t="n">
-        <v>124.53</v>
+        <v>96.51000000000001</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5350,28 +5350,28 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Parker-Hannifin Corporation</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1171.76</v>
+        <v>1842.79</v>
       </c>
       <c r="F159" t="n">
-        <v>925.97</v>
+        <v>342.22</v>
       </c>
       <c r="G159" t="n">
-        <v>954.3</v>
+        <v>353.25</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CCZ</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5381,28 +5381,28 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Comcast Holdings Corp.</t>
+          <t>Novartis AG</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>615.7</v>
+        <v>2837.32</v>
       </c>
       <c r="F160" t="n">
-        <v>65</v>
+        <v>147.87</v>
       </c>
       <c r="G160" t="n">
-        <v>66.90000000000001</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5412,28 +5412,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1536.67</v>
+        <v>1576.95</v>
       </c>
       <c r="F161" t="n">
-        <v>273.94</v>
+        <v>93.62</v>
       </c>
       <c r="G161" t="n">
-        <v>281.36</v>
+        <v>96.44</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5443,28 +5443,28 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2993.16</v>
+        <v>2674.3</v>
       </c>
       <c r="F162" t="n">
-        <v>638.91</v>
+        <v>199.46</v>
       </c>
       <c r="G162" t="n">
-        <v>655.78</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CCZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5474,28 +5474,28 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Comcast Holdings Corp.</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1407.39</v>
+        <v>615.7</v>
       </c>
       <c r="F163" t="n">
-        <v>519.1900000000001</v>
+        <v>65</v>
       </c>
       <c r="G163" t="n">
-        <v>532.61</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5505,59 +5505,59 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>McDonald's Corporation</t>
+          <t>UBS Group AG</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2241.65</v>
+        <v>1511.32</v>
       </c>
       <c r="F164" t="n">
-        <v>314.13</v>
+        <v>47.96</v>
       </c>
       <c r="G164" t="n">
-        <v>321.79</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>Banco Santander, S.A.</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>524.8200000000001</v>
+        <v>1875.06</v>
       </c>
       <c r="F165" t="n">
-        <v>1095.49</v>
+        <v>12.68</v>
       </c>
       <c r="G165" t="n">
-        <v>1121.48</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5567,28 +5567,28 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>McDonald's Corporation</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>795.39</v>
+        <v>2232.15</v>
       </c>
       <c r="F166" t="n">
-        <v>81.41</v>
+        <v>312.8</v>
       </c>
       <c r="G166" t="n">
-        <v>83.23999999999999</v>
+        <v>321.79</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5598,28 +5598,28 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc.</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3108.72</v>
+        <v>790.61</v>
       </c>
       <c r="F167" t="n">
-        <v>78.68000000000001</v>
+        <v>80.92</v>
       </c>
       <c r="G167" t="n">
-        <v>80.39</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5629,28 +5629,28 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NextEra Energy, Inc.</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1814.99</v>
+        <v>1012.54</v>
       </c>
       <c r="F168" t="n">
-        <v>87.15000000000001</v>
+        <v>50.1</v>
       </c>
       <c r="G168" t="n">
-        <v>88.95999999999999</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5660,28 +5660,28 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1882.75</v>
+        <v>1937.12</v>
       </c>
       <c r="F169" t="n">
-        <v>103.72</v>
+        <v>711.59</v>
       </c>
       <c r="G169" t="n">
-        <v>105.81</v>
+        <v>730.46</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5691,28 +5691,28 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Honeywell International Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1488.65</v>
+        <v>17753.4</v>
       </c>
       <c r="F170" t="n">
-        <v>220.91</v>
+        <v>342.3</v>
       </c>
       <c r="G170" t="n">
-        <v>225.29</v>
+        <v>351.33</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5722,59 +5722,59 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Carvana Co.</t>
+          <t>The Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1035.71</v>
+        <v>1878.21</v>
       </c>
       <c r="F171" t="n">
-        <v>477.72</v>
+        <v>103.47</v>
       </c>
       <c r="G171" t="n">
-        <v>486.89</v>
+        <v>105.81</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>FER</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Baker Hughes Company</t>
+          <t>Ferrovial SE</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>557.53</v>
+        <v>488.26</v>
       </c>
       <c r="F172" t="n">
-        <v>56.5</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="G172" t="n">
-        <v>57.58</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5784,28 +5784,28 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>40440.64</v>
+        <v>2682.69</v>
       </c>
       <c r="F173" t="n">
-        <v>335</v>
+        <v>336.75</v>
       </c>
       <c r="G173" t="n">
-        <v>341.2</v>
+        <v>344.04</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5815,28 +5815,28 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>40521.1</v>
+        <v>3013.63</v>
       </c>
       <c r="F174" t="n">
-        <v>334.55</v>
+        <v>643.28</v>
       </c>
       <c r="G174" t="n">
-        <v>340.49</v>
+        <v>655.78</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5846,28 +5846,28 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>PACCAR Inc</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1395.03</v>
+        <v>646.3200000000001</v>
       </c>
       <c r="F175" t="n">
-        <v>127</v>
+        <v>123.06</v>
       </c>
       <c r="G175" t="n">
-        <v>129.25</v>
+        <v>125.36</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5877,28 +5877,28 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Shell plc</t>
+          <t>Philip Morris International Inc.</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2136.62</v>
+        <v>2780</v>
       </c>
       <c r="F176" t="n">
-        <v>75.45</v>
+        <v>178.59</v>
       </c>
       <c r="G176" t="n">
-        <v>76.73999999999999</v>
+        <v>181.91</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5908,59 +5908,59 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc.</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2784.52</v>
+        <v>3021.18</v>
       </c>
       <c r="F177" t="n">
-        <v>178.88</v>
+        <v>239.58</v>
       </c>
       <c r="G177" t="n">
-        <v>181.91</v>
+        <v>243.99</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>Cisco Systems, Inc.</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>866.11</v>
+        <v>3119.78</v>
       </c>
       <c r="F178" t="n">
-        <v>252.66</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="G178" t="n">
-        <v>256.5</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5970,28 +5970,28 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>HSBC Holdings plc</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4617.29</v>
+        <v>2986.87</v>
       </c>
       <c r="F179" t="n">
-        <v>410.24</v>
+        <v>87</v>
       </c>
       <c r="G179" t="n">
-        <v>416.45</v>
+        <v>88.54000000000001</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6001,28 +6001,28 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Baker Hughes Company</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5645.96</v>
+        <v>558.8099999999999</v>
       </c>
       <c r="F180" t="n">
-        <v>1454.59</v>
+        <v>56.63</v>
       </c>
       <c r="G180" t="n">
-        <v>1473.59</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>SCCO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6032,28 +6032,28 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>GSK plc</t>
+          <t>Southern Copper Corporation</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1026.69</v>
+        <v>1623.28</v>
       </c>
       <c r="F181" t="n">
-        <v>50.8</v>
+        <v>198.18</v>
       </c>
       <c r="G181" t="n">
-        <v>51.46</v>
+        <v>201.44</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6063,90 +6063,90 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>NextEra Energy, Inc.</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2650.51</v>
+        <v>1823.74</v>
       </c>
       <c r="F182" t="n">
-        <v>332.71</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="G182" t="n">
-        <v>336.4</v>
+        <v>88.95999999999999</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>AstraZeneca PLC</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2964.14</v>
+        <v>958.8</v>
       </c>
       <c r="F183" t="n">
-        <v>95.59999999999999</v>
+        <v>279.7</v>
       </c>
       <c r="G183" t="n">
-        <v>96.51000000000001</v>
+        <v>284</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Seagate Technology Holdings plc</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2698.71</v>
+        <v>965.02</v>
       </c>
       <c r="F184" t="n">
-        <v>201.28</v>
+        <v>442.93</v>
       </c>
       <c r="G184" t="n">
-        <v>203.03</v>
+        <v>449.5</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6156,28 +6156,28 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>CME Group Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1022.74</v>
+        <v>40595.16</v>
       </c>
       <c r="F185" t="n">
-        <v>284.48</v>
+        <v>336.28</v>
       </c>
       <c r="G185" t="n">
-        <v>286.76</v>
+        <v>341.2</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6187,23 +6187,23 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1891.79</v>
+        <v>1423.17</v>
       </c>
       <c r="F186" t="n">
-        <v>351.32</v>
+        <v>525.01</v>
       </c>
       <c r="G186" t="n">
-        <v>353.25</v>
+        <v>532.61</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1749.17</v>
+        <v>1733.66</v>
       </c>
       <c r="F187" t="n">
-        <v>140.97</v>
+        <v>139.72</v>
       </c>
       <c r="G187" t="n">
         <v>141.71</v>
@@ -6234,12 +6234,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6249,28 +6249,28 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2034.99</v>
+        <v>2142.77</v>
       </c>
       <c r="F188" t="n">
-        <v>166.25</v>
+        <v>1627.2</v>
       </c>
       <c r="G188" t="n">
-        <v>167.04</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6280,28 +6280,28 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5407.42</v>
+        <v>40697.94</v>
       </c>
       <c r="F189" t="n">
-        <v>224.44</v>
+        <v>336.01</v>
       </c>
       <c r="G189" t="n">
-        <v>225.5</v>
+        <v>340.49</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6311,28 +6311,28 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Shell plc</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>3007.06</v>
+        <v>2145.32</v>
       </c>
       <c r="F190" t="n">
-        <v>238.46</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="G190" t="n">
-        <v>239.5</v>
+        <v>76.73999999999999</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6342,28 +6342,28 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1389</v>
+        <v>1532.32</v>
       </c>
       <c r="F191" t="n">
-        <v>594.95</v>
+        <v>71.52</v>
       </c>
       <c r="G191" t="n">
-        <v>597.48</v>
+        <v>72.37</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6373,59 +6373,59 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1618.22</v>
+        <v>1965.28</v>
       </c>
       <c r="F192" t="n">
-        <v>96.06999999999999</v>
+        <v>216.17</v>
       </c>
       <c r="G192" t="n">
-        <v>96.44</v>
+        <v>218.15</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Electronic Arts Inc.</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>511.14</v>
+        <v>556.5700000000001</v>
       </c>
       <c r="F193" t="n">
-        <v>204.37</v>
+        <v>1161.78</v>
       </c>
       <c r="G193" t="n">
-        <v>204.89</v>
+        <v>1171.57</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6435,28 +6435,28 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>UBS Group AG</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1551.97</v>
+        <v>4899.12</v>
       </c>
       <c r="F194" t="n">
-        <v>49.25</v>
+        <v>435.28</v>
       </c>
       <c r="G194" t="n">
-        <v>49.36</v>
+        <v>438.94</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6466,28 +6466,28 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Itaú Unibanco Holding S.A.</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>3406.06</v>
+        <v>979.16</v>
       </c>
       <c r="F195" t="n">
-        <v>169.05</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G195" t="n">
-        <v>169.37</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6497,28 +6497,28 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Novartis AG</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2920.79</v>
+        <v>3144.26</v>
       </c>
       <c r="F196" t="n">
-        <v>152.22</v>
+        <v>73.06</v>
       </c>
       <c r="G196" t="n">
-        <v>152.48</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6528,28 +6528,28 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Agnico Eagle Mines Limited</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2128.46</v>
+        <v>1119.51</v>
       </c>
       <c r="F197" t="n">
-        <v>1616.33</v>
+        <v>222.99</v>
       </c>
       <c r="G197" t="n">
-        <v>1618.19</v>
+        <v>224.3</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6559,28 +6559,28 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
+          <t>Electronic Arts Inc.</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1484.15</v>
+        <v>510.07</v>
       </c>
       <c r="F198" t="n">
-        <v>26.11</v>
+        <v>203.94</v>
       </c>
       <c r="G198" t="n">
-        <v>26.14</v>
+        <v>204.89</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6590,28 +6590,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corporation</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5833.4</v>
+        <v>5486.45</v>
       </c>
       <c r="F199" t="n">
-        <v>136.83</v>
+        <v>227.72</v>
       </c>
       <c r="G199" t="n">
-        <v>136.94</v>
+        <v>228.57</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SCCO</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6621,59 +6621,59 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Southern Copper Corporation</t>
+          <t>British American Tobacco p.l.c.</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1595.93</v>
+        <v>1305.64</v>
       </c>
       <c r="F200" t="n">
-        <v>194.84</v>
+        <v>60.16</v>
       </c>
       <c r="G200" t="n">
-        <v>194.98</v>
+        <v>60.38</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>FER</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Ferrovial SE</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>498.49</v>
+        <v>1394.42</v>
       </c>
       <c r="F201" t="n">
-        <v>69.72</v>
+        <v>597.27</v>
       </c>
       <c r="G201" t="n">
-        <v>69.77</v>
+        <v>599.3200000000001</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6683,28 +6683,28 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1810.79</v>
+        <v>1449.4</v>
       </c>
       <c r="F202" t="n">
-        <v>70.48999999999999</v>
+        <v>131.95</v>
       </c>
       <c r="G202" t="n">
-        <v>70.54000000000001</v>
+        <v>132.4</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6714,28 +6714,28 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Exxon Mobil Corporation</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1538.11</v>
+        <v>5865.38</v>
       </c>
       <c r="F203" t="n">
-        <v>71.79000000000001</v>
+        <v>137.58</v>
       </c>
       <c r="G203" t="n">
-        <v>71.84</v>
+        <v>138</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6745,28 +6745,28 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>British American Tobacco p.l.c.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1309.69</v>
+        <v>3423.79</v>
       </c>
       <c r="F204" t="n">
-        <v>60.34</v>
+        <v>169.93</v>
       </c>
       <c r="G204" t="n">
-        <v>60.38</v>
+        <v>170.42</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6776,28 +6776,28 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc</t>
+          <t>CME Group Inc.</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>3038.03</v>
+        <v>1028.39</v>
       </c>
       <c r="F205" t="n">
-        <v>88.48999999999999</v>
+        <v>286.05</v>
       </c>
       <c r="G205" t="n">
-        <v>88.54000000000001</v>
+        <v>286.76</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6807,28 +6807,28 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Rio Tinto Group</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1854.33</v>
+        <v>1555.26</v>
       </c>
       <c r="F206" t="n">
-        <v>92.91</v>
+        <v>317.62</v>
       </c>
       <c r="G206" t="n">
-        <v>92.94</v>
+        <v>318.17</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6838,28 +6838,28 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Rio Tinto Group</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>3165.35</v>
+        <v>1863.52</v>
       </c>
       <c r="F207" t="n">
-        <v>73.55</v>
+        <v>93.37</v>
       </c>
       <c r="G207" t="n">
-        <v>73.56</v>
+        <v>93.45</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6869,17 +6869,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Banco Santander, S.A.</t>
+          <t>BHP Group Limited</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1929.77</v>
+        <v>1822.86</v>
       </c>
       <c r="F208" t="n">
-        <v>13.05</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="G208" t="n">
-        <v>13.05</v>
+        <v>70.98</v>
       </c>
     </row>
   </sheetData>

--- a/美股回撤分析报告.xlsx
+++ b/美股回撤分析报告.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>82.52%</t>
+          <t>82.84%</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>516.67</v>
+        <v>507.4</v>
       </c>
       <c r="F2" t="n">
-        <v>54.08</v>
+        <v>53.11</v>
       </c>
       <c r="G2" t="n">
         <v>309.44</v>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>77.86%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>249.7</v>
+        <v>261.6</v>
       </c>
       <c r="F3" t="n">
-        <v>182.81</v>
+        <v>191.52</v>
       </c>
       <c r="G3" t="n">
         <v>825.62</v>
@@ -530,7 +530,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>72.11%</t>
+          <t>75.08%</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>354.73</v>
+        <v>316.88</v>
       </c>
       <c r="F4" t="n">
-        <v>134.76</v>
+        <v>120.38</v>
       </c>
       <c r="G4" t="n">
         <v>483.13</v>
@@ -561,7 +561,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>70.82%</t>
+          <t>73.63%</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>458.47</v>
+        <v>414.31</v>
       </c>
       <c r="F5" t="n">
-        <v>158.45</v>
+        <v>143.19</v>
       </c>
       <c r="G5" t="n">
         <v>543</v>
@@ -592,7 +592,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>70.14%</t>
+          <t>69.88%</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2043.34</v>
+        <v>2061.23</v>
       </c>
       <c r="F6" t="n">
-        <v>114.2</v>
+        <v>115.2</v>
       </c>
       <c r="G6" t="n">
         <v>382.43</v>
@@ -623,12 +623,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>64.23%</t>
+          <t>64.68%</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -638,28 +638,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Kraft Heinz Company</t>
+          <t>Warner Bros. Discovery, Inc.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>274.49</v>
+        <v>684.34</v>
       </c>
       <c r="F7" t="n">
-        <v>23.19</v>
+        <v>27.6</v>
       </c>
       <c r="G7" t="n">
-        <v>64.84</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>64.19%</t>
+          <t>64.31%</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -669,23 +669,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery, Inc.</t>
+          <t>The Kraft Heinz Company</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>693.76</v>
+        <v>273.9</v>
       </c>
       <c r="F8" t="n">
-        <v>27.98</v>
+        <v>23.14</v>
       </c>
       <c r="G8" t="n">
-        <v>78.14</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.69%</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2680.75</v>
+        <v>2636.32</v>
       </c>
       <c r="F9" t="n">
-        <v>60.33</v>
+        <v>59.33</v>
       </c>
       <c r="G9" t="n">
         <v>143.64</v>
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>57.17%</t>
+          <t>58.31%</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1254.04</v>
+        <v>1220.85</v>
       </c>
       <c r="F10" t="n">
-        <v>299.58</v>
+        <v>291.65</v>
       </c>
       <c r="G10" t="n">
         <v>699.54</v>
@@ -747,7 +747,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.11%</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>287.69</v>
+        <v>290.19</v>
       </c>
       <c r="F11" t="n">
-        <v>73.36</v>
+        <v>74</v>
       </c>
       <c r="G11" t="n">
         <v>164.86</v>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>52.05%</t>
+          <t>52.34%</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2663.35</v>
+        <v>2647.68</v>
       </c>
       <c r="F12" t="n">
-        <v>294.02</v>
+        <v>292.29</v>
       </c>
       <c r="G12" t="n">
         <v>613.22</v>
@@ -809,7 +809,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51.64%</t>
+          <t>51.69%</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1459.54</v>
+        <v>1457.98</v>
       </c>
       <c r="F13" t="n">
-        <v>102.81</v>
+        <v>102.7</v>
       </c>
       <c r="G13" t="n">
         <v>212.6</v>
@@ -840,12 +840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>51.28%</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -855,28 +855,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4964.77</v>
+        <v>1231.67</v>
       </c>
       <c r="F14" t="n">
-        <v>172.8</v>
+        <v>116.73</v>
       </c>
       <c r="G14" t="n">
-        <v>344.21</v>
+        <v>239.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>47.67%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -886,28 +886,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1470.32</v>
+        <v>4855.88</v>
       </c>
       <c r="F15" t="n">
-        <v>25.86</v>
+        <v>169.01</v>
       </c>
       <c r="G15" t="n">
-        <v>49.42</v>
+        <v>344.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>45.91%</t>
+          <t>47.97%</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -917,28 +917,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1367.68</v>
+        <v>509.71</v>
       </c>
       <c r="F16" t="n">
-        <v>129.62</v>
+        <v>112.76</v>
       </c>
       <c r="G16" t="n">
-        <v>239.62</v>
+        <v>216.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>45.89%</t>
+          <t>47.19%</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -948,28 +948,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>530.14</v>
+        <v>1483.97</v>
       </c>
       <c r="F17" t="n">
-        <v>117.28</v>
+        <v>26.1</v>
       </c>
       <c r="G17" t="n">
-        <v>216.72</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>44.76%</t>
+          <t>46.66%</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -979,23 +979,23 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Zscaler, Inc.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1955.96</v>
+        <v>319.95</v>
       </c>
       <c r="F18" t="n">
-        <v>109.56</v>
+        <v>200.63</v>
       </c>
       <c r="G18" t="n">
-        <v>198.35</v>
+        <v>376.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>44.53%</t>
+          <t>46.27%</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1891.82</v>
+        <v>1832.7</v>
       </c>
       <c r="F19" t="n">
-        <v>241.59</v>
+        <v>234.04</v>
       </c>
       <c r="G19" t="n">
         <v>435.56</v>
@@ -1026,12 +1026,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.89%</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1041,28 +1041,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Comcast Corporation</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1119.68</v>
+        <v>466.34</v>
       </c>
       <c r="F20" t="n">
-        <v>28.41</v>
+        <v>174.66</v>
       </c>
       <c r="G20" t="n">
-        <v>50.46</v>
+        <v>311.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>43.12%</t>
+          <t>43.75%</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1072,28 +1072,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Zscaler, Inc.</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>341.19</v>
+        <v>1992.03</v>
       </c>
       <c r="F21" t="n">
-        <v>213.95</v>
+        <v>111.58</v>
       </c>
       <c r="G21" t="n">
-        <v>376.11</v>
+        <v>198.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42.08%</t>
+          <t>42.55%</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1103,28 +1103,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Limited</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4193.57</v>
+        <v>1150.44</v>
       </c>
       <c r="F22" t="n">
-        <v>175.66</v>
+        <v>108.43</v>
       </c>
       <c r="G22" t="n">
-        <v>303.26</v>
+        <v>188.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>41.74%</t>
+          <t>42.54%</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1134,59 +1134,59 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Alibaba Group Holding Limited</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1166.67</v>
+        <v>4159.91</v>
       </c>
       <c r="F23" t="n">
-        <v>109.96</v>
+        <v>174.25</v>
       </c>
       <c r="G23" t="n">
-        <v>188.75</v>
+        <v>303.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>40.19%</t>
+          <t>42.48%</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Airbnb, Inc.</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>805.4</v>
+        <v>404.8</v>
       </c>
       <c r="F24" t="n">
-        <v>131.55</v>
+        <v>509.58</v>
       </c>
       <c r="G24" t="n">
-        <v>219.94</v>
+        <v>885.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>39.24%</t>
+          <t>42.05%</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1196,28 +1196,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Comcast Corporation</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>504.95</v>
+        <v>1152.4</v>
       </c>
       <c r="F25" t="n">
-        <v>189.12</v>
+        <v>29.24</v>
       </c>
       <c r="G25" t="n">
-        <v>311.28</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>39.05%</t>
+          <t>41.54%</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1227,28 +1227,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Roper Technologies, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>387.89</v>
+        <v>2038.04</v>
       </c>
       <c r="F26" t="n">
-        <v>360.37</v>
+        <v>214.08</v>
       </c>
       <c r="G26" t="n">
-        <v>591.26</v>
+        <v>366.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>40.09%</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1258,28 +1258,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mizuho Financial Group, Inc.</t>
+          <t>Airbnb, Inc.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1067.87</v>
+        <v>806.74</v>
       </c>
       <c r="F27" t="n">
-        <v>8.630000000000001</v>
+        <v>131.77</v>
       </c>
       <c r="G27" t="n">
-        <v>14.08</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38.29%</t>
+          <t>38.71%</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1289,59 +1289,59 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Anheuser-Busch InBev SA/NV</t>
+          <t>CoStar Group, Inc.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1358.67</v>
+        <v>262.47</v>
       </c>
       <c r="F28" t="n">
-        <v>69.81999999999999</v>
+        <v>61.93</v>
       </c>
       <c r="G28" t="n">
-        <v>113.15</v>
+        <v>101.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>37.93%</t>
+          <t>38.63%</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>Mizuho Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>436.79</v>
+        <v>1069.1</v>
       </c>
       <c r="F29" t="n">
-        <v>549.86</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>885.92</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>37.75%</t>
+          <t>38.27%</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1351,28 +1351,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Roper Technologies, Inc.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2170.18</v>
+        <v>392.88</v>
       </c>
       <c r="F30" t="n">
-        <v>227.96</v>
+        <v>365</v>
       </c>
       <c r="G30" t="n">
-        <v>366.19</v>
+        <v>591.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>37.64%</t>
+          <t>37.99%</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>796.1</v>
+        <v>3527.56</v>
       </c>
       <c r="F31" t="n">
-        <v>751.13</v>
+        <v>83.16</v>
       </c>
       <c r="G31" t="n">
-        <v>1204.52</v>
+        <v>134.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>36.91%</t>
+          <t>37.96%</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1413,28 +1413,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Copart, Inc.</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>393.21</v>
+        <v>1400.3</v>
       </c>
       <c r="F32" t="n">
-        <v>40.62</v>
+        <v>502.98</v>
       </c>
       <c r="G32" t="n">
-        <v>64.38</v>
+        <v>810.72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>36.89%</t>
+          <t>37.78%</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1444,28 +1444,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3590.34</v>
+        <v>794.3099999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>84.64</v>
+        <v>749.4400000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>134.12</v>
+        <v>1204.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35.48%</t>
+          <t>37.43%</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1475,28 +1475,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CoStar Group, Inc.</t>
+          <t>Copart, Inc.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>276.33</v>
+        <v>389.92</v>
       </c>
       <c r="F34" t="n">
-        <v>65.2</v>
+        <v>40.28</v>
       </c>
       <c r="G34" t="n">
-        <v>101.05</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35.36%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1506,28 +1506,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Anheuser-Busch InBev SA/NV</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>367.76</v>
+        <v>1385.73</v>
       </c>
       <c r="F35" t="n">
-        <v>102.45</v>
+        <v>71.28</v>
       </c>
       <c r="G35" t="n">
-        <v>158.49</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.45%</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1537,28 +1537,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Spotify Technology S.A.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1047.38</v>
+        <v>449.49</v>
       </c>
       <c r="F36" t="n">
-        <v>508.7</v>
+        <v>128.18</v>
       </c>
       <c r="G36" t="n">
-        <v>785</v>
+        <v>201.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>34.19%</t>
+          <t>36.09%</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1568,28 +1568,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>720.89</v>
+        <v>2336.04</v>
       </c>
       <c r="F37" t="n">
-        <v>83.62</v>
+        <v>200.21</v>
       </c>
       <c r="G37" t="n">
-        <v>127.06</v>
+        <v>313.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>33.55%</t>
+          <t>35.98%</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1599,28 +1599,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1499.74</v>
+        <v>701.23</v>
       </c>
       <c r="F38" t="n">
-        <v>538.7</v>
+        <v>81.34</v>
       </c>
       <c r="G38" t="n">
-        <v>810.72</v>
+        <v>127.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>31.82%</t>
+          <t>35.81%</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1630,28 +1630,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Spotify Technology S.A.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>306.02</v>
+        <v>1037.54</v>
       </c>
       <c r="F39" t="n">
-        <v>219.03</v>
+        <v>503.92</v>
       </c>
       <c r="G39" t="n">
-        <v>321.24</v>
+        <v>785</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>31.81%</t>
+          <t>34.83%</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1661,28 +1661,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>T-Mobile US, Inc.</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2096.09</v>
+        <v>366.97</v>
       </c>
       <c r="F40" t="n">
-        <v>186.25</v>
+        <v>102.23</v>
       </c>
       <c r="G40" t="n">
-        <v>273.15</v>
+        <v>156.86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>33.77%</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1692,28 +1692,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>QUALCOMM Incorporated</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1635.42</v>
+        <v>1619.93</v>
       </c>
       <c r="F41" t="n">
-        <v>152.7</v>
+        <v>261.22</v>
       </c>
       <c r="G41" t="n">
-        <v>223.25</v>
+        <v>394.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>31.43%</t>
+          <t>32.58%</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1723,23 +1723,23 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1677.04</v>
+        <v>302.61</v>
       </c>
       <c r="F42" t="n">
-        <v>270.43</v>
+        <v>216.59</v>
       </c>
       <c r="G42" t="n">
-        <v>394.41</v>
+        <v>321.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>31.08%</t>
+          <t>32.14%</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1081.2</v>
+        <v>1064.63</v>
       </c>
       <c r="F43" t="n">
-        <v>116.77</v>
+        <v>114.98</v>
       </c>
       <c r="G43" t="n">
         <v>169.44</v>
@@ -1770,12 +1770,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>30.31%</t>
+          <t>31.82%</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1785,28 +1785,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>QUALCOMM Incorporated</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>492.9</v>
+        <v>1630.28</v>
       </c>
       <c r="F44" t="n">
-        <v>140.56</v>
+        <v>152.22</v>
       </c>
       <c r="G44" t="n">
-        <v>201.69</v>
+        <v>223.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>30.15%</t>
+          <t>30.71%</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1816,85 +1816,85 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Constellation Energy Corporation</t>
+          <t>T-Mobile US, Inc.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1043.21</v>
+        <v>2130.19</v>
       </c>
       <c r="F45" t="n">
-        <v>287.95</v>
+        <v>189.28</v>
       </c>
       <c r="G45" t="n">
-        <v>412.23</v>
+        <v>273.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>29.46%</t>
+          <t>30.27%</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ALNY</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Alnylam Pharmaceuticals, Inc.</t>
+          <t>Constellation Energy Corporation</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>461.84</v>
+        <v>1041.4</v>
       </c>
       <c r="F46" t="n">
-        <v>349.58</v>
+        <v>287.45</v>
       </c>
       <c r="G46" t="n">
-        <v>495.55</v>
+        <v>412.23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28.94%</t>
+          <t>30.02%</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>ALNY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>Alnylam Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>362.88</v>
+        <v>458.16</v>
       </c>
       <c r="F47" t="n">
-        <v>26.71</v>
+        <v>346.79</v>
       </c>
       <c r="G47" t="n">
-        <v>37.59</v>
+        <v>495.55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28.51%</t>
+          <t>29.01%</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>628.95</v>
+        <v>624.58</v>
       </c>
       <c r="F48" t="n">
-        <v>82.08</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="G48" t="n">
         <v>114.82</v>
@@ -1925,12 +1925,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27.61%</t>
+          <t>28.65%</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1940,17 +1940,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>890.7</v>
+        <v>364.37</v>
       </c>
       <c r="F49" t="n">
-        <v>206.66</v>
+        <v>26.82</v>
       </c>
       <c r="G49" t="n">
-        <v>285.5</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="50">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1971,28 +1971,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AppLovin Corporation</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1834.53</v>
+        <v>895.1</v>
       </c>
       <c r="F50" t="n">
-        <v>542.36</v>
+        <v>207.68</v>
       </c>
       <c r="G50" t="n">
-        <v>745.61</v>
+        <v>285.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26.73%</t>
+          <t>26.82%</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2002,28 +2002,28 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Insmed Incorporated</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>332.47</v>
+        <v>3619.49</v>
       </c>
       <c r="F51" t="n">
-        <v>155.89</v>
+        <v>151.86</v>
       </c>
       <c r="G51" t="n">
-        <v>212.75</v>
+        <v>207.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26.57%</t>
+          <t>26.67%</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2033,28 +2033,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sony Group Corporation</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1338.41</v>
+        <v>1753.96</v>
       </c>
       <c r="F52" t="n">
-        <v>22.28</v>
+        <v>142.94</v>
       </c>
       <c r="G52" t="n">
-        <v>30.34</v>
+        <v>194.94</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25.33%</t>
+          <t>26.53%</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2064,28 +2064,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Old Dominion Freight Line, Inc.</t>
+          <t>Sony Group Corporation</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>363</v>
+        <v>1339.01</v>
       </c>
       <c r="F53" t="n">
-        <v>172.72</v>
+        <v>22.29</v>
       </c>
       <c r="G53" t="n">
-        <v>231.32</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>26.35%</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2095,90 +2095,90 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1801.2</v>
+        <v>918.33</v>
       </c>
       <c r="F54" t="n">
-        <v>146.79</v>
+        <v>480</v>
       </c>
       <c r="G54" t="n">
-        <v>194.94</v>
+        <v>651.73</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>24.63%</t>
+          <t>25.82%</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Insmed Incorporated</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2754.92</v>
+        <v>336.59</v>
       </c>
       <c r="F55" t="n">
-        <v>236.11</v>
+        <v>157.82</v>
       </c>
       <c r="G55" t="n">
-        <v>313.28</v>
+        <v>212.75</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>24.18%</t>
+          <t>25.76%</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3750.34</v>
+        <v>544.6</v>
       </c>
       <c r="F56" t="n">
-        <v>157.35</v>
+        <v>255.68</v>
       </c>
       <c r="G56" t="n">
-        <v>207.52</v>
+        <v>344.39</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>23.75%</t>
+          <t>25.39%</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2188,28 +2188,28 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Old Dominion Freight Line, Inc.</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1808.52</v>
+        <v>362.73</v>
       </c>
       <c r="F57" t="n">
-        <v>138.92</v>
+        <v>172.59</v>
       </c>
       <c r="G57" t="n">
-        <v>182.19</v>
+        <v>231.32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.32%</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2219,28 +2219,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>The Progressive Corporation</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1845.76</v>
+        <v>1220.82</v>
       </c>
       <c r="F58" t="n">
-        <v>106.05</v>
+        <v>208.26</v>
       </c>
       <c r="G58" t="n">
-        <v>138.63</v>
+        <v>275.18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22.74%</t>
+          <t>24.31%</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2250,28 +2250,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Automatic Data Processing, Inc.</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1015.52</v>
+        <v>1552.49</v>
       </c>
       <c r="F59" t="n">
-        <v>250.69</v>
+        <v>219.62</v>
       </c>
       <c r="G59" t="n">
-        <v>324.5</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>22.69%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2281,28 +2281,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>The Progressive Corporation</t>
+          <t>Automatic Data Processing, Inc.</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1247.08</v>
+        <v>994.8200000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>212.74</v>
+        <v>245.97</v>
       </c>
       <c r="G60" t="n">
-        <v>275.18</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>22.61%</t>
+          <t>23.65%</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2312,28 +2312,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>AppLovin Corporation</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1607.82</v>
+        <v>1925.45</v>
       </c>
       <c r="F61" t="n">
-        <v>224.54</v>
+        <v>569.24</v>
       </c>
       <c r="G61" t="n">
-        <v>290.14</v>
+        <v>745.61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.47%</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2343,28 +2343,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Company</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1111.93</v>
+        <v>1846.45</v>
       </c>
       <c r="F62" t="n">
-        <v>54.62</v>
+        <v>106.09</v>
       </c>
       <c r="G62" t="n">
-        <v>70.48</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22.09%</t>
+          <t>22.98%</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2374,28 +2374,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>Bristol-Myers Squibb Company</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>571.54</v>
+        <v>1105.01</v>
       </c>
       <c r="F63" t="n">
-        <v>268.33</v>
+        <v>54.28</v>
       </c>
       <c r="G63" t="n">
-        <v>344.39</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21.85%</t>
+          <t>21.88%</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2405,28 +2405,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Diamondback Energy, Inc.</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>463.96</v>
+        <v>2430.65</v>
       </c>
       <c r="F64" t="n">
-        <v>160.27</v>
+        <v>48.66</v>
       </c>
       <c r="G64" t="n">
-        <v>205.08</v>
+        <v>62.29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21.78%</t>
+          <t>21.68%</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2436,28 +2436,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1663.75</v>
+        <v>32222.78</v>
       </c>
       <c r="F65" t="n">
-        <v>79.78</v>
+        <v>433.5</v>
       </c>
       <c r="G65" t="n">
-        <v>101.99</v>
+        <v>553.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21.69%</t>
+          <t>21.57%</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2467,28 +2467,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2436.65</v>
+        <v>1120.88</v>
       </c>
       <c r="F66" t="n">
-        <v>48.78</v>
+        <v>444.62</v>
       </c>
       <c r="G66" t="n">
-        <v>62.29</v>
+        <v>566.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21.54%</t>
+          <t>21.39%</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2498,28 +2498,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>Mondelez International, Inc.</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>978.3099999999999</v>
+        <v>741.5599999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>511.35</v>
+        <v>57.31</v>
       </c>
       <c r="G67" t="n">
-        <v>651.73</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20.81%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2529,28 +2529,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mondelez International, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>746.99</v>
+        <v>1205.18</v>
       </c>
       <c r="F68" t="n">
-        <v>57.73</v>
+        <v>176.2</v>
       </c>
       <c r="G68" t="n">
-        <v>72.90000000000001</v>
+        <v>223.61</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20.79%</t>
+          <t>21.16%</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2560,28 +2560,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1266.3</v>
+        <v>1869.97</v>
       </c>
       <c r="F69" t="n">
-        <v>101.39</v>
+        <v>143.64</v>
       </c>
       <c r="G69" t="n">
-        <v>128.01</v>
+        <v>182.19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.48%</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2591,23 +2591,23 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>Diamondback Energy, Inc.</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1111.7</v>
+        <v>472.07</v>
       </c>
       <c r="F70" t="n">
-        <v>45.77</v>
+        <v>163.07</v>
       </c>
       <c r="G70" t="n">
-        <v>57.57</v>
+        <v>205.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>19.47%</t>
+          <t>20.08%</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>15799.82</v>
+        <v>15680.81</v>
       </c>
       <c r="F71" t="n">
-        <v>333.24</v>
+        <v>330.73</v>
       </c>
       <c r="G71" t="n">
         <v>413.82</v>
@@ -2638,12 +2638,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>18.71%</t>
+          <t>19.89%</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2653,28 +2653,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Financial Group, Inc.</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1344.83</v>
+        <v>1703.79</v>
       </c>
       <c r="F72" t="n">
-        <v>20.95</v>
+        <v>81.7</v>
       </c>
       <c r="G72" t="n">
-        <v>25.77</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>18.28%</t>
+          <t>19.75%</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2684,28 +2684,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Prologis, Inc.</t>
+          <t>Sanofi</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1180.87</v>
+        <v>1122.15</v>
       </c>
       <c r="F73" t="n">
-        <v>127.13</v>
+        <v>46.2</v>
       </c>
       <c r="G73" t="n">
-        <v>155.57</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>17.87%</t>
+          <t>19.69%</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2715,28 +2715,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HDFC Bank Limited</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1657.16</v>
+        <v>1283.91</v>
       </c>
       <c r="F74" t="n">
-        <v>32.31</v>
+        <v>102.8</v>
       </c>
       <c r="G74" t="n">
-        <v>39.34</v>
+        <v>128.01</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>17.83%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2746,28 +2746,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Cadence Design Systems, Inc.</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1280.67</v>
+        <v>824.75</v>
       </c>
       <c r="F75" t="n">
-        <v>183.74</v>
+        <v>302.67</v>
       </c>
       <c r="G75" t="n">
-        <v>223.61</v>
+        <v>376.45</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>17.37%</t>
+          <t>18.93%</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2777,23 +2777,23 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc.</t>
+          <t>NXP Semiconductors N.V.</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1721.1</v>
+        <v>588.6900000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>24.07</v>
+        <v>233.5</v>
       </c>
       <c r="G76" t="n">
-        <v>29.13</v>
+        <v>288.03</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>17.28%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1084.12</v>
+        <v>1069.57</v>
       </c>
       <c r="F77" t="n">
-        <v>95.16</v>
+        <v>93.88</v>
       </c>
       <c r="G77" t="n">
         <v>115.04</v>
@@ -2824,12 +2824,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>17.28%</t>
+          <t>17.68%</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2839,28 +2839,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PepsiCo, Inc.</t>
+          <t>Petróleo Brasileiro S.A. - Petrobras</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2033.08</v>
+        <v>1000.17</v>
       </c>
       <c r="F78" t="n">
-        <v>148.5</v>
+        <v>15.52</v>
       </c>
       <c r="G78" t="n">
-        <v>179.53</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>17.24%</t>
+          <t>17.61%</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2870,28 +2870,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Intuitive Surgical, Inc.</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1182.82</v>
+        <v>1819.45</v>
       </c>
       <c r="F79" t="n">
-        <v>469.19</v>
+        <v>507.55</v>
       </c>
       <c r="G79" t="n">
-        <v>566.9</v>
+        <v>616</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>17.12%</t>
+          <t>17.59%</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2901,28 +2901,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Microchip Technology Incorporated</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>760.17</v>
+        <v>428.9</v>
       </c>
       <c r="F80" t="n">
-        <v>189.16</v>
+        <v>79.36</v>
       </c>
       <c r="G80" t="n">
-        <v>228.23</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>17.39%</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2932,28 +2932,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NXP Semiconductors N.V.</t>
+          <t>Sumitomo Mitsui Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>605.15</v>
+        <v>1366.66</v>
       </c>
       <c r="F81" t="n">
-        <v>240.03</v>
+        <v>21.29</v>
       </c>
       <c r="G81" t="n">
-        <v>288.03</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>16.63%</t>
+          <t>17.26%</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2963,28 +2963,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Microchip Technology Incorporated</t>
+          <t>HDFC Bank Limited</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>433.87</v>
+        <v>1669.47</v>
       </c>
       <c r="F82" t="n">
-        <v>80.28</v>
+        <v>32.55</v>
       </c>
       <c r="G82" t="n">
-        <v>96.3</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.18%</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2994,28 +2994,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Merck &amp; Co., Inc.</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2670.13</v>
+        <v>2035.68</v>
       </c>
       <c r="F83" t="n">
-        <v>106.9</v>
+        <v>148.69</v>
       </c>
       <c r="G83" t="n">
-        <v>127.87</v>
+        <v>179.53</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>16.24%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3025,28 +3025,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>GE HealthCare Technologies Inc.</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>361.87</v>
+        <v>762.14</v>
       </c>
       <c r="F84" t="n">
-        <v>79.26000000000001</v>
+        <v>189.65</v>
       </c>
       <c r="G84" t="n">
-        <v>94.63</v>
+        <v>228.23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>15.89%</t>
+          <t>16.75%</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3056,28 +3056,28 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>GE HealthCare Technologies Inc.</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3442.94</v>
+        <v>359.68</v>
       </c>
       <c r="F85" t="n">
-        <v>147.34</v>
+        <v>78.78</v>
       </c>
       <c r="G85" t="n">
-        <v>175.18</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>15.89%</t>
+          <t>16.49%</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>16855.52</v>
+        <v>13854.03</v>
       </c>
       <c r="F86" t="n">
-        <v>668.73</v>
+        <v>416.56</v>
       </c>
       <c r="G86" t="n">
-        <v>795.0599999999999</v>
+        <v>498.83</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>15.88%</t>
+          <t>16.17%</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3118,28 +3118,28 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Capital One Financial Corporation</t>
+          <t>Prologis, Inc.</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1388.51</v>
+        <v>1211.34</v>
       </c>
       <c r="F87" t="n">
-        <v>218.41</v>
+        <v>130.41</v>
       </c>
       <c r="G87" t="n">
-        <v>259.64</v>
+        <v>155.57</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>15.35%</t>
+          <t>16.15%</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3149,28 +3149,28 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>MercadoLibre, Inc.</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1292.75</v>
+        <v>1124.53</v>
       </c>
       <c r="F88" t="n">
-        <v>100.79</v>
+        <v>2218.14</v>
       </c>
       <c r="G88" t="n">
-        <v>119.06</v>
+        <v>2645.22</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>15.25%</t>
+          <t>15.68%</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Intuitive Surgical, Inc.</t>
+          <t>Boston Scientific Corporation</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1871.39</v>
+        <v>1369.27</v>
       </c>
       <c r="F89" t="n">
-        <v>522.04</v>
+        <v>92.33</v>
       </c>
       <c r="G89" t="n">
-        <v>616</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14.87%</t>
+          <t>15.53%</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3211,28 +3211,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cadence Design Systems, Inc.</t>
+          <t>Capital One Financial Corporation</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>873.3</v>
+        <v>1394.23</v>
       </c>
       <c r="F90" t="n">
-        <v>320.49</v>
+        <v>219.31</v>
       </c>
       <c r="G90" t="n">
-        <v>376.45</v>
+        <v>259.64</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>14.35%</t>
+          <t>15.27%</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3242,28 +3242,28 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Boston Scientific Corporation</t>
+          <t>Merck &amp; Co., Inc.</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1390.92</v>
+        <v>2706.1</v>
       </c>
       <c r="F91" t="n">
-        <v>93.79000000000001</v>
+        <v>108.34</v>
       </c>
       <c r="G91" t="n">
-        <v>109.5</v>
+        <v>127.87</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14.24%</t>
+          <t>15.17%</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3273,28 +3273,28 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MercadoLibre, Inc.</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1150.12</v>
+        <v>1295.44</v>
       </c>
       <c r="F92" t="n">
-        <v>2268.6</v>
+        <v>101</v>
       </c>
       <c r="G92" t="n">
-        <v>2645.22</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>13.76%</t>
+          <t>14.43%</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IBN</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3304,28 +3304,28 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1057.81</v>
+        <v>3508.39</v>
       </c>
       <c r="F93" t="n">
-        <v>29.58</v>
+        <v>149.9</v>
       </c>
       <c r="G93" t="n">
-        <v>34.3</v>
+        <v>175.18</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>13.51%</t>
+          <t>13.99%</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3335,28 +3335,28 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>14349.58</v>
+        <v>497.34</v>
       </c>
       <c r="F94" t="n">
-        <v>431.46</v>
+        <v>43.32</v>
       </c>
       <c r="G94" t="n">
-        <v>498.83</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.73%</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3366,28 +3366,28 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>AT&amp;T Inc.</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>500.78</v>
+        <v>1781.58</v>
       </c>
       <c r="F95" t="n">
-        <v>43.62</v>
+        <v>25.13</v>
       </c>
       <c r="G95" t="n">
-        <v>50.37</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13.12%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IBN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3397,28 +3397,28 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4713.25</v>
+        <v>1064.6</v>
       </c>
       <c r="F96" t="n">
-        <v>521.37</v>
+        <v>29.77</v>
       </c>
       <c r="G96" t="n">
-        <v>600.08</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12.99%</t>
+          <t>12.81%</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3428,28 +3428,28 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>The Home Depot, Inc.</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>35800.36</v>
+        <v>3701.41</v>
       </c>
       <c r="F97" t="n">
-        <v>481.63</v>
+        <v>371.81</v>
       </c>
       <c r="G97" t="n">
-        <v>553.5</v>
+        <v>426.44</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>12.82%</t>
+          <t>12.12%</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3459,28 +3459,28 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Eaton Corporation plc</t>
+          <t>Booking Holdings Inc.</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1352.12</v>
+        <v>1657.22</v>
       </c>
       <c r="F98" t="n">
-        <v>347.32</v>
+        <v>5113.32</v>
       </c>
       <c r="G98" t="n">
-        <v>398.4</v>
+        <v>5818.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12.67%</t>
+          <t>12.11%</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3490,28 +3490,28 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc.</t>
+          <t>IDEXX Laboratories, Inc.</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1661.69</v>
+        <v>541.4</v>
       </c>
       <c r="F99" t="n">
-        <v>39.41</v>
+        <v>676.71</v>
       </c>
       <c r="G99" t="n">
-        <v>45.13</v>
+        <v>769.98</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12.62%</t>
+          <t>12.07%</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3521,28 +3521,28 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1786.63</v>
+        <v>1354.93</v>
       </c>
       <c r="F100" t="n">
-        <v>145.96</v>
+        <v>354.3</v>
       </c>
       <c r="G100" t="n">
-        <v>167.04</v>
+        <v>402.95</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.79%</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3552,23 +3552,23 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc.</t>
+          <t>Verizon Communications Inc.</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1648.11</v>
+        <v>1678.56</v>
       </c>
       <c r="F101" t="n">
-        <v>5085.22</v>
+        <v>39.81</v>
       </c>
       <c r="G101" t="n">
-        <v>5818.24</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.31%</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6310.38</v>
+        <v>6403.4</v>
       </c>
       <c r="F102" t="n">
-        <v>326.98</v>
+        <v>331.8</v>
       </c>
       <c r="G102" t="n">
         <v>374.11</v>
@@ -3599,12 +3599,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12.11%</t>
+          <t>11.26%</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3614,23 +3614,23 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3085.12</v>
+        <v>4230.43</v>
       </c>
       <c r="F103" t="n">
-        <v>292.48</v>
+        <v>952.89</v>
       </c>
       <c r="G103" t="n">
-        <v>332.79</v>
+        <v>1073.82</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>12.01%</t>
+          <t>11.17%</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3649,10 +3649,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1262.43</v>
+        <v>1274.44</v>
       </c>
       <c r="F104" t="n">
-        <v>183.94</v>
+        <v>185.69</v>
       </c>
       <c r="G104" t="n">
         <v>209.05</v>
@@ -3661,12 +3661,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>11.99%</t>
+          <t>11.05%</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3676,28 +3676,28 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>The Home Depot, Inc.</t>
+          <t>Eaton Corporation plc</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3736.15</v>
+        <v>1379.56</v>
       </c>
       <c r="F105" t="n">
-        <v>375.3</v>
+        <v>354.37</v>
       </c>
       <c r="G105" t="n">
-        <v>426.44</v>
+        <v>398.4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.94%</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3707,23 +3707,23 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1368.43</v>
+        <v>2224.79</v>
       </c>
       <c r="F106" t="n">
-        <v>357.83</v>
+        <v>592.16</v>
       </c>
       <c r="G106" t="n">
-        <v>402.95</v>
+        <v>664.9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>11.15%</t>
+          <t>10.51%</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>37892.48</v>
+        <v>38164.36</v>
       </c>
       <c r="F107" t="n">
-        <v>256.44</v>
+        <v>258.28</v>
       </c>
       <c r="G107" t="n">
         <v>288.62</v>
@@ -3754,12 +3754,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>10.45%</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3769,28 +3769,28 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Toyota Motor Corporation</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2866.34</v>
+        <v>1830.94</v>
       </c>
       <c r="F108" t="n">
-        <v>218.89</v>
+        <v>149.58</v>
       </c>
       <c r="G108" t="n">
-        <v>245.75</v>
+        <v>167.04</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10.85%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3800,28 +3800,28 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1350.69</v>
+        <v>3152.42</v>
       </c>
       <c r="F109" t="n">
-        <v>227.71</v>
+        <v>298.86</v>
       </c>
       <c r="G109" t="n">
-        <v>255.44</v>
+        <v>332.79</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10.68%</t>
+          <t>10.18%</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3831,28 +3831,28 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories, Inc.</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>550.22</v>
+        <v>1865.63</v>
       </c>
       <c r="F110" t="n">
-        <v>687.74</v>
+        <v>148.15</v>
       </c>
       <c r="G110" t="n">
-        <v>769.98</v>
+        <v>164.94</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10.53%</t>
+          <t>9.86%</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3862,28 +3862,28 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>Altria Group, Inc.</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4265.46</v>
+        <v>1003.9</v>
       </c>
       <c r="F111" t="n">
-        <v>960.78</v>
+        <v>59.76</v>
       </c>
       <c r="G111" t="n">
-        <v>1073.82</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10.45%</t>
+          <t>9.68%</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3893,28 +3893,28 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>8187.75</v>
+        <v>9180.969999999999</v>
       </c>
       <c r="F112" t="n">
-        <v>300.77</v>
+        <v>1024.14</v>
       </c>
       <c r="G112" t="n">
-        <v>335.87</v>
+        <v>1133.95</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9.97%</t>
+          <t>9.64%</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3924,28 +3924,28 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Take-Two Interactive Software, Inc.</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3783.42</v>
+        <v>442.12</v>
       </c>
       <c r="F113" t="n">
-        <v>51.81</v>
+        <v>239.27</v>
       </c>
       <c r="G113" t="n">
-        <v>57.55</v>
+        <v>264.79</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9.95%</t>
+          <t>9.39%</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3955,23 +3955,23 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2763.34</v>
+        <v>4915.38</v>
       </c>
       <c r="F114" t="n">
-        <v>88.03</v>
+        <v>543.73</v>
       </c>
       <c r="G114" t="n">
-        <v>97.76000000000001</v>
+        <v>600.08</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>9.74%</t>
+          <t>9.27%</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>46629.38</v>
+        <v>46870.41</v>
       </c>
       <c r="F115" t="n">
-        <v>191.52</v>
+        <v>192.51</v>
       </c>
       <c r="G115" t="n">
         <v>212.18</v>
@@ -4002,12 +4002,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9.71%</t>
+          <t>9.08%</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4017,28 +4017,28 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>O'Reilly Automotive, Inc.</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>9177.92</v>
+        <v>836.3</v>
       </c>
       <c r="F116" t="n">
-        <v>1023.8</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="G116" t="n">
-        <v>1133.95</v>
+        <v>108.72</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>9.46%</t>
+          <t>8.77%</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4048,23 +4048,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2749.62</v>
+        <v>8341.559999999999</v>
       </c>
       <c r="F117" t="n">
-        <v>294.16</v>
+        <v>306.42</v>
       </c>
       <c r="G117" t="n">
-        <v>324.9</v>
+        <v>335.87</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>9.31%</t>
+          <t>8.58%</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3864.74</v>
+        <v>3895.85</v>
       </c>
       <c r="F118" t="n">
-        <v>218.67</v>
+        <v>220.43</v>
       </c>
       <c r="G118" t="n">
         <v>241.12</v>
@@ -4095,12 +4095,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8.97%</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4110,28 +4110,28 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1890.82</v>
+        <v>1385.51</v>
       </c>
       <c r="F119" t="n">
-        <v>150.15</v>
+        <v>233.58</v>
       </c>
       <c r="G119" t="n">
-        <v>164.94</v>
+        <v>255.44</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8.55%</t>
+          <t>8.53%</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4141,28 +4141,28 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>HCA Healthcare, Inc.</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2284.38</v>
+        <v>1129.09</v>
       </c>
       <c r="F120" t="n">
-        <v>608.02</v>
+        <v>482.53</v>
       </c>
       <c r="G120" t="n">
-        <v>664.9</v>
+        <v>527.55</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8.46%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4172,28 +4172,28 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc.</t>
+          <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1612.35</v>
+        <v>1219.6</v>
       </c>
       <c r="F121" t="n">
-        <v>528.12</v>
+        <v>475.68</v>
       </c>
       <c r="G121" t="n">
-        <v>576.91</v>
+        <v>519.88</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>8.37%</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4203,28 +4203,28 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1451.64</v>
+        <v>1613.91</v>
       </c>
       <c r="F122" t="n">
-        <v>66.53</v>
+        <v>528.63</v>
       </c>
       <c r="G122" t="n">
-        <v>72.58</v>
+        <v>576.91</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4234,23 +4234,23 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software, Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>449.35</v>
+        <v>1022.81</v>
       </c>
       <c r="F123" t="n">
-        <v>243.18</v>
+        <v>822.3</v>
       </c>
       <c r="G123" t="n">
-        <v>264.79</v>
+        <v>894.75</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8.14%</t>
+          <t>7.95%</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>415.36</v>
+        <v>416.23</v>
       </c>
       <c r="F124" t="n">
-        <v>91.03</v>
+        <v>91.22</v>
       </c>
       <c r="G124" t="n">
         <v>99.09999999999999</v>
@@ -4281,12 +4281,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8.07%</t>
+          <t>7.77%</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4296,28 +4296,28 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals Incorporated</t>
+          <t>Xcel Energy Inc.</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1225.32</v>
+        <v>449.39</v>
       </c>
       <c r="F125" t="n">
-        <v>477.91</v>
+        <v>75.97</v>
       </c>
       <c r="G125" t="n">
-        <v>519.88</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>7.73%</t>
+          <t>7.77%</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4327,28 +4327,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Xcel Energy Inc.</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>449.63</v>
+        <v>3876.16</v>
       </c>
       <c r="F126" t="n">
-        <v>76.01000000000001</v>
+        <v>53.08</v>
       </c>
       <c r="G126" t="n">
-        <v>82.37</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>7.67%</t>
+          <t>7.75%</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4358,28 +4358,28 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>American Express Company</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2484.23</v>
+        <v>402.68</v>
       </c>
       <c r="F127" t="n">
-        <v>356.99</v>
+        <v>82.45</v>
       </c>
       <c r="G127" t="n">
-        <v>386.63</v>
+        <v>89.37</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>7.65%</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4389,28 +4389,28 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Exelon Corporation</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1028.19</v>
+        <v>448.54</v>
       </c>
       <c r="F128" t="n">
-        <v>826.62</v>
+        <v>44.41</v>
       </c>
       <c r="G128" t="n">
-        <v>894.75</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4420,23 +4420,23 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>BlackRock, Inc.</t>
+          <t>Toyota Motor Corporation</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1740.28</v>
+        <v>2973.46</v>
       </c>
       <c r="F129" t="n">
-        <v>1121.67</v>
+        <v>227.07</v>
       </c>
       <c r="G129" t="n">
-        <v>1214.03</v>
+        <v>245.75</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7.33%</t>
+          <t>7.53%</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1644.81</v>
+        <v>1641.25</v>
       </c>
       <c r="F130" t="n">
-        <v>147.79</v>
+        <v>147.47</v>
       </c>
       <c r="G130" t="n">
         <v>159.48</v>
@@ -4467,12 +4467,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>7.28%</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4482,28 +4482,28 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Exelon Corporation</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>452.07</v>
+        <v>2845.27</v>
       </c>
       <c r="F131" t="n">
-        <v>44.76</v>
+        <v>90.64</v>
       </c>
       <c r="G131" t="n">
-        <v>48.09</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>7.28%</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4513,28 +4513,28 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>HCA Healthcare, Inc.</t>
+          <t>American Express Company</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1149.45</v>
+        <v>2494.74</v>
       </c>
       <c r="F132" t="n">
-        <v>491.23</v>
+        <v>358.5</v>
       </c>
       <c r="G132" t="n">
-        <v>527.55</v>
+        <v>386.63</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.14%</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4544,28 +4544,28 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>406.83</v>
+        <v>18609.31</v>
       </c>
       <c r="F133" t="n">
-        <v>83.3</v>
+        <v>738.3099999999999</v>
       </c>
       <c r="G133" t="n">
-        <v>89.37</v>
+        <v>795.0599999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6.76%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4575,28 +4575,28 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>O'Reilly Automotive, Inc.</t>
+          <t>BlackRock, Inc.</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>857.62</v>
+        <v>1749.76</v>
       </c>
       <c r="F134" t="n">
-        <v>101.37</v>
+        <v>1127.78</v>
       </c>
       <c r="G134" t="n">
-        <v>108.72</v>
+        <v>1214.03</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6.53%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4606,23 +4606,23 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2117.13</v>
+        <v>1473.46</v>
       </c>
       <c r="F135" t="n">
-        <v>451.5</v>
+        <v>67.53</v>
       </c>
       <c r="G135" t="n">
-        <v>483.05</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>6.52%</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>25978.29</v>
+        <v>25841.46</v>
       </c>
       <c r="F136" t="n">
-        <v>243.01</v>
+        <v>241.73</v>
       </c>
       <c r="G136" t="n">
         <v>258.6</v>
@@ -4653,12 +4653,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5.74%</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>BN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4668,28 +4668,28 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Marriott International, Inc.</t>
+          <t>Brookfield Corporation</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>847.14</v>
+        <v>1046.1</v>
       </c>
       <c r="F137" t="n">
-        <v>312.07</v>
+        <v>46.55</v>
       </c>
       <c r="G137" t="n">
-        <v>331.09</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.85%</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4699,28 +4699,28 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4114.71</v>
+        <v>1394.26</v>
       </c>
       <c r="F138" t="n">
-        <v>252.74</v>
+        <v>126.93</v>
       </c>
       <c r="G138" t="n">
-        <v>267.08</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.81%</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4730,28 +4730,28 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2897.95</v>
+        <v>2133.54</v>
       </c>
       <c r="F139" t="n">
-        <v>182.34</v>
+        <v>455</v>
       </c>
       <c r="G139" t="n">
-        <v>192.68</v>
+        <v>483.05</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5.03%</t>
+          <t>5.58%</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4761,28 +4761,28 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Mitsubishi UFJ Financial Group, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2055.87</v>
+        <v>4105.6</v>
       </c>
       <c r="F140" t="n">
-        <v>17.95</v>
+        <v>252.18</v>
       </c>
       <c r="G140" t="n">
-        <v>18.9</v>
+        <v>267.08</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.34%</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4792,28 +4792,28 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Brookfield Corporation</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1058.23</v>
+        <v>2898.9</v>
       </c>
       <c r="F141" t="n">
-        <v>47.09</v>
+        <v>182.4</v>
       </c>
       <c r="G141" t="n">
-        <v>49.57</v>
+        <v>192.68</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>5.23%</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4823,28 +4823,28 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc.</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2835.92</v>
+        <v>1495.72</v>
       </c>
       <c r="F142" t="n">
-        <v>936.8099999999999</v>
+        <v>266.64</v>
       </c>
       <c r="G142" t="n">
-        <v>984.7</v>
+        <v>281.36</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4.78%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SATA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4854,28 +4854,28 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Altria Group, Inc.</t>
+          <t>Strive Asset Management, LLC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1060.52</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>63.13</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="G143" t="n">
-        <v>66.3</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.97%</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SCCO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4885,28 +4885,28 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Southern Copper Corporation</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5523.03</v>
+        <v>1703.15</v>
       </c>
       <c r="F144" t="n">
-        <v>1422.92</v>
+        <v>207.93</v>
       </c>
       <c r="G144" t="n">
-        <v>1493.47</v>
+        <v>218.81</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>International Business Machines Corporation</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2340.34</v>
+        <v>2890.58</v>
       </c>
       <c r="F145" t="n">
-        <v>166.58</v>
+        <v>309.24</v>
       </c>
       <c r="G145" t="n">
-        <v>174.61</v>
+        <v>324.9</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4.56%</t>
+          <t>4.53%</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4947,23 +4947,23 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Ross Stores, Inc.</t>
+          <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>605.05</v>
+        <v>2845.94</v>
       </c>
       <c r="F146" t="n">
-        <v>186.04</v>
+        <v>940.12</v>
       </c>
       <c r="G146" t="n">
-        <v>194.92</v>
+        <v>984.7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>637.61</v>
+        <v>638.09</v>
       </c>
       <c r="F147" t="n">
-        <v>119.12</v>
+        <v>119.21</v>
       </c>
       <c r="G147" t="n">
         <v>124.8</v>
@@ -4994,12 +4994,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5009,28 +5009,28 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>Ross Stores, Inc.</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1511.32</v>
+        <v>606.55</v>
       </c>
       <c r="F148" t="n">
-        <v>269.42</v>
+        <v>186.5</v>
       </c>
       <c r="G148" t="n">
-        <v>281.36</v>
+        <v>194.92</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5040,28 +5040,28 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Agnico Eagle Mines Limited</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1210.62</v>
+        <v>1081.96</v>
       </c>
       <c r="F149" t="n">
-        <v>303.65</v>
+        <v>215.51</v>
       </c>
       <c r="G149" t="n">
-        <v>316.94</v>
+        <v>225</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>TBB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5071,28 +5071,28 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>9293.950000000001</v>
+        <v>1376.54</v>
       </c>
       <c r="F150" t="n">
-        <v>116.57</v>
+        <v>22.42</v>
       </c>
       <c r="G150" t="n">
-        <v>121.62</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5102,28 +5102,28 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>AstraZeneca PLC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>696.87</v>
+        <v>2870.81</v>
       </c>
       <c r="F151" t="n">
-        <v>37.38</v>
+        <v>92.59</v>
       </c>
       <c r="G151" t="n">
-        <v>38.95</v>
+        <v>96.51000000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>3.84%</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5133,28 +5133,28 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Strive Asset Management, LLC</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>782.01</v>
       </c>
       <c r="F152" t="n">
-        <v>97.27</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="G152" t="n">
-        <v>101.35</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5164,28 +5164,28 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Parker-Hannifin Corporation</t>
+          <t>BHP Group Limited</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1159.49</v>
+        <v>1853.95</v>
       </c>
       <c r="F153" t="n">
-        <v>916.27</v>
+        <v>72.17</v>
       </c>
       <c r="G153" t="n">
-        <v>954.3</v>
+        <v>74.98</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ENB</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5195,28 +5195,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Enbridge Inc.</t>
+          <t>Mitsubishi UFJ Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1060.06</v>
+        <v>2084.5</v>
       </c>
       <c r="F154" t="n">
-        <v>48.56</v>
+        <v>18.2</v>
       </c>
       <c r="G154" t="n">
-        <v>50.54</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5226,28 +5226,28 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Honeywell International Inc.</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1459.87</v>
+        <v>1453.34</v>
       </c>
       <c r="F155" t="n">
-        <v>216.64</v>
+        <v>622.51</v>
       </c>
       <c r="G155" t="n">
-        <v>225.29</v>
+        <v>645.67</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5257,28 +5257,28 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
+          <t>Walmart Inc.</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1429.02</v>
+        <v>9360.92</v>
       </c>
       <c r="F156" t="n">
-        <v>25.14</v>
+        <v>117.41</v>
       </c>
       <c r="G156" t="n">
-        <v>26.14</v>
+        <v>121.62</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TBB</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5288,28 +5288,28 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
+          <t>Marriott International, Inc.</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1382.68</v>
+        <v>868.04</v>
       </c>
       <c r="F157" t="n">
-        <v>22.52</v>
+        <v>319.77</v>
       </c>
       <c r="G157" t="n">
-        <v>23.41</v>
+        <v>331.09</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5319,28 +5319,28 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AstraZeneca PLC</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2890.35</v>
+        <v>1220.67</v>
       </c>
       <c r="F158" t="n">
-        <v>93.22</v>
+        <v>306.17</v>
       </c>
       <c r="G158" t="n">
-        <v>96.51000000000001</v>
+        <v>316.94</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5350,28 +5350,28 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1842.79</v>
+        <v>17610.78</v>
       </c>
       <c r="F159" t="n">
-        <v>342.22</v>
+        <v>339.55</v>
       </c>
       <c r="G159" t="n">
-        <v>353.25</v>
+        <v>351.33</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.34%</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5381,28 +5381,28 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Novartis AG</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2837.32</v>
+        <v>2371.25</v>
       </c>
       <c r="F160" t="n">
-        <v>147.87</v>
+        <v>168.78</v>
       </c>
       <c r="G160" t="n">
-        <v>152.48</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5412,28 +5412,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Baker Hughes Company</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1576.95</v>
+        <v>559.8</v>
       </c>
       <c r="F161" t="n">
-        <v>93.62</v>
+        <v>56.73</v>
       </c>
       <c r="G161" t="n">
-        <v>96.44</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5443,17 +5443,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2674.3</v>
+        <v>1846.67</v>
       </c>
       <c r="F162" t="n">
-        <v>199.46</v>
+        <v>342.94</v>
       </c>
       <c r="G162" t="n">
-        <v>205.36</v>
+        <v>353.25</v>
       </c>
     </row>
     <row r="163">
@@ -5490,12 +5490,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5505,28 +5505,28 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>UBS Group AG</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1511.32</v>
+        <v>706</v>
       </c>
       <c r="F164" t="n">
-        <v>47.96</v>
+        <v>37.87</v>
       </c>
       <c r="G164" t="n">
-        <v>49.36</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5536,28 +5536,28 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Banco Santander, S.A.</t>
+          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1875.06</v>
+        <v>1446.07</v>
       </c>
       <c r="F165" t="n">
-        <v>12.68</v>
+        <v>25.44</v>
       </c>
       <c r="G165" t="n">
-        <v>13.05</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.67%</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5567,28 +5567,28 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>McDonald's Corporation</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2232.15</v>
+        <v>2679.94</v>
       </c>
       <c r="F166" t="n">
-        <v>312.8</v>
+        <v>199.88</v>
       </c>
       <c r="G166" t="n">
-        <v>321.79</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>ENB</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5598,28 +5598,28 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Enbridge Inc.</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>790.61</v>
+        <v>1074.91</v>
       </c>
       <c r="F167" t="n">
-        <v>80.92</v>
+        <v>49.24</v>
       </c>
       <c r="G167" t="n">
-        <v>83.23999999999999</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5629,152 +5629,152 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>GSK plc</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1012.54</v>
+        <v>5648.17</v>
       </c>
       <c r="F168" t="n">
-        <v>50.1</v>
+        <v>1455.16</v>
       </c>
       <c r="G168" t="n">
-        <v>51.46</v>
+        <v>1493.48</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>Seagate Technology Holdings plc</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1937.12</v>
+        <v>972.95</v>
       </c>
       <c r="F169" t="n">
-        <v>711.59</v>
+        <v>446.57</v>
       </c>
       <c r="G169" t="n">
-        <v>730.46</v>
+        <v>457.84</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>17753.4</v>
+        <v>954.38</v>
       </c>
       <c r="F170" t="n">
-        <v>342.3</v>
+        <v>278.41</v>
       </c>
       <c r="G170" t="n">
-        <v>351.33</v>
+        <v>285.42</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>FER</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation</t>
+          <t>Ferrovial SE</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1878.21</v>
+        <v>486.98</v>
       </c>
       <c r="F171" t="n">
-        <v>103.47</v>
+        <v>68.11</v>
       </c>
       <c r="G171" t="n">
-        <v>105.81</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FER</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Ferrovial SE</t>
+          <t>Cisco Systems, Inc.</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>488.26</v>
+        <v>3098.84</v>
       </c>
       <c r="F172" t="n">
-        <v>68.29000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="G172" t="n">
-        <v>69.81999999999999</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5784,28 +5784,28 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>UBS Group AG</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2682.69</v>
+        <v>1517.62</v>
       </c>
       <c r="F173" t="n">
-        <v>336.75</v>
+        <v>48.16</v>
       </c>
       <c r="G173" t="n">
-        <v>344.04</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5815,28 +5815,28 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Novartis AG</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3013.63</v>
+        <v>2857.27</v>
       </c>
       <c r="F174" t="n">
-        <v>643.28</v>
+        <v>148.91</v>
       </c>
       <c r="G174" t="n">
-        <v>655.78</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5846,23 +5846,23 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>PACCAR Inc</t>
+          <t>The Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>646.3200000000001</v>
+        <v>1878.21</v>
       </c>
       <c r="F175" t="n">
-        <v>123.06</v>
+        <v>103.47</v>
       </c>
       <c r="G175" t="n">
-        <v>125.36</v>
+        <v>105.81</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2780</v>
+        <v>2769.1</v>
       </c>
       <c r="F176" t="n">
-        <v>178.59</v>
+        <v>177.89</v>
       </c>
       <c r="G176" t="n">
         <v>181.91</v>
@@ -5893,12 +5893,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5908,28 +5908,28 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3021.18</v>
+        <v>3116.51</v>
       </c>
       <c r="F177" t="n">
-        <v>239.58</v>
+        <v>665.24</v>
       </c>
       <c r="G177" t="n">
-        <v>243.99</v>
+        <v>679.99</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5939,28 +5939,28 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3119.78</v>
+        <v>3449.17</v>
       </c>
       <c r="F178" t="n">
-        <v>78.95999999999999</v>
+        <v>171.19</v>
       </c>
       <c r="G178" t="n">
-        <v>80.39</v>
+        <v>174.92</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5970,28 +5970,28 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc</t>
+          <t>Rio Tinto Group</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2986.87</v>
+        <v>1898.64</v>
       </c>
       <c r="F179" t="n">
-        <v>87</v>
+        <v>95.13</v>
       </c>
       <c r="G179" t="n">
-        <v>88.54000000000001</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6001,28 +6001,28 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Baker Hughes Company</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>558.8099999999999</v>
+        <v>4904.86</v>
       </c>
       <c r="F180" t="n">
-        <v>56.63</v>
+        <v>435.79</v>
       </c>
       <c r="G180" t="n">
-        <v>57.58</v>
+        <v>444.71</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SCCO</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6032,28 +6032,28 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Southern Copper Corporation</t>
+          <t>McDonald's Corporation</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1623.28</v>
+        <v>2251.49</v>
       </c>
       <c r="F181" t="n">
-        <v>198.18</v>
+        <v>315.51</v>
       </c>
       <c r="G181" t="n">
-        <v>201.44</v>
+        <v>321.79</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ITUB</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6063,90 +6063,90 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NextEra Energy, Inc.</t>
+          <t>Itaú Unibanco Holding S.A.</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1823.74</v>
+        <v>984.67</v>
       </c>
       <c r="F182" t="n">
-        <v>87.56999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="G182" t="n">
-        <v>88.95999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>Banco Santander, S.A.</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>958.8</v>
+        <v>1894.28</v>
       </c>
       <c r="F183" t="n">
-        <v>279.7</v>
+        <v>12.81</v>
       </c>
       <c r="G183" t="n">
-        <v>284</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings plc</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>965.02</v>
+        <v>1952.91</v>
       </c>
       <c r="F184" t="n">
-        <v>442.93</v>
+        <v>717.39</v>
       </c>
       <c r="G184" t="n">
-        <v>449.5</v>
+        <v>730.46</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6156,28 +6156,28 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Parker-Hannifin Corporation</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>40595.16</v>
+        <v>1200.14</v>
       </c>
       <c r="F185" t="n">
-        <v>336.28</v>
+        <v>948.4</v>
       </c>
       <c r="G185" t="n">
-        <v>341.2</v>
+        <v>965</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6187,28 +6187,28 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>PACCAR Inc</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1423.17</v>
+        <v>647.92</v>
       </c>
       <c r="F186" t="n">
-        <v>525.01</v>
+        <v>123.32</v>
       </c>
       <c r="G186" t="n">
-        <v>532.61</v>
+        <v>125.36</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6218,28 +6218,28 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc.</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1733.66</v>
+        <v>1599.02</v>
       </c>
       <c r="F187" t="n">
-        <v>139.72</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="G187" t="n">
-        <v>141.71</v>
+        <v>96.44</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6249,28 +6249,28 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2142.77</v>
+        <v>1023.86</v>
       </c>
       <c r="F188" t="n">
-        <v>1627.2</v>
+        <v>50.66</v>
       </c>
       <c r="G188" t="n">
-        <v>1650</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6280,28 +6280,28 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>40697.94</v>
+        <v>1731.55</v>
       </c>
       <c r="F189" t="n">
-        <v>336.01</v>
+        <v>139.55</v>
       </c>
       <c r="G189" t="n">
-        <v>340.49</v>
+        <v>141.71</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6311,28 +6311,28 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Shell plc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2145.32</v>
+        <v>1556.1</v>
       </c>
       <c r="F190" t="n">
-        <v>75.79000000000001</v>
+        <v>72.63</v>
       </c>
       <c r="G190" t="n">
-        <v>76.73999999999999</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6342,28 +6342,28 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1532.32</v>
+        <v>1989.61</v>
       </c>
       <c r="F191" t="n">
-        <v>71.52</v>
+        <v>218.97</v>
       </c>
       <c r="G191" t="n">
-        <v>72.37</v>
+        <v>222</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6373,59 +6373,59 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1965.28</v>
+        <v>1436.88</v>
       </c>
       <c r="F192" t="n">
-        <v>216.17</v>
+        <v>530.0700000000001</v>
       </c>
       <c r="G192" t="n">
-        <v>218.15</v>
+        <v>537.26</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>Exxon Mobil Corporation</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>556.5700000000001</v>
+        <v>5990.29</v>
       </c>
       <c r="F193" t="n">
-        <v>1161.78</v>
+        <v>140.51</v>
       </c>
       <c r="G193" t="n">
-        <v>1171.57</v>
+        <v>142.34</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6435,28 +6435,28 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4899.12</v>
+        <v>3129.5</v>
       </c>
       <c r="F194" t="n">
-        <v>435.28</v>
+        <v>248.17</v>
       </c>
       <c r="G194" t="n">
-        <v>438.94</v>
+        <v>251.32</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6466,28 +6466,28 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Itaú Unibanco Holding S.A.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>979.16</v>
+        <v>40969.25</v>
       </c>
       <c r="F195" t="n">
-        <v>8.880000000000001</v>
+        <v>338.25</v>
       </c>
       <c r="G195" t="n">
-        <v>8.949999999999999</v>
+        <v>342.26</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6497,28 +6497,28 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>3144.26</v>
+        <v>5476.09</v>
       </c>
       <c r="F196" t="n">
-        <v>73.06</v>
+        <v>227.29</v>
       </c>
       <c r="G196" t="n">
-        <v>73.62</v>
+        <v>229.98</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6528,28 +6528,28 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Agnico Eagle Mines Limited</t>
+          <t>NextEra Energy, Inc.</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1119.51</v>
+        <v>1836.45</v>
       </c>
       <c r="F197" t="n">
-        <v>222.99</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="G197" t="n">
-        <v>224.3</v>
+        <v>89.19</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6559,28 +6559,28 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Electronic Arts Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>510.07</v>
+        <v>40882.47</v>
       </c>
       <c r="F198" t="n">
-        <v>203.94</v>
+        <v>338.66</v>
       </c>
       <c r="G198" t="n">
-        <v>204.89</v>
+        <v>342.29</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6590,28 +6590,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>British American Tobacco p.l.c.</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5486.45</v>
+        <v>1306.94</v>
       </c>
       <c r="F199" t="n">
-        <v>227.72</v>
+        <v>60.22</v>
       </c>
       <c r="G199" t="n">
-        <v>228.57</v>
+        <v>60.82</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6621,28 +6621,28 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>British American Tobacco p.l.c.</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1305.64</v>
+        <v>2719.26</v>
       </c>
       <c r="F200" t="n">
-        <v>60.16</v>
+        <v>341.34</v>
       </c>
       <c r="G200" t="n">
-        <v>60.38</v>
+        <v>344.6</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6652,28 +6652,28 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>Shell plc</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1394.42</v>
+        <v>2192.36</v>
       </c>
       <c r="F201" t="n">
-        <v>597.27</v>
+        <v>77.47</v>
       </c>
       <c r="G201" t="n">
-        <v>599.3200000000001</v>
+        <v>78.17</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6683,28 +6683,28 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1449.4</v>
+        <v>3160.18</v>
       </c>
       <c r="F202" t="n">
-        <v>131.95</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="G202" t="n">
-        <v>132.4</v>
+        <v>74.08</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6714,28 +6714,28 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corporation</t>
+          <t>CME Group Inc.</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5865.38</v>
+        <v>1041.97</v>
       </c>
       <c r="F203" t="n">
-        <v>137.58</v>
+        <v>289.83</v>
       </c>
       <c r="G203" t="n">
-        <v>138</v>
+        <v>291.76</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6745,28 +6745,28 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3423.79</v>
+        <v>2218.5</v>
       </c>
       <c r="F204" t="n">
-        <v>169.93</v>
+        <v>1684.71</v>
       </c>
       <c r="G204" t="n">
-        <v>170.42</v>
+        <v>1693.35</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6776,28 +6776,28 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>CME Group Inc.</t>
+          <t>HSBC Holdings plc</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1028.39</v>
+        <v>3039.74</v>
       </c>
       <c r="F205" t="n">
-        <v>286.05</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="G205" t="n">
-        <v>286.76</v>
+        <v>88.98999999999999</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6807,28 +6807,28 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Electronic Arts Inc.</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1555.26</v>
+        <v>510.09</v>
       </c>
       <c r="F206" t="n">
-        <v>317.62</v>
+        <v>203.95</v>
       </c>
       <c r="G206" t="n">
-        <v>318.17</v>
+        <v>204.89</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6838,48 +6838,110 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Rio Tinto Group</t>
+          <t>Honeywell International Inc.</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1863.52</v>
+        <v>1531.3</v>
       </c>
       <c r="F207" t="n">
-        <v>93.37</v>
+        <v>227.24</v>
       </c>
       <c r="G207" t="n">
-        <v>93.45</v>
+        <v>227.86</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1822.86</v>
+        <v>566.8099999999999</v>
       </c>
       <c r="F208" t="n">
-        <v>70.95999999999999</v>
+        <v>1183.15</v>
       </c>
       <c r="G208" t="n">
-        <v>70.98</v>
+        <v>1184.87</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>BMO</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Bank of Montreal</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>1016.34</v>
+      </c>
+      <c r="F209" t="n">
+        <v>141.4</v>
+      </c>
+      <c r="G209" t="n">
+        <v>141.6</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Analog Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>1560.53</v>
+      </c>
+      <c r="F210" t="n">
+        <v>318.7</v>
+      </c>
+      <c r="G210" t="n">
+        <v>319.11</v>
       </c>
     </row>
   </sheetData>

--- a/美股回撤分析报告.xlsx
+++ b/美股回撤分析报告.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G210"/>
+  <dimension ref="A1:G206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>82.84%</t>
+          <t>82.97%</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>507.4</v>
+        <v>503.39</v>
       </c>
       <c r="F2" t="n">
-        <v>53.11</v>
+        <v>52.69</v>
       </c>
       <c r="G2" t="n">
         <v>309.44</v>
@@ -499,12 +499,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>75.54%</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,28 +514,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Charter Communications, Inc.</t>
+          <t>Atlassian Corporation</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>261.6</v>
+        <v>311.09</v>
       </c>
       <c r="F3" t="n">
-        <v>191.52</v>
+        <v>118.18</v>
       </c>
       <c r="G3" t="n">
-        <v>825.62</v>
+        <v>483.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>75.08%</t>
+          <t>75.03%</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -545,23 +545,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atlassian Corporation</t>
+          <t>Charter Communications, Inc.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>316.88</v>
+        <v>281.54</v>
       </c>
       <c r="F4" t="n">
-        <v>120.38</v>
+        <v>206.12</v>
       </c>
       <c r="G4" t="n">
-        <v>483.13</v>
+        <v>825.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>73.63%</t>
+          <t>72.43%</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>414.31</v>
+        <v>433.18</v>
       </c>
       <c r="F5" t="n">
-        <v>143.19</v>
+        <v>149.71</v>
       </c>
       <c r="G5" t="n">
         <v>543</v>
@@ -592,7 +592,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>69.88%</t>
+          <t>69.74%</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2061.23</v>
+        <v>2070.36</v>
       </c>
       <c r="F6" t="n">
-        <v>115.2</v>
+        <v>115.71</v>
       </c>
       <c r="G6" t="n">
         <v>382.43</v>
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>64.68%</t>
+          <t>64.76%</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>684.34</v>
+        <v>682.85</v>
       </c>
       <c r="F7" t="n">
-        <v>27.6</v>
+        <v>27.54</v>
       </c>
       <c r="G7" t="n">
         <v>78.14</v>
@@ -654,7 +654,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>64.31%</t>
+          <t>63.38%</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>273.9</v>
+        <v>281</v>
       </c>
       <c r="F8" t="n">
-        <v>23.14</v>
+        <v>23.74</v>
       </c>
       <c r="G8" t="n">
         <v>64.84</v>
@@ -685,7 +685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>58.69%</t>
+          <t>58.63%</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2636.32</v>
+        <v>2640.76</v>
       </c>
       <c r="F9" t="n">
-        <v>59.33</v>
+        <v>59.43</v>
       </c>
       <c r="G9" t="n">
         <v>143.64</v>
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>58.31%</t>
+          <t>58.08%</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1220.85</v>
+        <v>1227.54</v>
       </c>
       <c r="F10" t="n">
-        <v>291.65</v>
+        <v>293.25</v>
       </c>
       <c r="G10" t="n">
         <v>699.54</v>
@@ -747,7 +747,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>55.11%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>290.19</v>
+        <v>286.43</v>
       </c>
       <c r="F11" t="n">
-        <v>74</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>164.86</v>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>52.34%</t>
+          <t>53.21%</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2647.68</v>
+        <v>2599.12</v>
       </c>
       <c r="F12" t="n">
-        <v>292.29</v>
+        <v>286.93</v>
       </c>
       <c r="G12" t="n">
         <v>613.22</v>
@@ -809,7 +809,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51.69%</t>
+          <t>52.47%</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1457.98</v>
+        <v>1434.55</v>
       </c>
       <c r="F13" t="n">
-        <v>102.7</v>
+        <v>101.05</v>
       </c>
       <c r="G13" t="n">
         <v>212.6</v>
@@ -840,12 +840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51.28%</t>
+          <t>52.19%</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -855,28 +855,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1231.67</v>
+        <v>4728.6</v>
       </c>
       <c r="F14" t="n">
-        <v>116.73</v>
+        <v>164.58</v>
       </c>
       <c r="G14" t="n">
-        <v>239.62</v>
+        <v>344.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.17%</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -886,23 +886,23 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4855.88</v>
+        <v>1234.62</v>
       </c>
       <c r="F15" t="n">
-        <v>169.01</v>
+        <v>117.01</v>
       </c>
       <c r="G15" t="n">
-        <v>344.21</v>
+        <v>239.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>47.97%</t>
+          <t>48.95%</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>509.71</v>
+        <v>500.08</v>
       </c>
       <c r="F16" t="n">
-        <v>112.76</v>
+        <v>110.63</v>
       </c>
       <c r="G16" t="n">
         <v>216.72</v>
@@ -933,12 +933,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>47.19%</t>
+          <t>46.82%</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -948,28 +948,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Zscaler, Inc.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1483.97</v>
+        <v>318.96</v>
       </c>
       <c r="F17" t="n">
-        <v>26.1</v>
+        <v>200.01</v>
       </c>
       <c r="G17" t="n">
-        <v>49.42</v>
+        <v>376.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>46.66%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -979,23 +979,23 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zscaler, Inc.</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>319.95</v>
+        <v>1503.3</v>
       </c>
       <c r="F18" t="n">
-        <v>200.63</v>
+        <v>26.44</v>
       </c>
       <c r="G18" t="n">
-        <v>376.11</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>46.27%</t>
+          <t>46.34%</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1832.7</v>
+        <v>1830.19</v>
       </c>
       <c r="F19" t="n">
-        <v>234.04</v>
+        <v>233.72</v>
       </c>
       <c r="G19" t="n">
         <v>435.56</v>
@@ -1026,43 +1026,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>43.89%</t>
+          <t>45.41%</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>466.34</v>
+        <v>384.14</v>
       </c>
       <c r="F20" t="n">
-        <v>174.66</v>
+        <v>483.58</v>
       </c>
       <c r="G20" t="n">
-        <v>311.28</v>
+        <v>885.92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>43.75%</t>
+          <t>44.18%</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1072,28 +1072,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1992.03</v>
+        <v>1117.87</v>
       </c>
       <c r="F21" t="n">
-        <v>111.58</v>
+        <v>105.36</v>
       </c>
       <c r="G21" t="n">
-        <v>198.35</v>
+        <v>188.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42.55%</t>
+          <t>44.09%</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1103,28 +1103,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Alibaba Group Holding Limited</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1150.44</v>
+        <v>4047.95</v>
       </c>
       <c r="F22" t="n">
-        <v>108.43</v>
+        <v>169.56</v>
       </c>
       <c r="G22" t="n">
-        <v>188.75</v>
+        <v>303.26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>42.54%</t>
+          <t>43.58%</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1134,59 +1134,59 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Limited</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4159.91</v>
+        <v>468.93</v>
       </c>
       <c r="F23" t="n">
-        <v>174.25</v>
+        <v>175.63</v>
       </c>
       <c r="G23" t="n">
-        <v>303.26</v>
+        <v>311.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>42.48%</t>
+          <t>43.13%</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>404.8</v>
+        <v>2013.81</v>
       </c>
       <c r="F24" t="n">
-        <v>509.58</v>
+        <v>112.8</v>
       </c>
       <c r="G24" t="n">
-        <v>885.92</v>
+        <v>198.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>42.05%</t>
+          <t>42.03%</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1196,28 +1196,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Comcast Corporation</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1152.4</v>
+        <v>2021</v>
       </c>
       <c r="F25" t="n">
-        <v>29.24</v>
+        <v>212.29</v>
       </c>
       <c r="G25" t="n">
-        <v>50.46</v>
+        <v>366.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>41.54%</t>
+          <t>41.18%</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1227,28 +1227,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Airbnb, Inc.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2038.04</v>
+        <v>792.05</v>
       </c>
       <c r="F26" t="n">
-        <v>214.08</v>
+        <v>129.37</v>
       </c>
       <c r="G26" t="n">
-        <v>366.19</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>40.09%</t>
+          <t>41.04%</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1258,23 +1258,23 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Airbnb, Inc.</t>
+          <t>Comcast Corporation</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>806.74</v>
+        <v>1172.5</v>
       </c>
       <c r="F27" t="n">
-        <v>131.77</v>
+        <v>29.75</v>
       </c>
       <c r="G27" t="n">
-        <v>219.94</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38.71%</t>
+          <t>39.14%</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>262.47</v>
+        <v>260.65</v>
       </c>
       <c r="F28" t="n">
-        <v>61.93</v>
+        <v>61.5</v>
       </c>
       <c r="G28" t="n">
         <v>101.05</v>
@@ -1305,7 +1305,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>38.63%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1069.1</v>
+        <v>1067.87</v>
       </c>
       <c r="F29" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>14.08</v>
@@ -1336,12 +1336,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>38.27%</t>
+          <t>38.46%</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1351,28 +1351,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Roper Technologies, Inc.</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>392.88</v>
+        <v>1388.99</v>
       </c>
       <c r="F30" t="n">
-        <v>365</v>
+        <v>498.92</v>
       </c>
       <c r="G30" t="n">
-        <v>591.26</v>
+        <v>810.72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>37.99%</t>
+          <t>38.44%</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3527.56</v>
+        <v>785.84</v>
       </c>
       <c r="F31" t="n">
-        <v>83.16</v>
+        <v>741.45</v>
       </c>
       <c r="G31" t="n">
-        <v>134.12</v>
+        <v>1204.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>37.96%</t>
+          <t>37.89%</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1413,28 +1413,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1400.3</v>
+        <v>680.37</v>
       </c>
       <c r="F32" t="n">
-        <v>502.98</v>
+        <v>78.92</v>
       </c>
       <c r="G32" t="n">
-        <v>810.72</v>
+        <v>127.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>37.78%</t>
+          <t>37.75%</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1444,28 +1444,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>794.3099999999999</v>
+        <v>3541.55</v>
       </c>
       <c r="F33" t="n">
-        <v>749.4400000000001</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>1204.52</v>
+        <v>134.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>37.43%</t>
+          <t>37.21%</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1475,28 +1475,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Copart, Inc.</t>
+          <t>Roper Technologies, Inc.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>389.92</v>
+        <v>399.58</v>
       </c>
       <c r="F34" t="n">
-        <v>40.28</v>
+        <v>371.23</v>
       </c>
       <c r="G34" t="n">
-        <v>64.38</v>
+        <v>591.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.97%</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1506,28 +1506,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Anheuser-Busch InBev SA/NV</t>
+          <t>Copart, Inc.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1385.73</v>
+        <v>392.82</v>
       </c>
       <c r="F35" t="n">
-        <v>71.28</v>
+        <v>40.58</v>
       </c>
       <c r="G35" t="n">
-        <v>113.15</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36.45%</t>
+          <t>36.65%</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1537,28 +1537,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Anheuser-Busch InBev SA/NV</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>449.49</v>
+        <v>1393.51</v>
       </c>
       <c r="F36" t="n">
-        <v>128.18</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>201.69</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36.09%</t>
+          <t>36.55%</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1568,28 +1568,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>AppLovin Corporation</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2336.04</v>
+        <v>1600.29</v>
       </c>
       <c r="F37" t="n">
-        <v>200.21</v>
+        <v>473.11</v>
       </c>
       <c r="G37" t="n">
-        <v>313.28</v>
+        <v>745.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>35.98%</t>
+          <t>36.26%</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1599,28 +1599,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Spotify Technology S.A.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>701.23</v>
+        <v>1030.19</v>
       </c>
       <c r="F38" t="n">
-        <v>81.34</v>
+        <v>500.35</v>
       </c>
       <c r="G38" t="n">
-        <v>127.06</v>
+        <v>785</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>35.81%</t>
+          <t>35.88%</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1630,28 +1630,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Spotify Technology S.A.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1037.54</v>
+        <v>453.49</v>
       </c>
       <c r="F39" t="n">
-        <v>503.92</v>
+        <v>129.32</v>
       </c>
       <c r="G39" t="n">
-        <v>785</v>
+        <v>201.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34.83%</t>
+          <t>35.83%</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1661,28 +1661,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>366.97</v>
+        <v>2345.72</v>
       </c>
       <c r="F40" t="n">
-        <v>102.23</v>
+        <v>201.04</v>
       </c>
       <c r="G40" t="n">
-        <v>156.86</v>
+        <v>313.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>33.77%</t>
+          <t>34.25%</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1692,28 +1692,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1619.93</v>
+        <v>370.2</v>
       </c>
       <c r="F41" t="n">
-        <v>261.22</v>
+        <v>103.13</v>
       </c>
       <c r="G41" t="n">
-        <v>394.41</v>
+        <v>156.86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>32.58%</t>
+          <t>33.16%</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1723,23 +1723,23 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>302.61</v>
+        <v>1634.93</v>
       </c>
       <c r="F42" t="n">
-        <v>216.59</v>
+        <v>263.64</v>
       </c>
       <c r="G42" t="n">
-        <v>321.24</v>
+        <v>394.41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>32.14%</t>
+          <t>32.56%</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1064.63</v>
+        <v>1057.96</v>
       </c>
       <c r="F43" t="n">
-        <v>114.98</v>
+        <v>114.26</v>
       </c>
       <c r="G43" t="n">
         <v>169.44</v>
@@ -1770,12 +1770,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>31.82%</t>
+          <t>32.31%</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1785,28 +1785,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>QUALCOMM Incorporated</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1630.28</v>
+        <v>303.82</v>
       </c>
       <c r="F44" t="n">
-        <v>152.22</v>
+        <v>217.46</v>
       </c>
       <c r="G44" t="n">
-        <v>223.25</v>
+        <v>321.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>30.71%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1816,23 +1816,23 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>T-Mobile US, Inc.</t>
+          <t>QUALCOMM Incorporated</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2130.19</v>
+        <v>1623.53</v>
       </c>
       <c r="F45" t="n">
-        <v>189.28</v>
+        <v>151.59</v>
       </c>
       <c r="G45" t="n">
-        <v>273.15</v>
+        <v>223.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>30.27%</t>
+          <t>31.91%</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1041.4</v>
+        <v>1016.88</v>
       </c>
       <c r="F46" t="n">
-        <v>287.45</v>
+        <v>280.68</v>
       </c>
       <c r="G46" t="n">
         <v>412.23</v>
@@ -1863,7 +1863,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>30.02%</t>
+          <t>31.78%</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>458.16</v>
+        <v>446.62</v>
       </c>
       <c r="F47" t="n">
-        <v>346.79</v>
+        <v>338.06</v>
       </c>
       <c r="G47" t="n">
         <v>495.55</v>
@@ -1894,43 +1894,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29.01%</t>
+          <t>29.36%</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>624.58</v>
+        <v>3493.88</v>
       </c>
       <c r="F48" t="n">
-        <v>81.51000000000001</v>
+        <v>146.59</v>
       </c>
       <c r="G48" t="n">
-        <v>114.82</v>
+        <v>207.52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>28.65%</t>
+          <t>29.23%</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1940,28 +1940,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>364.37</v>
+        <v>622.67</v>
       </c>
       <c r="F49" t="n">
-        <v>26.82</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>37.59</v>
+        <v>114.82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27.26%</t>
+          <t>28.63%</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1971,59 +1971,59 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>895.1</v>
+        <v>889.85</v>
       </c>
       <c r="F50" t="n">
-        <v>207.68</v>
+        <v>465.11</v>
       </c>
       <c r="G50" t="n">
-        <v>285.5</v>
+        <v>651.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26.82%</t>
+          <t>28.33%</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3619.49</v>
+        <v>881.91</v>
       </c>
       <c r="F51" t="n">
-        <v>151.86</v>
+        <v>204.62</v>
       </c>
       <c r="G51" t="n">
-        <v>207.52</v>
+        <v>285.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26.67%</t>
+          <t>27.97%</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2033,28 +2033,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1753.96</v>
+        <v>1708.41</v>
       </c>
       <c r="F52" t="n">
-        <v>142.94</v>
+        <v>131.23</v>
       </c>
       <c r="G52" t="n">
-        <v>194.94</v>
+        <v>182.19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>26.53%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2064,28 +2064,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sony Group Corporation</t>
+          <t>T-Mobile US, Inc.</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1339.01</v>
+        <v>2219.44</v>
       </c>
       <c r="F53" t="n">
-        <v>22.29</v>
+        <v>197.21</v>
       </c>
       <c r="G53" t="n">
-        <v>30.34</v>
+        <v>273.15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>26.35%</t>
+          <t>27.16%</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2095,59 +2095,59 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>Sony Group Corporation</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>918.33</v>
+        <v>1327.6</v>
       </c>
       <c r="F54" t="n">
-        <v>480</v>
+        <v>22.1</v>
       </c>
       <c r="G54" t="n">
-        <v>651.73</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25.82%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Insmed Incorporated</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>336.59</v>
+        <v>372.8</v>
       </c>
       <c r="F55" t="n">
-        <v>157.82</v>
+        <v>27.44</v>
       </c>
       <c r="G55" t="n">
-        <v>212.75</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25.76%</t>
+          <t>26.94%</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2157,28 +2157,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>544.6</v>
+        <v>1800.38</v>
       </c>
       <c r="F56" t="n">
-        <v>255.68</v>
+        <v>142.42</v>
       </c>
       <c r="G56" t="n">
-        <v>344.39</v>
+        <v>194.94</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>25.39%</t>
+          <t>26.57%</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2188,59 +2188,59 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Old Dominion Freight Line, Inc.</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>362.73</v>
+        <v>538.61</v>
       </c>
       <c r="F57" t="n">
-        <v>172.59</v>
+        <v>252.87</v>
       </c>
       <c r="G57" t="n">
-        <v>231.32</v>
+        <v>344.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>24.32%</t>
+          <t>26.27%</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>The Progressive Corporation</t>
+          <t>Insmed Incorporated</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1220.82</v>
+        <v>334.56</v>
       </c>
       <c r="F58" t="n">
-        <v>208.26</v>
+        <v>156.87</v>
       </c>
       <c r="G58" t="n">
-        <v>275.18</v>
+        <v>212.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>24.31%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2250,28 +2250,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1552.49</v>
+        <v>2321.26</v>
       </c>
       <c r="F59" t="n">
-        <v>219.62</v>
+        <v>46.47</v>
       </c>
       <c r="G59" t="n">
-        <v>290.14</v>
+        <v>62.29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.12%</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2281,28 +2281,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Automatic Data Processing, Inc.</t>
+          <t>Old Dominion Freight Line, Inc.</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>994.8200000000001</v>
+        <v>364.01</v>
       </c>
       <c r="F60" t="n">
-        <v>245.97</v>
+        <v>173.2</v>
       </c>
       <c r="G60" t="n">
-        <v>324.5</v>
+        <v>231.32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>23.65%</t>
+          <t>24.56%</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2312,28 +2312,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AppLovin Corporation</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1925.45</v>
+        <v>1547.33</v>
       </c>
       <c r="F61" t="n">
-        <v>569.24</v>
+        <v>218.89</v>
       </c>
       <c r="G61" t="n">
-        <v>745.61</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>23.47%</t>
+          <t>24.41%</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2343,28 +2343,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>The Progressive Corporation</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1846.45</v>
+        <v>1219.3</v>
       </c>
       <c r="F62" t="n">
-        <v>106.09</v>
+        <v>208</v>
       </c>
       <c r="G62" t="n">
-        <v>138.63</v>
+        <v>275.18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22.98%</t>
+          <t>23.94%</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2374,28 +2374,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Company</t>
+          <t>Automatic Data Processing, Inc.</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1105.01</v>
+        <v>998.26</v>
       </c>
       <c r="F63" t="n">
-        <v>54.28</v>
+        <v>246.82</v>
       </c>
       <c r="G63" t="n">
-        <v>70.48</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21.88%</t>
+          <t>22.26%</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2405,28 +2405,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2430.65</v>
+        <v>31951.74</v>
       </c>
       <c r="F64" t="n">
-        <v>48.66</v>
+        <v>430.29</v>
       </c>
       <c r="G64" t="n">
-        <v>62.29</v>
+        <v>553.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21.68%</t>
+          <t>22.14%</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2436,28 +2436,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>32222.78</v>
+        <v>1112.78</v>
       </c>
       <c r="F65" t="n">
-        <v>433.5</v>
+        <v>441.4</v>
       </c>
       <c r="G65" t="n">
-        <v>553.5</v>
+        <v>566.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21.57%</t>
+          <t>21.89%</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2467,28 +2467,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Bristol-Myers Squibb Company</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1120.88</v>
+        <v>1120.68</v>
       </c>
       <c r="F66" t="n">
-        <v>444.62</v>
+        <v>55.05</v>
       </c>
       <c r="G66" t="n">
-        <v>566.9</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21.39%</t>
+          <t>21.51%</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2498,28 +2498,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mondelez International, Inc.</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>741.5599999999999</v>
+        <v>1669.38</v>
       </c>
       <c r="F67" t="n">
-        <v>57.31</v>
+        <v>80.05</v>
       </c>
       <c r="G67" t="n">
-        <v>72.90000000000001</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.49%</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2529,28 +2529,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>NXP Semiconductors N.V.</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1205.18</v>
+        <v>570.13</v>
       </c>
       <c r="F68" t="n">
-        <v>176.2</v>
+        <v>226.14</v>
       </c>
       <c r="G68" t="n">
-        <v>223.61</v>
+        <v>288.03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21.16%</t>
+          <t>21.28%</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2560,28 +2560,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Cadence Design Systems, Inc.</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1869.97</v>
+        <v>807.55</v>
       </c>
       <c r="F69" t="n">
-        <v>143.64</v>
+        <v>296.36</v>
       </c>
       <c r="G69" t="n">
-        <v>182.19</v>
+        <v>376.45</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20.48%</t>
+          <t>21.16%</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2591,28 +2591,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Diamondback Energy, Inc.</t>
+          <t>Microchip Technology Incorporated</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>472.07</v>
+        <v>410.31</v>
       </c>
       <c r="F70" t="n">
-        <v>163.07</v>
+        <v>75.92</v>
       </c>
       <c r="G70" t="n">
-        <v>205.08</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20.08%</t>
+          <t>21.16%</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2622,28 +2622,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>15680.81</v>
+        <v>1902.32</v>
       </c>
       <c r="F71" t="n">
-        <v>330.73</v>
+        <v>109.3</v>
       </c>
       <c r="G71" t="n">
-        <v>413.82</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>19.89%</t>
+          <t>20.86%</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2653,28 +2653,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1703.79</v>
+        <v>1233.48</v>
       </c>
       <c r="F72" t="n">
-        <v>81.7</v>
+        <v>176.97</v>
       </c>
       <c r="G72" t="n">
-        <v>101.99</v>
+        <v>223.61</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>19.75%</t>
+          <t>20.07%</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2684,28 +2684,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>Starbucks Corporation</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1122.15</v>
+        <v>1047.59</v>
       </c>
       <c r="F73" t="n">
-        <v>46.2</v>
+        <v>91.95</v>
       </c>
       <c r="G73" t="n">
-        <v>57.57</v>
+        <v>115.04</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>19.69%</t>
+          <t>20.05%</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2715,28 +2715,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Diamondback Energy, Inc.</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1283.91</v>
+        <v>474.61</v>
       </c>
       <c r="F74" t="n">
-        <v>102.8</v>
+        <v>163.95</v>
       </c>
       <c r="G74" t="n">
-        <v>128.01</v>
+        <v>205.08</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.94%</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2746,28 +2746,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cadence Design Systems, Inc.</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>824.75</v>
+        <v>15707.84</v>
       </c>
       <c r="F75" t="n">
-        <v>302.67</v>
+        <v>331.3</v>
       </c>
       <c r="G75" t="n">
-        <v>376.45</v>
+        <v>413.82</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>18.93%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2777,28 +2777,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NXP Semiconductors N.V.</t>
+          <t>Mondelez International, Inc.</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>588.6900000000001</v>
+        <v>756.5700000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>233.5</v>
+        <v>58.47</v>
       </c>
       <c r="G76" t="n">
-        <v>288.03</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2808,28 +2808,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Starbucks Corporation</t>
+          <t>MercadoLibre, Inc.</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1069.57</v>
+        <v>1088.87</v>
       </c>
       <c r="F77" t="n">
-        <v>93.88</v>
+        <v>2147.79</v>
       </c>
       <c r="G77" t="n">
-        <v>115.04</v>
+        <v>2645.22</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>17.68%</t>
+          <t>18.57%</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2839,28 +2839,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Petróleo Brasileiro S.A. - Petrobras</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1000.17</v>
+        <v>1301.77</v>
       </c>
       <c r="F78" t="n">
-        <v>15.52</v>
+        <v>104.23</v>
       </c>
       <c r="G78" t="n">
-        <v>18.85</v>
+        <v>128.01</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>17.61%</t>
+          <t>18.55%</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2870,28 +2870,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Intuitive Surgical, Inc.</t>
+          <t>Sumitomo Mitsui Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1819.45</v>
+        <v>1347.4</v>
       </c>
       <c r="F79" t="n">
-        <v>507.55</v>
+        <v>20.99</v>
       </c>
       <c r="G79" t="n">
-        <v>616</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>17.59%</t>
+          <t>18.29%</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2901,28 +2901,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Microchip Technology Incorporated</t>
+          <t>Sanofi</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>428.9</v>
+        <v>1142.55</v>
       </c>
       <c r="F80" t="n">
-        <v>79.36</v>
+        <v>47.04</v>
       </c>
       <c r="G80" t="n">
-        <v>96.3</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>17.39%</t>
+          <t>18.15%</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2932,23 +2932,23 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Financial Group, Inc.</t>
+          <t>Intuitive Surgical, Inc.</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1366.66</v>
+        <v>1807.51</v>
       </c>
       <c r="F81" t="n">
-        <v>21.29</v>
+        <v>504.22</v>
       </c>
       <c r="G81" t="n">
-        <v>25.77</v>
+        <v>616</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17.26%</t>
+          <t>17.69%</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1669.47</v>
+        <v>1660.75</v>
       </c>
       <c r="F82" t="n">
-        <v>32.55</v>
+        <v>32.38</v>
       </c>
       <c r="G82" t="n">
         <v>39.34</v>
@@ -2979,12 +2979,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>17.18%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2994,28 +2994,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PepsiCo, Inc.</t>
+          <t>Take-Two Interactive Software, Inc.</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2035.68</v>
+        <v>407.07</v>
       </c>
       <c r="F83" t="n">
-        <v>148.69</v>
+        <v>220.3</v>
       </c>
       <c r="G83" t="n">
-        <v>179.53</v>
+        <v>264.79</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3025,23 +3025,23 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>762.14</v>
+        <v>1234.11</v>
       </c>
       <c r="F84" t="n">
-        <v>189.65</v>
+        <v>112.35</v>
       </c>
       <c r="G84" t="n">
-        <v>228.23</v>
+        <v>134.88</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>16.75%</t>
+          <t>16.55%</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>359.68</v>
+        <v>360.55</v>
       </c>
       <c r="F85" t="n">
-        <v>78.78</v>
+        <v>78.97</v>
       </c>
       <c r="G85" t="n">
         <v>94.63</v>
@@ -3072,12 +3072,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16.49%</t>
+          <t>16.14%</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3087,23 +3087,23 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>13854.03</v>
+        <v>769.13</v>
       </c>
       <c r="F86" t="n">
-        <v>416.56</v>
+        <v>191.39</v>
       </c>
       <c r="G86" t="n">
-        <v>498.83</v>
+        <v>228.23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>16.17%</t>
+          <t>16.08%</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1211.34</v>
+        <v>1212.73</v>
       </c>
       <c r="F87" t="n">
-        <v>130.41</v>
+        <v>130.56</v>
       </c>
       <c r="G87" t="n">
         <v>155.57</v>
@@ -3134,12 +3134,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>16.15%</t>
+          <t>15.68%</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3149,28 +3149,28 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MercadoLibre, Inc.</t>
+          <t>Capital One Financial Corporation</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1124.53</v>
+        <v>1391.81</v>
       </c>
       <c r="F88" t="n">
-        <v>2218.14</v>
+        <v>218.93</v>
       </c>
       <c r="G88" t="n">
-        <v>2645.22</v>
+        <v>259.64</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>15.68%</t>
+          <t>15.67%</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Boston Scientific Corporation</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1369.27</v>
+        <v>1880.38</v>
       </c>
       <c r="F89" t="n">
-        <v>92.33</v>
+        <v>1427.94</v>
       </c>
       <c r="G89" t="n">
-        <v>109.5</v>
+        <v>1693.35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>15.53%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>IBN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3211,28 +3211,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Capital One Financial Corporation</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1394.23</v>
+        <v>1047.44</v>
       </c>
       <c r="F90" t="n">
-        <v>219.31</v>
+        <v>29.29</v>
       </c>
       <c r="G90" t="n">
-        <v>259.64</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15.27%</t>
+          <t>14.58%</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3242,28 +3242,28 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Merck &amp; Co., Inc.</t>
+          <t>Boston Scientific Corporation</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2706.1</v>
+        <v>1387.07</v>
       </c>
       <c r="F91" t="n">
-        <v>108.34</v>
+        <v>93.53</v>
       </c>
       <c r="G91" t="n">
-        <v>127.87</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>15.17%</t>
+          <t>14.42%</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3273,28 +3273,28 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1295.44</v>
+        <v>2103.31</v>
       </c>
       <c r="F92" t="n">
-        <v>101</v>
+        <v>153.63</v>
       </c>
       <c r="G92" t="n">
-        <v>119.06</v>
+        <v>179.53</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14.43%</t>
+          <t>14.07%</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3304,28 +3304,28 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3508.39</v>
+        <v>1784.91</v>
       </c>
       <c r="F93" t="n">
-        <v>149.9</v>
+        <v>141.74</v>
       </c>
       <c r="G93" t="n">
-        <v>175.18</v>
+        <v>164.94</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>13.99%</t>
+          <t>14.03%</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3335,28 +3335,28 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Booking Holdings Inc.</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>497.34</v>
+        <v>1621.09</v>
       </c>
       <c r="F94" t="n">
-        <v>43.32</v>
+        <v>5001.84</v>
       </c>
       <c r="G94" t="n">
-        <v>50.37</v>
+        <v>5818.24</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13.73%</t>
+          <t>13.97%</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3366,28 +3366,28 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1781.58</v>
+        <v>6210.99</v>
       </c>
       <c r="F95" t="n">
-        <v>25.13</v>
+        <v>321.83</v>
       </c>
       <c r="G95" t="n">
-        <v>29.13</v>
+        <v>374.11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.76%</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IBN</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3397,28 +3397,28 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>Merck &amp; Co., Inc.</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1064.6</v>
+        <v>2754.31</v>
       </c>
       <c r="F96" t="n">
-        <v>29.77</v>
+        <v>110.27</v>
       </c>
       <c r="G96" t="n">
-        <v>34.3</v>
+        <v>127.87</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12.81%</t>
+          <t>13.75%</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3428,28 +3428,28 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>The Home Depot, Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3701.41</v>
+        <v>1763.62</v>
       </c>
       <c r="F97" t="n">
-        <v>371.81</v>
+        <v>144.08</v>
       </c>
       <c r="G97" t="n">
-        <v>426.44</v>
+        <v>167.04</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>12.12%</t>
+          <t>13.72%</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3459,28 +3459,28 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc.</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1657.22</v>
+        <v>16150.84</v>
       </c>
       <c r="F98" t="n">
-        <v>5113.32</v>
+        <v>430.41</v>
       </c>
       <c r="G98" t="n">
-        <v>5818.24</v>
+        <v>498.83</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12.11%</t>
+          <t>13.52%</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3490,28 +3490,28 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories, Inc.</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>541.4</v>
+        <v>1320.58</v>
       </c>
       <c r="F99" t="n">
-        <v>676.71</v>
+        <v>102.96</v>
       </c>
       <c r="G99" t="n">
-        <v>769.98</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12.07%</t>
+          <t>13.44%</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3521,28 +3521,28 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1354.93</v>
+        <v>497.8</v>
       </c>
       <c r="F100" t="n">
-        <v>354.3</v>
+        <v>43.36</v>
       </c>
       <c r="G100" t="n">
-        <v>402.95</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>11.79%</t>
+          <t>13.36%</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3552,28 +3552,28 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc.</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1678.56</v>
+        <v>3546.46</v>
       </c>
       <c r="F101" t="n">
-        <v>39.81</v>
+        <v>151.77</v>
       </c>
       <c r="G101" t="n">
-        <v>45.13</v>
+        <v>175.18</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>11.31%</t>
+          <t>13.02%</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>SCCO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3583,28 +3583,28 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Southern Copper Corporation</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6403.4</v>
+        <v>1558.91</v>
       </c>
       <c r="F102" t="n">
-        <v>331.8</v>
+        <v>190.32</v>
       </c>
       <c r="G102" t="n">
-        <v>374.11</v>
+        <v>218.81</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>11.26%</t>
+          <t>12.98%</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3614,28 +3614,28 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4230.43</v>
+        <v>2173.88</v>
       </c>
       <c r="F103" t="n">
-        <v>952.89</v>
+        <v>578.61</v>
       </c>
       <c r="G103" t="n">
-        <v>1073.82</v>
+        <v>664.9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>11.17%</t>
+          <t>12.93%</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3645,28 +3645,28 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>IDEXX Laboratories, Inc.</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1274.44</v>
+        <v>536.4</v>
       </c>
       <c r="F104" t="n">
-        <v>185.69</v>
+        <v>670.46</v>
       </c>
       <c r="G104" t="n">
-        <v>209.05</v>
+        <v>769.98</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>11.05%</t>
+          <t>12.44%</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3676,59 +3676,59 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Eaton Corporation plc</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1379.56</v>
+        <v>4174.31</v>
       </c>
       <c r="F105" t="n">
-        <v>354.37</v>
+        <v>940.25</v>
       </c>
       <c r="G105" t="n">
-        <v>398.4</v>
+        <v>1073.82</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10.94%</t>
+          <t>12.33%</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2224.79</v>
+        <v>857.78</v>
       </c>
       <c r="F106" t="n">
-        <v>592.16</v>
+        <v>250.23</v>
       </c>
       <c r="G106" t="n">
-        <v>664.9</v>
+        <v>285.42</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10.51%</t>
+          <t>12.16%</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3738,28 +3738,28 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>The Home Depot, Inc.</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>38164.36</v>
+        <v>3729.09</v>
       </c>
       <c r="F107" t="n">
-        <v>258.28</v>
+        <v>374.59</v>
       </c>
       <c r="G107" t="n">
-        <v>288.62</v>
+        <v>426.44</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10.45%</t>
+          <t>11.79%</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3769,28 +3769,28 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Eaton Corporation plc</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1830.94</v>
+        <v>1368.08</v>
       </c>
       <c r="F108" t="n">
-        <v>149.58</v>
+        <v>351.42</v>
       </c>
       <c r="G108" t="n">
-        <v>167.04</v>
+        <v>398.4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.36%</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3800,59 +3800,59 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3152.42</v>
+        <v>3854.06</v>
       </c>
       <c r="F109" t="n">
-        <v>298.86</v>
+        <v>236.73</v>
       </c>
       <c r="G109" t="n">
-        <v>332.79</v>
+        <v>267.08</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10.18%</t>
+          <t>10.95%</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Seagate Technology Holdings plc</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1865.63</v>
+        <v>888.24</v>
       </c>
       <c r="F110" t="n">
-        <v>148.15</v>
+        <v>407.69</v>
       </c>
       <c r="G110" t="n">
-        <v>164.94</v>
+        <v>457.84</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>9.86%</t>
+          <t>10.21%</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3862,28 +3862,28 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Altria Group, Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1003.9</v>
+        <v>4813.75</v>
       </c>
       <c r="F111" t="n">
-        <v>59.76</v>
+        <v>538.79</v>
       </c>
       <c r="G111" t="n">
-        <v>66.3</v>
+        <v>600.08</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>9.68%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3893,28 +3893,28 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>9180.969999999999</v>
+        <v>38341.68</v>
       </c>
       <c r="F112" t="n">
-        <v>1024.14</v>
+        <v>259.48</v>
       </c>
       <c r="G112" t="n">
-        <v>1133.95</v>
+        <v>288.62</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9.64%</t>
+          <t>10.03%</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3924,28 +3924,28 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software, Inc.</t>
+          <t>AT&amp;T Inc.</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>442.12</v>
+        <v>1858.14</v>
       </c>
       <c r="F113" t="n">
-        <v>239.27</v>
+        <v>26.21</v>
       </c>
       <c r="G113" t="n">
-        <v>264.79</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9.39%</t>
+          <t>9.92%</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3955,28 +3955,28 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4915.38</v>
+        <v>46534.42</v>
       </c>
       <c r="F114" t="n">
-        <v>543.73</v>
+        <v>191.13</v>
       </c>
       <c r="G114" t="n">
-        <v>600.08</v>
+        <v>212.18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3986,28 +3986,28 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>46870.41</v>
+        <v>1292.77</v>
       </c>
       <c r="F115" t="n">
-        <v>192.51</v>
+        <v>188.36</v>
       </c>
       <c r="G115" t="n">
-        <v>212.18</v>
+        <v>209.05</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9.08%</t>
+          <t>9.88%</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4017,28 +4017,28 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>O'Reilly Automotive, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>836.3</v>
+        <v>18124.27</v>
       </c>
       <c r="F116" t="n">
-        <v>98.84999999999999</v>
+        <v>716.5</v>
       </c>
       <c r="G116" t="n">
-        <v>108.72</v>
+        <v>795.0599999999999</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8.77%</t>
+          <t>9.61%</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4048,28 +4048,28 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>8341.559999999999</v>
+        <v>1204.78</v>
       </c>
       <c r="F117" t="n">
-        <v>306.42</v>
+        <v>469.9</v>
       </c>
       <c r="G117" t="n">
-        <v>335.87</v>
+        <v>519.88</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8.58%</t>
+          <t>9.48%</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4079,28 +4079,28 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>O'Reilly Automotive, Inc.</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3895.85</v>
+        <v>832.58</v>
       </c>
       <c r="F118" t="n">
-        <v>220.43</v>
+        <v>98.41</v>
       </c>
       <c r="G118" t="n">
-        <v>241.12</v>
+        <v>108.72</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8.56%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4110,28 +4110,28 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1385.51</v>
+        <v>8327.129999999999</v>
       </c>
       <c r="F119" t="n">
-        <v>233.58</v>
+        <v>305.89</v>
       </c>
       <c r="G119" t="n">
-        <v>255.44</v>
+        <v>335.87</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>8.91%</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4141,28 +4141,28 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>HCA Healthcare, Inc.</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1129.09</v>
+        <v>4669.51</v>
       </c>
       <c r="F120" t="n">
-        <v>482.53</v>
+        <v>414.88</v>
       </c>
       <c r="G120" t="n">
-        <v>527.55</v>
+        <v>455.48</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.91%</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4172,28 +4172,28 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals Incorporated</t>
+          <t>American Express Company</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1219.6</v>
+        <v>2450.69</v>
       </c>
       <c r="F121" t="n">
-        <v>475.68</v>
+        <v>352.17</v>
       </c>
       <c r="G121" t="n">
-        <v>519.88</v>
+        <v>386.63</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8.37%</t>
+          <t>8.54%</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4203,28 +4203,28 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1613.91</v>
+        <v>9297.6</v>
       </c>
       <c r="F122" t="n">
-        <v>528.63</v>
+        <v>1037.15</v>
       </c>
       <c r="G122" t="n">
-        <v>576.91</v>
+        <v>1133.95</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.51%</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4234,28 +4234,28 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1022.81</v>
+        <v>1611.34</v>
       </c>
       <c r="F123" t="n">
-        <v>822.3</v>
+        <v>527.79</v>
       </c>
       <c r="G123" t="n">
-        <v>894.75</v>
+        <v>576.91</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7.95%</t>
+          <t>8.34%</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4265,28 +4265,28 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Coca-Cola Europacific Partners PLC</t>
+          <t>BHP Group Limited</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>416.23</v>
+        <v>1765.58</v>
       </c>
       <c r="F124" t="n">
-        <v>91.22</v>
+        <v>68.73</v>
       </c>
       <c r="G124" t="n">
-        <v>99.09999999999999</v>
+        <v>74.98</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7.77%</t>
+          <t>8.29%</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4296,28 +4296,28 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Xcel Energy Inc.</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>449.39</v>
+        <v>1413.28</v>
       </c>
       <c r="F125" t="n">
-        <v>75.97</v>
+        <v>369.56</v>
       </c>
       <c r="G125" t="n">
-        <v>82.37</v>
+        <v>402.95</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>7.77%</t>
+          <t>8.18%</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4327,28 +4327,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3876.16</v>
+        <v>400.78</v>
       </c>
       <c r="F126" t="n">
-        <v>53.08</v>
+        <v>82.06</v>
       </c>
       <c r="G126" t="n">
-        <v>57.55</v>
+        <v>89.37</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>7.75%</t>
+          <t>8.11%</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>BN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4358,28 +4358,28 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>Brookfield Corporation</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>402.68</v>
+        <v>1023.62</v>
       </c>
       <c r="F127" t="n">
-        <v>82.45</v>
+        <v>45.55</v>
       </c>
       <c r="G127" t="n">
-        <v>89.37</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7.65%</t>
+          <t>7.96%</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4389,28 +4389,28 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Exelon Corporation</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>448.54</v>
+        <v>1394.52</v>
       </c>
       <c r="F128" t="n">
-        <v>44.41</v>
+        <v>235.1</v>
       </c>
       <c r="G128" t="n">
-        <v>48.09</v>
+        <v>255.44</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.83%</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4420,28 +4420,28 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Toyota Motor Corporation</t>
+          <t>BlackRock, Inc.</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2973.46</v>
+        <v>1736.05</v>
       </c>
       <c r="F129" t="n">
-        <v>227.07</v>
+        <v>1118.94</v>
       </c>
       <c r="G129" t="n">
-        <v>245.75</v>
+        <v>1214.03</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7.53%</t>
+          <t>7.81%</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4451,28 +4451,28 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>The TJX Companies, Inc.</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1641.25</v>
+        <v>3236.06</v>
       </c>
       <c r="F130" t="n">
-        <v>147.47</v>
+        <v>306.79</v>
       </c>
       <c r="G130" t="n">
-        <v>159.48</v>
+        <v>332.79</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7.28%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4482,28 +4482,28 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>Toyota Motor Corporation</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2845.27</v>
+        <v>2970.71</v>
       </c>
       <c r="F131" t="n">
-        <v>90.64</v>
+        <v>226.86</v>
       </c>
       <c r="G131" t="n">
-        <v>97.76000000000001</v>
+        <v>245.75</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7.28%</t>
+          <t>7.67%</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4513,28 +4513,28 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>American Express Company</t>
+          <t>Xcel Energy Inc.</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2494.74</v>
+        <v>449.93</v>
       </c>
       <c r="F132" t="n">
-        <v>358.5</v>
+        <v>76.06</v>
       </c>
       <c r="G132" t="n">
-        <v>386.63</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7.14%</t>
+          <t>7.56%</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4544,28 +4544,28 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>18609.31</v>
+        <v>3884.93</v>
       </c>
       <c r="F133" t="n">
-        <v>738.3099999999999</v>
+        <v>53.2</v>
       </c>
       <c r="G133" t="n">
-        <v>795.0599999999999</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.51%</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4575,28 +4575,28 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>BlackRock, Inc.</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1749.76</v>
+        <v>3941.44</v>
       </c>
       <c r="F134" t="n">
-        <v>1127.78</v>
+        <v>223.01</v>
       </c>
       <c r="G134" t="n">
-        <v>1214.03</v>
+        <v>241.12</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>7.47%</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4606,23 +4606,23 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Coca-Cola Europacific Partners PLC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1473.46</v>
+        <v>418.42</v>
       </c>
       <c r="F135" t="n">
-        <v>67.53</v>
+        <v>91.7</v>
       </c>
       <c r="G135" t="n">
-        <v>72.58</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6.52%</t>
+          <t>7.46%</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>25841.46</v>
+        <v>25581.69</v>
       </c>
       <c r="F136" t="n">
-        <v>241.73</v>
+        <v>239.3</v>
       </c>
       <c r="G136" t="n">
         <v>258.6</v>
@@ -4653,12 +4653,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>7.45%</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4668,28 +4668,28 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Brookfield Corporation</t>
+          <t>HCA Healthcare, Inc.</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1046.1</v>
+        <v>1142.52</v>
       </c>
       <c r="F137" t="n">
-        <v>46.55</v>
+        <v>488.27</v>
       </c>
       <c r="G137" t="n">
-        <v>49.57</v>
+        <v>527.55</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>7.44%</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4699,28 +4699,28 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1394.26</v>
+        <v>2840.56</v>
       </c>
       <c r="F138" t="n">
-        <v>126.93</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="G138" t="n">
-        <v>134.81</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4730,28 +4730,28 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2133.54</v>
+        <v>2921.01</v>
       </c>
       <c r="F139" t="n">
-        <v>455</v>
+        <v>233.46</v>
       </c>
       <c r="G139" t="n">
-        <v>483.05</v>
+        <v>251.84</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4761,28 +4761,28 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4105.6</v>
+        <v>1033.9</v>
       </c>
       <c r="F140" t="n">
-        <v>252.18</v>
+        <v>831.21</v>
       </c>
       <c r="G140" t="n">
-        <v>267.08</v>
+        <v>894.75</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5.34%</t>
+          <t>6.88%</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4792,28 +4792,28 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Exelon Corporation</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2898.9</v>
+        <v>452.27</v>
       </c>
       <c r="F141" t="n">
-        <v>182.4</v>
+        <v>44.78</v>
       </c>
       <c r="G141" t="n">
-        <v>192.68</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>6.49%</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4823,28 +4823,28 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>Altria Group, Inc.</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1495.72</v>
+        <v>1040.61</v>
       </c>
       <c r="F142" t="n">
-        <v>266.64</v>
+        <v>61.99</v>
       </c>
       <c r="G142" t="n">
-        <v>281.36</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>6.47%</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4854,28 +4854,28 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Strive Asset Management, LLC</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>2558.32</v>
       </c>
       <c r="F143" t="n">
-        <v>96.23999999999999</v>
+        <v>322.32</v>
       </c>
       <c r="G143" t="n">
-        <v>101.35</v>
+        <v>344.6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4.97%</t>
+          <t>6.42%</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SCCO</t>
+          <t>SATA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4885,28 +4885,28 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Southern Copper Corporation</t>
+          <t>Strive Asset Management, LLC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1703.15</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>207.93</v>
+        <v>94.84</v>
       </c>
       <c r="G144" t="n">
-        <v>218.81</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation</t>
+          <t>Rio Tinto Group</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2890.58</v>
+        <v>1816.81</v>
       </c>
       <c r="F145" t="n">
-        <v>309.24</v>
+        <v>91.03</v>
       </c>
       <c r="G145" t="n">
-        <v>324.9</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4.53%</t>
+          <t>6.06%</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4947,28 +4947,28 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc.</t>
+          <t>The TJX Companies, Inc.</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2845.94</v>
+        <v>1667.29</v>
       </c>
       <c r="F146" t="n">
-        <v>940.12</v>
+        <v>149.81</v>
       </c>
       <c r="G146" t="n">
-        <v>984.7</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>5.91%</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4978,28 +4978,28 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>American Electric Power Company, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>638.09</v>
+        <v>17144.51</v>
       </c>
       <c r="F147" t="n">
-        <v>119.21</v>
+        <v>330.56</v>
       </c>
       <c r="G147" t="n">
-        <v>124.8</v>
+        <v>351.33</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>5.81%</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5009,28 +5009,28 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Ross Stores, Inc.</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>606.55</v>
+        <v>1491.57</v>
       </c>
       <c r="F148" t="n">
-        <v>186.5</v>
+        <v>68.36</v>
       </c>
       <c r="G148" t="n">
-        <v>194.92</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5040,59 +5040,59 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Agnico Eagle Mines Limited</t>
+          <t>International Business Machines Corporation</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1081.96</v>
+        <v>2866.83</v>
       </c>
       <c r="F149" t="n">
-        <v>215.51</v>
+        <v>306.7</v>
       </c>
       <c r="G149" t="n">
-        <v>225</v>
+        <v>324.9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TBB</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1376.54</v>
+        <v>538.55</v>
       </c>
       <c r="F150" t="n">
-        <v>22.42</v>
+        <v>1124.15</v>
       </c>
       <c r="G150" t="n">
-        <v>23.41</v>
+        <v>1188.66</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5102,28 +5102,28 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>AstraZeneca PLC</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2870.81</v>
+        <v>2142.78</v>
       </c>
       <c r="F151" t="n">
-        <v>92.59</v>
+        <v>456.97</v>
       </c>
       <c r="G151" t="n">
-        <v>96.51000000000001</v>
+        <v>483.05</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5133,28 +5133,28 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>782.01</v>
+        <v>2905.26</v>
       </c>
       <c r="F152" t="n">
-        <v>80.04000000000001</v>
+        <v>182.8</v>
       </c>
       <c r="G152" t="n">
-        <v>83.23999999999999</v>
+        <v>192.68</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>5.08%</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5164,28 +5164,28 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1853.95</v>
+        <v>1498.08</v>
       </c>
       <c r="F153" t="n">
-        <v>72.17</v>
+        <v>267.06</v>
       </c>
       <c r="G153" t="n">
-        <v>74.98</v>
+        <v>281.36</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.01%</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5195,28 +5195,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Mitsubishi UFJ Financial Group, Inc.</t>
+          <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2084.5</v>
+        <v>2831.68</v>
       </c>
       <c r="F154" t="n">
-        <v>18.2</v>
+        <v>935.41</v>
       </c>
       <c r="G154" t="n">
-        <v>18.9</v>
+        <v>984.7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5226,28 +5226,28 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1453.34</v>
+        <v>2335.43</v>
       </c>
       <c r="F155" t="n">
-        <v>622.51</v>
+        <v>166.23</v>
       </c>
       <c r="G155" t="n">
-        <v>645.67</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>4.77%</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5257,28 +5257,28 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>Marriott International, Inc.</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>9360.92</v>
+        <v>855.91</v>
       </c>
       <c r="F156" t="n">
-        <v>117.41</v>
+        <v>315.3</v>
       </c>
       <c r="G156" t="n">
-        <v>121.62</v>
+        <v>331.09</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5288,28 +5288,28 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Marriott International, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>868.04</v>
+        <v>5523.34</v>
       </c>
       <c r="F157" t="n">
-        <v>319.77</v>
+        <v>1423</v>
       </c>
       <c r="G157" t="n">
-        <v>331.09</v>
+        <v>1493.48</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5319,28 +5319,28 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Mitsubishi UFJ Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1220.67</v>
+        <v>2067.32</v>
       </c>
       <c r="F158" t="n">
-        <v>306.17</v>
+        <v>18.05</v>
       </c>
       <c r="G158" t="n">
-        <v>316.94</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5350,28 +5350,28 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>UBS Group AG</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>17610.78</v>
+        <v>1485.79</v>
       </c>
       <c r="F159" t="n">
-        <v>339.55</v>
+        <v>47.15</v>
       </c>
       <c r="G159" t="n">
-        <v>351.33</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>4.21%</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5381,28 +5381,28 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Baker Hughes Company</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2371.25</v>
+        <v>552.99</v>
       </c>
       <c r="F160" t="n">
-        <v>168.78</v>
+        <v>56.04</v>
       </c>
       <c r="G160" t="n">
-        <v>174.61</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>TBB</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5412,28 +5412,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Baker Hughes Company</t>
+          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>559.8</v>
+        <v>1378.99</v>
       </c>
       <c r="F161" t="n">
-        <v>56.73</v>
+        <v>22.46</v>
       </c>
       <c r="G161" t="n">
-        <v>58.47</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5443,28 +5443,28 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>American Electric Power Company, Inc.</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1846.67</v>
+        <v>641.11</v>
       </c>
       <c r="F162" t="n">
-        <v>342.94</v>
+        <v>119.78</v>
       </c>
       <c r="G162" t="n">
-        <v>353.25</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CCZ</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5474,28 +5474,28 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Comcast Holdings Corp.</t>
+          <t>AstraZeneca PLC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>615.7</v>
+        <v>2876.4</v>
       </c>
       <c r="F163" t="n">
-        <v>65</v>
+        <v>92.77</v>
       </c>
       <c r="G163" t="n">
-        <v>66.90000000000001</v>
+        <v>96.51000000000001</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>3.41%</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5505,28 +5505,28 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>706</v>
+        <v>1970.79</v>
       </c>
       <c r="F164" t="n">
-        <v>37.87</v>
+        <v>726.37</v>
       </c>
       <c r="G164" t="n">
-        <v>38.95</v>
+        <v>752.02</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>ENB</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5536,28 +5536,28 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
+          <t>Enbridge Inc.</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1446.07</v>
+        <v>1066.18</v>
       </c>
       <c r="F165" t="n">
-        <v>25.44</v>
+        <v>48.84</v>
       </c>
       <c r="G165" t="n">
-        <v>26.14</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5567,28 +5567,28 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2679.94</v>
+        <v>3079.59</v>
       </c>
       <c r="F166" t="n">
-        <v>199.88</v>
+        <v>657.36</v>
       </c>
       <c r="G166" t="n">
-        <v>205.36</v>
+        <v>679.99</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ENB</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5598,28 +5598,28 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Enbridge Inc.</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1074.91</v>
+        <v>1840.96</v>
       </c>
       <c r="F167" t="n">
-        <v>49.24</v>
+        <v>341.88</v>
       </c>
       <c r="G167" t="n">
-        <v>50.54</v>
+        <v>353.25</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5629,121 +5629,121 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Ross Stores, Inc.</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5648.17</v>
+        <v>613.54</v>
       </c>
       <c r="F168" t="n">
-        <v>1455.16</v>
+        <v>188.65</v>
       </c>
       <c r="G168" t="n">
-        <v>1493.48</v>
+        <v>194.92</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings plc</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>972.95</v>
+        <v>703.95</v>
       </c>
       <c r="F169" t="n">
-        <v>446.57</v>
+        <v>37.76</v>
       </c>
       <c r="G169" t="n">
-        <v>457.84</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>954.38</v>
+        <v>1574.76</v>
       </c>
       <c r="F170" t="n">
-        <v>278.41</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="G170" t="n">
-        <v>285.42</v>
+        <v>96.44</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FER</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Ferrovial SE</t>
+          <t>Parker-Hannifin Corporation</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>486.98</v>
+        <v>1184.25</v>
       </c>
       <c r="F171" t="n">
-        <v>68.11</v>
+        <v>935.84</v>
       </c>
       <c r="G171" t="n">
-        <v>69.81999999999999</v>
+        <v>965</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5753,28 +5753,28 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc.</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3098.84</v>
+        <v>789.04</v>
       </c>
       <c r="F172" t="n">
-        <v>78.43000000000001</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="G172" t="n">
-        <v>80.39</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5784,28 +5784,28 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>UBS Group AG</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1517.62</v>
+        <v>1958.54</v>
       </c>
       <c r="F173" t="n">
-        <v>48.16</v>
+        <v>215.55</v>
       </c>
       <c r="G173" t="n">
-        <v>49.36</v>
+        <v>222</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>CCZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5815,28 +5815,28 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Novartis AG</t>
+          <t>Comcast Holdings Corp.</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2857.27</v>
+        <v>615.7</v>
       </c>
       <c r="F174" t="n">
-        <v>148.91</v>
+        <v>65</v>
       </c>
       <c r="G174" t="n">
-        <v>152.48</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5846,28 +5846,28 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation</t>
+          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1878.21</v>
+        <v>1444.93</v>
       </c>
       <c r="F175" t="n">
-        <v>103.47</v>
+        <v>25.42</v>
       </c>
       <c r="G175" t="n">
-        <v>105.81</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5877,59 +5877,59 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc.</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2769.1</v>
+        <v>1522.24</v>
       </c>
       <c r="F176" t="n">
-        <v>177.89</v>
+        <v>310.88</v>
       </c>
       <c r="G176" t="n">
-        <v>181.91</v>
+        <v>319.26</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>FER</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Ferrovial SE</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3116.51</v>
+        <v>485.96</v>
       </c>
       <c r="F177" t="n">
-        <v>665.24</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="G177" t="n">
-        <v>679.99</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5939,28 +5939,28 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Cisco Systems, Inc.</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3449.17</v>
+        <v>3094.5</v>
       </c>
       <c r="F178" t="n">
-        <v>171.19</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="G178" t="n">
-        <v>174.92</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5970,28 +5970,28 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Rio Tinto Group</t>
+          <t>Novartis AG</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1898.64</v>
+        <v>2852.86</v>
       </c>
       <c r="F179" t="n">
-        <v>95.13</v>
+        <v>148.68</v>
       </c>
       <c r="G179" t="n">
-        <v>97.11</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6001,28 +6001,28 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4904.86</v>
+        <v>1234.19</v>
       </c>
       <c r="F180" t="n">
-        <v>435.79</v>
+        <v>309.56</v>
       </c>
       <c r="G180" t="n">
-        <v>444.71</v>
+        <v>316.94</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6032,28 +6032,28 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>McDonald's Corporation</t>
+          <t>Banco Santander, S.A.</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2251.49</v>
+        <v>1885.41</v>
       </c>
       <c r="F181" t="n">
-        <v>315.51</v>
+        <v>12.75</v>
       </c>
       <c r="G181" t="n">
-        <v>321.79</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ITUB</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6063,28 +6063,28 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Itaú Unibanco Holding S.A.</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>984.67</v>
+        <v>2694.01</v>
       </c>
       <c r="F182" t="n">
-        <v>8.93</v>
+        <v>200.93</v>
       </c>
       <c r="G182" t="n">
-        <v>9.1</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6094,28 +6094,28 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Banco Santander, S.A.</t>
+          <t>McDonald's Corporation</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1894.28</v>
+        <v>2247.85</v>
       </c>
       <c r="F183" t="n">
-        <v>12.81</v>
+        <v>315</v>
       </c>
       <c r="G183" t="n">
-        <v>13.05</v>
+        <v>321.79</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6125,28 +6125,28 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>Walmart Inc.</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1952.91</v>
+        <v>9498.85</v>
       </c>
       <c r="F184" t="n">
-        <v>717.39</v>
+        <v>119.14</v>
       </c>
       <c r="G184" t="n">
-        <v>730.46</v>
+        <v>121.62</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6156,28 +6156,28 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Parker-Hannifin Corporation</t>
+          <t>PACCAR Inc</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1200.14</v>
+        <v>645.77</v>
       </c>
       <c r="F185" t="n">
-        <v>948.4</v>
+        <v>122.91</v>
       </c>
       <c r="G185" t="n">
-        <v>965</v>
+        <v>125.36</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6187,28 +6187,28 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>PACCAR Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>647.92</v>
+        <v>1551.18</v>
       </c>
       <c r="F186" t="n">
-        <v>123.32</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G186" t="n">
-        <v>125.36</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6218,28 +6218,28 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>The Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1599.02</v>
+        <v>1886.38</v>
       </c>
       <c r="F187" t="n">
-        <v>94.93000000000001</v>
+        <v>103.92</v>
       </c>
       <c r="G187" t="n">
-        <v>96.44</v>
+        <v>105.81</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6249,28 +6249,28 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>GSK plc</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1023.86</v>
+        <v>1467.57</v>
       </c>
       <c r="F188" t="n">
-        <v>50.66</v>
+        <v>634.22</v>
       </c>
       <c r="G188" t="n">
-        <v>51.46</v>
+        <v>645.67</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6280,28 +6280,28 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc.</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1731.55</v>
+        <v>1431.27</v>
       </c>
       <c r="F189" t="n">
-        <v>139.55</v>
+        <v>528</v>
       </c>
       <c r="G189" t="n">
-        <v>141.71</v>
+        <v>537.26</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6311,28 +6311,28 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Shell plc</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1556.1</v>
+        <v>2179.5</v>
       </c>
       <c r="F190" t="n">
-        <v>72.63</v>
+        <v>77.03</v>
       </c>
       <c r="G190" t="n">
-        <v>73.75</v>
+        <v>78.17</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6342,28 +6342,28 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>NextEra Energy, Inc.</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1989.61</v>
+        <v>1830.61</v>
       </c>
       <c r="F191" t="n">
-        <v>218.97</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G191" t="n">
-        <v>222</v>
+        <v>89.19</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6373,28 +6373,28 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Philip Morris International Inc.</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1436.88</v>
+        <v>2793.23</v>
       </c>
       <c r="F192" t="n">
-        <v>530.0700000000001</v>
+        <v>179.44</v>
       </c>
       <c r="G192" t="n">
-        <v>537.26</v>
+        <v>181.91</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6404,17 +6404,17 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corporation</t>
+          <t>Verizon Communications Inc.</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5990.29</v>
+        <v>1877.15</v>
       </c>
       <c r="F193" t="n">
-        <v>140.51</v>
+        <v>44.52</v>
       </c>
       <c r="G193" t="n">
-        <v>142.34</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="194">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6435,28 +6435,28 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>3129.5</v>
+        <v>40938.97</v>
       </c>
       <c r="F194" t="n">
-        <v>248.17</v>
+        <v>338</v>
       </c>
       <c r="G194" t="n">
-        <v>251.32</v>
+        <v>342.29</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6466,28 +6466,28 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>40969.25</v>
+        <v>5475.12</v>
       </c>
       <c r="F195" t="n">
-        <v>338.25</v>
+        <v>227.25</v>
       </c>
       <c r="G195" t="n">
-        <v>342.26</v>
+        <v>230</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6497,28 +6497,28 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>HSBC Holdings plc</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5476.09</v>
+        <v>3021.55</v>
       </c>
       <c r="F196" t="n">
-        <v>227.29</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="G196" t="n">
-        <v>229.98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6528,28 +6528,28 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NextEra Energy, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1836.45</v>
+        <v>40866.78</v>
       </c>
       <c r="F197" t="n">
-        <v>88.18000000000001</v>
+        <v>338.53</v>
       </c>
       <c r="G197" t="n">
-        <v>89.19</v>
+        <v>342.29</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6559,28 +6559,28 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>CME Group Inc.</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>40882.47</v>
+        <v>1039.21</v>
       </c>
       <c r="F198" t="n">
-        <v>338.66</v>
+        <v>289.06</v>
       </c>
       <c r="G198" t="n">
-        <v>342.29</v>
+        <v>291.76</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6590,28 +6590,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>British American Tobacco p.l.c.</t>
+          <t>Honeywell International Inc.</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1306.94</v>
+        <v>1533.19</v>
       </c>
       <c r="F199" t="n">
-        <v>60.22</v>
+        <v>227.52</v>
       </c>
       <c r="G199" t="n">
-        <v>60.82</v>
+        <v>229.59</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6621,28 +6621,28 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>Exxon Mobil Corporation</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2719.26</v>
+        <v>6028.23</v>
       </c>
       <c r="F200" t="n">
-        <v>341.34</v>
+        <v>141.4</v>
       </c>
       <c r="G200" t="n">
-        <v>344.6</v>
+        <v>142.34</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6652,28 +6652,28 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Shell plc</t>
+          <t>Electronic Arts Inc.</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2192.36</v>
+        <v>510.02</v>
       </c>
       <c r="F201" t="n">
-        <v>77.47</v>
+        <v>203.92</v>
       </c>
       <c r="G201" t="n">
-        <v>78.17</v>
+        <v>204.89</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6683,28 +6683,28 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>British American Tobacco p.l.c.</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3160.18</v>
+        <v>1316.78</v>
       </c>
       <c r="F202" t="n">
-        <v>73.43000000000001</v>
+        <v>60.68</v>
       </c>
       <c r="G202" t="n">
-        <v>74.08</v>
+        <v>60.82</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6714,28 +6714,28 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>CME Group Inc.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1041.97</v>
+        <v>3564.22</v>
       </c>
       <c r="F203" t="n">
-        <v>289.83</v>
+        <v>176.9</v>
       </c>
       <c r="G203" t="n">
-        <v>291.76</v>
+        <v>177.3</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6745,28 +6745,28 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2218.5</v>
+        <v>1761.33</v>
       </c>
       <c r="F204" t="n">
-        <v>1684.71</v>
+        <v>141.95</v>
       </c>
       <c r="G204" t="n">
-        <v>1693.35</v>
+        <v>142.2</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6776,28 +6776,28 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>3039.74</v>
+        <v>1042.86</v>
       </c>
       <c r="F205" t="n">
-        <v>88.54000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="G205" t="n">
-        <v>88.98999999999999</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6807,141 +6807,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Electronic Arts Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>510.09</v>
+        <v>3219.57</v>
       </c>
       <c r="F206" t="n">
-        <v>203.95</v>
+        <v>74.81</v>
       </c>
       <c r="G206" t="n">
-        <v>204.89</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>常规</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Honeywell International Inc.</t>
-        </is>
-      </c>
-      <c r="E207" t="n">
-        <v>1531.3</v>
-      </c>
-      <c r="F207" t="n">
-        <v>227.24</v>
-      </c>
-      <c r="G207" t="n">
-        <v>227.86</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>0.15%</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>MPWR</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>新纳入</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Monolithic Power Systems, Inc.</t>
-        </is>
-      </c>
-      <c r="E208" t="n">
-        <v>566.8099999999999</v>
-      </c>
-      <c r="F208" t="n">
-        <v>1183.15</v>
-      </c>
-      <c r="G208" t="n">
-        <v>1184.87</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>0.14%</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>BMO</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>常规</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Bank of Montreal</t>
-        </is>
-      </c>
-      <c r="E209" t="n">
-        <v>1016.34</v>
-      </c>
-      <c r="F209" t="n">
-        <v>141.4</v>
-      </c>
-      <c r="G209" t="n">
-        <v>141.6</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>0.13%</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>ADI</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>常规</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Analog Devices, Inc.</t>
-        </is>
-      </c>
-      <c r="E210" t="n">
-        <v>1560.53</v>
-      </c>
-      <c r="F210" t="n">
-        <v>318.7</v>
-      </c>
-      <c r="G210" t="n">
-        <v>319.11</v>
+        <v>74.89</v>
       </c>
     </row>
   </sheetData>

--- a/美股回撤分析报告.xlsx
+++ b/美股回撤分析报告.xlsx
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>281.54</v>
+        <v>266.74</v>
       </c>
       <c r="F4" t="n">
         <v>206.12</v>
@@ -1978,7 +1978,7 @@
         <v>889.85</v>
       </c>
       <c r="F50" t="n">
-        <v>465.11</v>
+        <v>465.12</v>
       </c>
       <c r="G50" t="n">
         <v>651.73</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1233.48</v>
+        <v>1210.44</v>
       </c>
       <c r="F72" t="n">
         <v>176.97</v>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1660.75</v>
+        <v>1660.88</v>
       </c>
       <c r="F82" t="n">
         <v>32.38</v>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1047.44</v>
+        <v>1047.55</v>
       </c>
       <c r="F90" t="n">
         <v>29.29</v>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6210.99</v>
+        <v>6205.01</v>
       </c>
       <c r="F95" t="n">
         <v>321.83</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3546.46</v>
+        <v>3552.15</v>
       </c>
       <c r="F101" t="n">
         <v>151.77</v>
@@ -3661,63 +3661,63 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>12.44%</t>
+          <t>12.33%</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4174.31</v>
+        <v>848.37</v>
       </c>
       <c r="F105" t="n">
-        <v>940.25</v>
+        <v>250.23</v>
       </c>
       <c r="G105" t="n">
-        <v>1073.82</v>
+        <v>285.42</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12.33%</t>
+          <t>12.32%</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>857.78</v>
+        <v>4174.31</v>
       </c>
       <c r="F106" t="n">
-        <v>250.23</v>
+        <v>940.25</v>
       </c>
       <c r="G106" t="n">
-        <v>285.42</v>
+        <v>1072.35</v>
       </c>
     </row>
     <row r="107">
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>38341.68</v>
+        <v>38138.18</v>
       </c>
       <c r="F112" t="n">
         <v>259.48</v>
@@ -4126,7 +4126,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8.91%</t>
+          <t>8.92%</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4151,7 +4151,7 @@
         <v>414.88</v>
       </c>
       <c r="G120" t="n">
-        <v>455.48</v>
+        <v>455.5</v>
       </c>
     </row>
     <row r="121">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2450.69</v>
+        <v>2425.93</v>
       </c>
       <c r="F121" t="n">
         <v>352.17</v>
@@ -4715,7 +4715,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.31%</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4734,13 +4734,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2921.01</v>
+        <v>2932.33</v>
       </c>
       <c r="F139" t="n">
         <v>233.46</v>
       </c>
       <c r="G139" t="n">
-        <v>251.84</v>
+        <v>251.87</v>
       </c>
     </row>
     <row r="140">
@@ -4870,12 +4870,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4885,28 +4885,28 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Strive Asset Management, LLC</t>
+          <t>Rio Tinto Group</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1816.81</v>
       </c>
       <c r="F144" t="n">
-        <v>94.84</v>
+        <v>91.03</v>
       </c>
       <c r="G144" t="n">
-        <v>101.35</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6.26%</t>
+          <t>6.06%</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Rio Tinto Group</t>
+          <t>The TJX Companies, Inc.</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1816.81</v>
+        <v>1667.29</v>
       </c>
       <c r="F145" t="n">
-        <v>91.03</v>
+        <v>149.81</v>
       </c>
       <c r="G145" t="n">
-        <v>97.11</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>6.06%</t>
+          <t>5.91%</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4947,28 +4947,28 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>The TJX Companies, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1667.29</v>
+        <v>17144.51</v>
       </c>
       <c r="F146" t="n">
-        <v>149.81</v>
+        <v>330.56</v>
       </c>
       <c r="G146" t="n">
-        <v>159.48</v>
+        <v>351.33</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>5.81%</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4978,28 +4978,28 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>17144.51</v>
+        <v>1491.57</v>
       </c>
       <c r="F147" t="n">
-        <v>330.56</v>
+        <v>68.36</v>
       </c>
       <c r="G147" t="n">
-        <v>351.33</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5009,79 +5009,79 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>International Business Machines Corporation</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1491.57</v>
+        <v>2866.83</v>
       </c>
       <c r="F148" t="n">
-        <v>68.36</v>
+        <v>306.7</v>
       </c>
       <c r="G148" t="n">
-        <v>72.58</v>
+        <v>324.9</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2866.83</v>
+        <v>538.55</v>
       </c>
       <c r="F149" t="n">
-        <v>306.7</v>
+        <v>1124.15</v>
       </c>
       <c r="G149" t="n">
-        <v>324.9</v>
+        <v>1188.66</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.42%</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>SATA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>Strive Asset Management, LLC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>538.55</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>1124.15</v>
+        <v>94.84</v>
       </c>
       <c r="G150" t="n">
-        <v>1188.66</v>
+        <v>100.27</v>
       </c>
     </row>
     <row r="151">
@@ -5118,12 +5118,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.08%</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5133,28 +5133,28 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2905.26</v>
+        <v>1498.08</v>
       </c>
       <c r="F152" t="n">
-        <v>182.8</v>
+        <v>267.06</v>
       </c>
       <c r="G152" t="n">
-        <v>192.68</v>
+        <v>281.36</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>5.01%</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5164,28 +5164,28 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1498.08</v>
+        <v>2831.68</v>
       </c>
       <c r="F153" t="n">
-        <v>267.06</v>
+        <v>935.41</v>
       </c>
       <c r="G153" t="n">
-        <v>281.36</v>
+        <v>984.7</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5195,28 +5195,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc.</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2831.68</v>
+        <v>2335.43</v>
       </c>
       <c r="F154" t="n">
-        <v>935.41</v>
+        <v>166.23</v>
       </c>
       <c r="G154" t="n">
-        <v>984.7</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.77%</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5226,28 +5226,28 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Marriott International, Inc.</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2335.43</v>
+        <v>855.91</v>
       </c>
       <c r="F155" t="n">
-        <v>166.23</v>
+        <v>315.3</v>
       </c>
       <c r="G155" t="n">
-        <v>174.61</v>
+        <v>331.09</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4.77%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5257,28 +5257,28 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Marriott International, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>855.91</v>
+        <v>5523.34</v>
       </c>
       <c r="F156" t="n">
-        <v>315.3</v>
+        <v>1423</v>
       </c>
       <c r="G156" t="n">
-        <v>331.09</v>
+        <v>1493.48</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5288,17 +5288,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5523.34</v>
+        <v>2905.26</v>
       </c>
       <c r="F157" t="n">
-        <v>1423</v>
+        <v>182.8</v>
       </c>
       <c r="G157" t="n">
-        <v>1493.48</v>
+        <v>191.62</v>
       </c>
     </row>
     <row r="158">
@@ -5428,7 +5428,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>4.02%</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1184.25</v>
+        <v>1181.18</v>
       </c>
       <c r="F171" t="n">
         <v>935.84</v>
@@ -5769,12 +5769,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>CCZ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5784,28 +5784,28 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>Comcast Holdings Corp.</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1958.54</v>
+        <v>615.7</v>
       </c>
       <c r="F173" t="n">
-        <v>215.55</v>
+        <v>65</v>
       </c>
       <c r="G173" t="n">
-        <v>222</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CCZ</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5815,28 +5815,28 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Comcast Holdings Corp.</t>
+          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>615.7</v>
+        <v>1444.93</v>
       </c>
       <c r="F174" t="n">
-        <v>65</v>
+        <v>25.42</v>
       </c>
       <c r="G174" t="n">
-        <v>66.90000000000001</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5846,90 +5846,90 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1444.93</v>
+        <v>1522.24</v>
       </c>
       <c r="F175" t="n">
-        <v>25.42</v>
+        <v>310.88</v>
       </c>
       <c r="G175" t="n">
-        <v>26.14</v>
+        <v>319.26</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>FER</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Ferrovial SE</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1522.24</v>
+        <v>485.96</v>
       </c>
       <c r="F176" t="n">
-        <v>310.88</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="G176" t="n">
-        <v>319.26</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FER</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Ferrovial SE</t>
+          <t>Cisco Systems, Inc.</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>485.96</v>
+        <v>3094.5</v>
       </c>
       <c r="F177" t="n">
-        <v>67.98999999999999</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="G177" t="n">
-        <v>69.81999999999999</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5939,28 +5939,28 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc.</t>
+          <t>Novartis AG</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3094.5</v>
+        <v>2852.86</v>
       </c>
       <c r="F178" t="n">
-        <v>78.31999999999999</v>
+        <v>148.68</v>
       </c>
       <c r="G178" t="n">
-        <v>80.39</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5970,28 +5970,28 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Novartis AG</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2852.86</v>
+        <v>1234.19</v>
       </c>
       <c r="F179" t="n">
-        <v>148.68</v>
+        <v>309.56</v>
       </c>
       <c r="G179" t="n">
-        <v>152.48</v>
+        <v>316.94</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6001,28 +6001,28 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Banco Santander, S.A.</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1234.19</v>
+        <v>1885.41</v>
       </c>
       <c r="F180" t="n">
-        <v>309.56</v>
+        <v>12.75</v>
       </c>
       <c r="G180" t="n">
-        <v>316.94</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6032,17 +6032,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Banco Santander, S.A.</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1885.41</v>
+        <v>1958.54</v>
       </c>
       <c r="F181" t="n">
-        <v>12.75</v>
+        <v>215.55</v>
       </c>
       <c r="G181" t="n">
-        <v>13.05</v>
+        <v>220.56</v>
       </c>
     </row>
     <row r="182">
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2179.5</v>
+        <v>2178.98</v>
       </c>
       <c r="F190" t="n">
         <v>77.03</v>
@@ -6408,7 +6408,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1877.15</v>
+        <v>1877.41</v>
       </c>
       <c r="F193" t="n">
         <v>44.52</v>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6028.23</v>
+        <v>5963.07</v>
       </c>
       <c r="F200" t="n">
         <v>141.4</v>
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1316.78</v>
+        <v>1316.7</v>
       </c>
       <c r="F202" t="n">
         <v>60.68</v>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3564.22</v>
+        <v>3536.86</v>
       </c>
       <c r="F203" t="n">
         <v>176.9</v>
@@ -6792,7 +6792,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6817,7 +6817,7 @@
         <v>74.81</v>
       </c>
       <c r="G206" t="n">
-        <v>74.89</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/美股回撤分析报告.xlsx
+++ b/美股回撤分析报告.xlsx
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3541.55</v>
+        <v>3541.85</v>
       </c>
       <c r="F33" t="n">
         <v>83.48999999999999</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>370.2</v>
+        <v>370.27</v>
       </c>
       <c r="F41" t="n">
         <v>103.13</v>
@@ -6439,7 +6439,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>40938.97</v>
+        <v>40967.19</v>
       </c>
       <c r="F194" t="n">
         <v>338</v>

--- a/美股回撤分析报告.xlsx
+++ b/美股回撤分析报告.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>82.97%</t>
+          <t>83.09%</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>503.39</v>
+        <v>499.95</v>
       </c>
       <c r="F2" t="n">
-        <v>52.69</v>
+        <v>52.33</v>
       </c>
       <c r="G2" t="n">
         <v>309.44</v>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>75.54%</t>
+          <t>76.47%</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>311.09</v>
+        <v>299.29</v>
       </c>
       <c r="F3" t="n">
-        <v>118.18</v>
+        <v>113.7</v>
       </c>
       <c r="G3" t="n">
         <v>483.13</v>
@@ -530,69 +530,69 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>75.03%</t>
+          <t>74.29%</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Charter Communications, Inc.</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>266.74</v>
+        <v>404.01</v>
       </c>
       <c r="F4" t="n">
-        <v>206.12</v>
+        <v>139.63</v>
       </c>
       <c r="G4" t="n">
-        <v>825.62</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>72.43%</t>
+          <t>74.13%</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Charter Communications, Inc.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>433.18</v>
+        <v>276.43</v>
       </c>
       <c r="F5" t="n">
-        <v>149.71</v>
+        <v>213.61</v>
       </c>
       <c r="G5" t="n">
-        <v>543</v>
+        <v>825.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>69.74%</t>
+          <t>69.61%</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2070.36</v>
+        <v>2079.66</v>
       </c>
       <c r="F6" t="n">
-        <v>115.71</v>
+        <v>116.23</v>
       </c>
       <c r="G6" t="n">
         <v>382.43</v>
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>64.76%</t>
+          <t>64.78%</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>682.85</v>
+        <v>682.35</v>
       </c>
       <c r="F7" t="n">
-        <v>27.54</v>
+        <v>27.52</v>
       </c>
       <c r="G7" t="n">
         <v>78.14</v>
@@ -654,7 +654,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>63.38%</t>
+          <t>63.75%</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>281</v>
+        <v>278.16</v>
       </c>
       <c r="F8" t="n">
-        <v>23.74</v>
+        <v>23.5</v>
       </c>
       <c r="G8" t="n">
         <v>64.84</v>
@@ -685,7 +685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>58.63%</t>
+          <t>58.97%</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2640.76</v>
+        <v>2618.54</v>
       </c>
       <c r="F9" t="n">
-        <v>59.43</v>
+        <v>58.93</v>
       </c>
       <c r="G9" t="n">
         <v>143.64</v>
@@ -716,7 +716,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>58.08%</t>
+          <t>58.06%</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1227.54</v>
+        <v>1228.09</v>
       </c>
       <c r="F10" t="n">
-        <v>293.25</v>
+        <v>293.38</v>
       </c>
       <c r="G10" t="n">
         <v>699.54</v>
@@ -747,7 +747,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.01%</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>286.43</v>
+        <v>284.43</v>
       </c>
       <c r="F11" t="n">
-        <v>73.04000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="G11" t="n">
         <v>164.86</v>
@@ -778,12 +778,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>53.21%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -793,28 +793,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UnitedHealth Group Incorporated</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2599.12</v>
+        <v>4598.73</v>
       </c>
       <c r="F12" t="n">
-        <v>286.93</v>
+        <v>160.06</v>
       </c>
       <c r="G12" t="n">
-        <v>613.22</v>
+        <v>344.21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>52.47%</t>
+          <t>53.43%</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -824,28 +824,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc.</t>
+          <t>UnitedHealth Group Incorporated</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1434.55</v>
+        <v>2586.98</v>
       </c>
       <c r="F13" t="n">
-        <v>101.05</v>
+        <v>285.59</v>
       </c>
       <c r="G13" t="n">
-        <v>212.6</v>
+        <v>613.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>52.19%</t>
+          <t>51.34%</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -855,23 +855,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>PDD Holdings Inc.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4728.6</v>
+        <v>1468.62</v>
       </c>
       <c r="F14" t="n">
-        <v>164.58</v>
+        <v>103.45</v>
       </c>
       <c r="G14" t="n">
-        <v>344.21</v>
+        <v>212.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51.17%</t>
+          <t>50.75%</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1234.62</v>
+        <v>1245.07</v>
       </c>
       <c r="F15" t="n">
-        <v>117.01</v>
+        <v>118</v>
       </c>
       <c r="G15" t="n">
         <v>239.62</v>
@@ -902,7 +902,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>48.95%</t>
+          <t>49.69%</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>500.08</v>
+        <v>492.85</v>
       </c>
       <c r="F16" t="n">
-        <v>110.63</v>
+        <v>109.03</v>
       </c>
       <c r="G16" t="n">
         <v>216.72</v>
@@ -933,43 +933,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>46.82%</t>
+          <t>48.08%</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zscaler, Inc.</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>318.96</v>
+        <v>365.4</v>
       </c>
       <c r="F17" t="n">
-        <v>200.01</v>
+        <v>459.99</v>
       </c>
       <c r="G17" t="n">
-        <v>376.11</v>
+        <v>885.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.34%</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -979,28 +979,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503.3</v>
+        <v>1864.73</v>
       </c>
       <c r="F18" t="n">
-        <v>26.44</v>
+        <v>104.45</v>
       </c>
       <c r="G18" t="n">
-        <v>49.42</v>
+        <v>198.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>46.34%</t>
+          <t>46.66%</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1010,59 +1010,59 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The Boeing Company</t>
+          <t>Zscaler, Inc.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1830.19</v>
+        <v>319.92</v>
       </c>
       <c r="F19" t="n">
-        <v>233.72</v>
+        <v>200.61</v>
       </c>
       <c r="G19" t="n">
-        <v>435.56</v>
+        <v>376.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45.41%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>The Boeing Company</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>384.14</v>
+        <v>1824.71</v>
       </c>
       <c r="F20" t="n">
-        <v>483.58</v>
+        <v>233.02</v>
       </c>
       <c r="G20" t="n">
-        <v>885.92</v>
+        <v>435.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>44.18%</t>
+          <t>46.05%</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1117.87</v>
+        <v>1515.81</v>
       </c>
       <c r="F21" t="n">
-        <v>105.36</v>
+        <v>26.66</v>
       </c>
       <c r="G21" t="n">
-        <v>188.75</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>44.09%</t>
+          <t>44.47%</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4047.95</v>
+        <v>4020.02</v>
       </c>
       <c r="F22" t="n">
-        <v>169.56</v>
+        <v>168.39</v>
       </c>
       <c r="G22" t="n">
         <v>303.26</v>
@@ -1119,7 +1119,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>43.58%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>468.93</v>
+        <v>462.92</v>
       </c>
       <c r="F23" t="n">
-        <v>175.63</v>
+        <v>173.38</v>
       </c>
       <c r="G23" t="n">
         <v>311.28</v>
@@ -1150,12 +1150,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43.13%</t>
+          <t>43.35%</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1165,23 +1165,23 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2013.81</v>
+        <v>1134.53</v>
       </c>
       <c r="F24" t="n">
-        <v>112.8</v>
+        <v>106.93</v>
       </c>
       <c r="G24" t="n">
-        <v>198.35</v>
+        <v>188.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>42.03%</t>
+          <t>42.43%</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2021</v>
+        <v>2006.91</v>
       </c>
       <c r="F25" t="n">
-        <v>212.29</v>
+        <v>210.81</v>
       </c>
       <c r="G25" t="n">
         <v>366.19</v>
@@ -1212,12 +1212,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>41.18%</t>
+          <t>41.36%</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1227,28 +1227,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Airbnb, Inc.</t>
+          <t>Comcast Corporation</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>792.05</v>
+        <v>1166.19</v>
       </c>
       <c r="F26" t="n">
-        <v>129.37</v>
+        <v>29.59</v>
       </c>
       <c r="G26" t="n">
-        <v>219.94</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>41.04%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1258,28 +1258,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Comcast Corporation</t>
+          <t>Airbnb, Inc.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1172.5</v>
+        <v>803.9299999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>29.75</v>
+        <v>131.31</v>
       </c>
       <c r="G27" t="n">
-        <v>50.46</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>39.14%</t>
+          <t>39.92%</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1289,28 +1289,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CoStar Group, Inc.</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>260.65</v>
+        <v>1356.14</v>
       </c>
       <c r="F28" t="n">
-        <v>61.5</v>
+        <v>487.12</v>
       </c>
       <c r="G28" t="n">
-        <v>101.05</v>
+        <v>810.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.46%</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1320,28 +1320,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mizuho Financial Group, Inc.</t>
+          <t>CoStar Group, Inc.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1067.87</v>
+        <v>259.29</v>
       </c>
       <c r="F29" t="n">
-        <v>8.630000000000001</v>
+        <v>61.18</v>
       </c>
       <c r="G29" t="n">
-        <v>14.08</v>
+        <v>101.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>38.46%</t>
+          <t>38.37%</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1351,28 +1351,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>Copart, Inc.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1388.99</v>
+        <v>384.11</v>
       </c>
       <c r="F30" t="n">
-        <v>498.92</v>
+        <v>39.68</v>
       </c>
       <c r="G30" t="n">
-        <v>810.72</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>38.44%</t>
+          <t>38.29%</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1382,23 +1382,23 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>785.84</v>
+        <v>3510.59</v>
       </c>
       <c r="F31" t="n">
-        <v>741.45</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>1204.52</v>
+        <v>134.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>37.89%</t>
+          <t>38.09%</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>680.37</v>
+        <v>678.13</v>
       </c>
       <c r="F32" t="n">
-        <v>78.92</v>
+        <v>78.66</v>
       </c>
       <c r="G32" t="n">
         <v>127.06</v>
@@ -1429,12 +1429,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>37.75%</t>
+          <t>37.32%</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3541.85</v>
+        <v>800.23</v>
       </c>
       <c r="F33" t="n">
-        <v>83.48999999999999</v>
+        <v>755.02</v>
       </c>
       <c r="G33" t="n">
-        <v>134.12</v>
+        <v>1204.52</v>
       </c>
     </row>
     <row r="34">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1475,28 +1475,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Roper Technologies, Inc.</t>
+          <t>Mizuho Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>399.58</v>
+        <v>1093.85</v>
       </c>
       <c r="F34" t="n">
-        <v>371.23</v>
+        <v>8.84</v>
       </c>
       <c r="G34" t="n">
-        <v>591.26</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>36.97%</t>
+          <t>36.98%</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1506,28 +1506,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Copart, Inc.</t>
+          <t>Roper Technologies, Inc.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>392.82</v>
+        <v>401.07</v>
       </c>
       <c r="F35" t="n">
-        <v>40.58</v>
+        <v>372.61</v>
       </c>
       <c r="G35" t="n">
-        <v>64.38</v>
+        <v>591.26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36.65%</t>
+          <t>36.02%</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1537,28 +1537,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Anheuser-Busch InBev SA/NV</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1393.51</v>
+        <v>452.54</v>
       </c>
       <c r="F36" t="n">
-        <v>71.68000000000001</v>
+        <v>129.05</v>
       </c>
       <c r="G36" t="n">
-        <v>113.15</v>
+        <v>201.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36.55%</t>
+          <t>35.97%</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1568,28 +1568,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AppLovin Corporation</t>
+          <t>Anheuser-Busch InBev SA/NV</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1600.29</v>
+        <v>1408.48</v>
       </c>
       <c r="F37" t="n">
-        <v>473.11</v>
+        <v>72.45</v>
       </c>
       <c r="G37" t="n">
-        <v>745.61</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>36.26%</t>
+          <t>35.22%</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1599,28 +1599,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Spotify Technology S.A.</t>
+          <t>AppLovin Corporation</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1030.19</v>
+        <v>1633.75</v>
       </c>
       <c r="F38" t="n">
-        <v>500.35</v>
+        <v>483</v>
       </c>
       <c r="G38" t="n">
-        <v>785</v>
+        <v>745.61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>35.88%</t>
+          <t>35.21%</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1630,28 +1630,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Spotify Technology S.A.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>453.49</v>
+        <v>1047.14</v>
       </c>
       <c r="F39" t="n">
-        <v>129.32</v>
+        <v>508.58</v>
       </c>
       <c r="G39" t="n">
-        <v>201.69</v>
+        <v>785</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>35.83%</t>
+          <t>34.68%</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1661,28 +1661,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2345.72</v>
+        <v>367.83</v>
       </c>
       <c r="F40" t="n">
-        <v>201.04</v>
+        <v>102.47</v>
       </c>
       <c r="G40" t="n">
-        <v>313.28</v>
+        <v>156.86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34.25%</t>
+          <t>34.29%</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1692,28 +1692,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Constellation Energy Corporation</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>370.27</v>
+        <v>981.37</v>
       </c>
       <c r="F41" t="n">
-        <v>103.13</v>
+        <v>270.88</v>
       </c>
       <c r="G41" t="n">
-        <v>156.86</v>
+        <v>412.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>33.16%</t>
+          <t>33.85%</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1723,28 +1723,28 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>SAP SE</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1634.93</v>
+        <v>2417.95</v>
       </c>
       <c r="F42" t="n">
-        <v>263.64</v>
+        <v>207.23</v>
       </c>
       <c r="G42" t="n">
-        <v>394.41</v>
+        <v>313.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>32.56%</t>
+          <t>33.34%</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1754,28 +1754,28 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc.</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1057.96</v>
+        <v>299.2</v>
       </c>
       <c r="F43" t="n">
-        <v>114.26</v>
+        <v>214.15</v>
       </c>
       <c r="G43" t="n">
-        <v>169.44</v>
+        <v>321.24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>32.31%</t>
+          <t>32.51%</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1785,28 +1785,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>KKR &amp; Co. Inc.</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>303.82</v>
+        <v>1058.88</v>
       </c>
       <c r="F44" t="n">
-        <v>217.46</v>
+        <v>114.36</v>
       </c>
       <c r="G44" t="n">
-        <v>321.24</v>
+        <v>169.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.36%</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1816,28 +1816,28 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>QUALCOMM Incorporated</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1623.53</v>
+        <v>1654.47</v>
       </c>
       <c r="F45" t="n">
-        <v>151.59</v>
+        <v>266.79</v>
       </c>
       <c r="G45" t="n">
-        <v>223.25</v>
+        <v>394.41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>31.91%</t>
+          <t>31.64%</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Constellation Energy Corporation</t>
+          <t>QUALCOMM Incorporated</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1016.88</v>
+        <v>1634.56</v>
       </c>
       <c r="F46" t="n">
-        <v>280.68</v>
+        <v>152.62</v>
       </c>
       <c r="G46" t="n">
-        <v>412.23</v>
+        <v>223.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>31.78%</t>
+          <t>31.57%</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>446.62</v>
+        <v>448.01</v>
       </c>
       <c r="F47" t="n">
-        <v>338.06</v>
+        <v>339.11</v>
       </c>
       <c r="G47" t="n">
         <v>495.55</v>
@@ -1894,38 +1894,38 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29.36%</t>
+          <t>29.74%</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3493.88</v>
+        <v>876.03</v>
       </c>
       <c r="F48" t="n">
-        <v>146.59</v>
+        <v>457.89</v>
       </c>
       <c r="G48" t="n">
-        <v>207.52</v>
+        <v>651.73</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29.23%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>622.67</v>
+        <v>622.9</v>
       </c>
       <c r="F49" t="n">
-        <v>81.26000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="G49" t="n">
         <v>114.82</v>
@@ -1956,43 +1956,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>28.63%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>889.85</v>
+        <v>3521.77</v>
       </c>
       <c r="F50" t="n">
-        <v>465.12</v>
+        <v>147.76</v>
       </c>
       <c r="G50" t="n">
-        <v>651.73</v>
+        <v>207.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>28.33%</t>
+          <t>28.61%</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2002,59 +2002,59 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>T-Mobile US, Inc.</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>881.91</v>
+        <v>2194.45</v>
       </c>
       <c r="F51" t="n">
-        <v>204.62</v>
+        <v>194.99</v>
       </c>
       <c r="G51" t="n">
-        <v>285.5</v>
+        <v>273.15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27.97%</t>
+          <t>27.62%</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Insmed Incorporated</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1708.41</v>
+        <v>328.4</v>
       </c>
       <c r="F52" t="n">
-        <v>131.23</v>
+        <v>153.98</v>
       </c>
       <c r="G52" t="n">
-        <v>182.19</v>
+        <v>212.75</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.53%</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2064,28 +2064,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>T-Mobile US, Inc.</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2219.44</v>
+        <v>1785.97</v>
       </c>
       <c r="F53" t="n">
-        <v>197.21</v>
+        <v>141.28</v>
       </c>
       <c r="G53" t="n">
-        <v>273.15</v>
+        <v>194.94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27.16%</t>
+          <t>27.44%</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2095,28 +2095,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sony Group Corporation</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1327.6</v>
+        <v>1721.04</v>
       </c>
       <c r="F54" t="n">
-        <v>22.1</v>
+        <v>132.2</v>
       </c>
       <c r="G54" t="n">
-        <v>30.34</v>
+        <v>182.19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.26%</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2126,28 +2126,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>372.8</v>
+        <v>895.05</v>
       </c>
       <c r="F55" t="n">
-        <v>27.44</v>
+        <v>207.67</v>
       </c>
       <c r="G55" t="n">
-        <v>37.59</v>
+        <v>285.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>26.94%</t>
+          <t>27.09%</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2157,28 +2157,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Sony Group Corporation</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1800.38</v>
+        <v>1328.8</v>
       </c>
       <c r="F56" t="n">
-        <v>142.42</v>
+        <v>22.12</v>
       </c>
       <c r="G56" t="n">
-        <v>194.94</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26.57%</t>
+          <t>26.92%</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2188,59 +2188,59 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>538.61</v>
+        <v>373.2</v>
       </c>
       <c r="F57" t="n">
-        <v>252.87</v>
+        <v>27.47</v>
       </c>
       <c r="G57" t="n">
-        <v>344.39</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>26.27%</t>
+          <t>26.21%</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Insmed Incorporated</t>
+          <t>The Progressive Corporation</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>334.56</v>
+        <v>1190.22</v>
       </c>
       <c r="F58" t="n">
-        <v>156.87</v>
+        <v>203.04</v>
       </c>
       <c r="G58" t="n">
-        <v>212.75</v>
+        <v>275.18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.79%</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2250,28 +2250,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2321.26</v>
+        <v>544.36</v>
       </c>
       <c r="F59" t="n">
-        <v>46.47</v>
+        <v>255.57</v>
       </c>
       <c r="G59" t="n">
-        <v>62.29</v>
+        <v>344.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>25.12%</t>
+          <t>23.71%</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2281,28 +2281,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Old Dominion Freight Line, Inc.</t>
+          <t>Automatic Data Processing, Inc.</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>364.01</v>
+        <v>1001.25</v>
       </c>
       <c r="F60" t="n">
-        <v>173.2</v>
+        <v>247.56</v>
       </c>
       <c r="G60" t="n">
-        <v>231.32</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>24.56%</t>
+          <t>23.51%</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2312,28 +2312,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1547.33</v>
+        <v>31437.89</v>
       </c>
       <c r="F61" t="n">
-        <v>218.89</v>
+        <v>423.37</v>
       </c>
       <c r="G61" t="n">
-        <v>290.14</v>
+        <v>553.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>23.18%</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2343,28 +2343,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>The Progressive Corporation</t>
+          <t>Cadence Design Systems, Inc.</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1219.3</v>
+        <v>788.01</v>
       </c>
       <c r="F62" t="n">
-        <v>208</v>
+        <v>289.19</v>
       </c>
       <c r="G62" t="n">
-        <v>275.18</v>
+        <v>376.45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>23.94%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2374,28 +2374,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Automatic Data Processing, Inc.</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>998.26</v>
+        <v>1579.36</v>
       </c>
       <c r="F63" t="n">
-        <v>246.82</v>
+        <v>223.42</v>
       </c>
       <c r="G63" t="n">
-        <v>324.5</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22.26%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2405,23 +2405,23 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Diamondback Energy, Inc.</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>31951.74</v>
+        <v>459.24</v>
       </c>
       <c r="F64" t="n">
-        <v>430.29</v>
+        <v>158.64</v>
       </c>
       <c r="G64" t="n">
-        <v>553.5</v>
+        <v>205.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22.14%</t>
+          <t>22.59%</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1112.78</v>
+        <v>1106.33</v>
       </c>
       <c r="F65" t="n">
-        <v>441.4</v>
+        <v>438.85</v>
       </c>
       <c r="G65" t="n">
         <v>566.9</v>
@@ -2452,12 +2452,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21.89%</t>
+          <t>21.64%</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2467,28 +2467,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Company</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1120.68</v>
+        <v>2438.15</v>
       </c>
       <c r="F66" t="n">
-        <v>55.05</v>
+        <v>48.81</v>
       </c>
       <c r="G66" t="n">
-        <v>70.48</v>
+        <v>62.29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21.51%</t>
+          <t>21.55%</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2498,28 +2498,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1669.38</v>
+        <v>1222.68</v>
       </c>
       <c r="F67" t="n">
-        <v>80.05</v>
+        <v>175.42</v>
       </c>
       <c r="G67" t="n">
-        <v>101.99</v>
+        <v>223.61</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21.49%</t>
+          <t>21.08%</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2529,28 +2529,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NXP Semiconductors N.V.</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>570.13</v>
+        <v>1904.24</v>
       </c>
       <c r="F68" t="n">
-        <v>226.14</v>
+        <v>109.41</v>
       </c>
       <c r="G68" t="n">
-        <v>288.03</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21.28%</t>
+          <t>20.74%</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2560,28 +2560,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cadence Design Systems, Inc.</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>807.55</v>
+        <v>1685.85</v>
       </c>
       <c r="F69" t="n">
-        <v>296.36</v>
+        <v>80.84</v>
       </c>
       <c r="G69" t="n">
-        <v>376.45</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21.16%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2591,28 +2591,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Microchip Technology Incorporated</t>
+          <t>Bristol-Myers Squibb Company</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>410.31</v>
+        <v>1137.78</v>
       </c>
       <c r="F70" t="n">
-        <v>75.92</v>
+        <v>55.89</v>
       </c>
       <c r="G70" t="n">
-        <v>96.3</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21.16%</t>
+          <t>20.48%</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2622,28 +2622,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1902.32</v>
+        <v>1271.3</v>
       </c>
       <c r="F71" t="n">
-        <v>109.3</v>
+        <v>101.79</v>
       </c>
       <c r="G71" t="n">
-        <v>138.63</v>
+        <v>128.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20.86%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2653,28 +2653,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Starbucks Corporation</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1210.44</v>
+        <v>1044.62</v>
       </c>
       <c r="F72" t="n">
-        <v>176.97</v>
+        <v>91.69</v>
       </c>
       <c r="G72" t="n">
-        <v>223.61</v>
+        <v>115.04</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20.07%</t>
+          <t>19.99%</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2684,28 +2684,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Starbucks Corporation</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1047.59</v>
+        <v>15698.83</v>
       </c>
       <c r="F73" t="n">
-        <v>91.95</v>
+        <v>331.11</v>
       </c>
       <c r="G73" t="n">
-        <v>115.04</v>
+        <v>413.82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20.05%</t>
+          <t>19.77%</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2715,28 +2715,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Diamondback Energy, Inc.</t>
+          <t>NXP Semiconductors N.V.</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>474.61</v>
+        <v>582.59</v>
       </c>
       <c r="F74" t="n">
-        <v>163.95</v>
+        <v>231.08</v>
       </c>
       <c r="G74" t="n">
-        <v>205.08</v>
+        <v>288.03</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>19.94%</t>
+          <t>19.53%</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2746,23 +2746,23 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>Old Dominion Freight Line, Inc.</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>15707.84</v>
+        <v>391.19</v>
       </c>
       <c r="F75" t="n">
-        <v>331.3</v>
+        <v>186.13</v>
       </c>
       <c r="G75" t="n">
-        <v>413.82</v>
+        <v>231.32</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.49%</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>756.5700000000001</v>
+        <v>759.42</v>
       </c>
       <c r="F76" t="n">
-        <v>58.47</v>
+        <v>58.69</v>
       </c>
       <c r="G76" t="n">
         <v>72.90000000000001</v>
@@ -2793,12 +2793,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.36%</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2808,28 +2808,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>MercadoLibre, Inc.</t>
+          <t>Intuitive Surgical, Inc.</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1088.87</v>
+        <v>1780.66</v>
       </c>
       <c r="F77" t="n">
-        <v>2147.79</v>
+        <v>496.73</v>
       </c>
       <c r="G77" t="n">
-        <v>2645.22</v>
+        <v>616</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>18.57%</t>
+          <t>18.92%</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2839,28 +2839,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Microchip Technology Incorporated</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1301.77</v>
+        <v>421.98</v>
       </c>
       <c r="F78" t="n">
-        <v>104.23</v>
+        <v>78.08</v>
       </c>
       <c r="G78" t="n">
-        <v>128.01</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>18.55%</t>
+          <t>18.83%</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2870,28 +2870,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Financial Group, Inc.</t>
+          <t>MercadoLibre, Inc.</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1347.4</v>
+        <v>1088.58</v>
       </c>
       <c r="F79" t="n">
-        <v>20.99</v>
+        <v>2147.22</v>
       </c>
       <c r="G79" t="n">
-        <v>25.77</v>
+        <v>2645.22</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>18.29%</t>
+          <t>18.13%</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2901,28 +2901,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>Sumitomo Mitsui Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1142.55</v>
+        <v>1354.46</v>
       </c>
       <c r="F80" t="n">
-        <v>47.04</v>
+        <v>21.1</v>
       </c>
       <c r="G80" t="n">
-        <v>57.57</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>18.15%</t>
+          <t>17.89%</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2932,28 +2932,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Intuitive Surgical, Inc.</t>
+          <t>Sanofi</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1807.51</v>
+        <v>1148.14</v>
       </c>
       <c r="F81" t="n">
-        <v>504.22</v>
+        <v>47.27</v>
       </c>
       <c r="G81" t="n">
-        <v>616</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17.69%</t>
+          <t>16.93%</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2963,28 +2963,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>HDFC Bank Limited</t>
+          <t>IDEXX Laboratories, Inc.</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1660.88</v>
+        <v>511.71</v>
       </c>
       <c r="F82" t="n">
-        <v>32.38</v>
+        <v>639.6</v>
       </c>
       <c r="G82" t="n">
-        <v>39.34</v>
+        <v>769.98</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.71%</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2994,28 +2994,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software, Inc.</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>407.07</v>
+        <v>1857.34</v>
       </c>
       <c r="F83" t="n">
-        <v>220.3</v>
+        <v>1410.45</v>
       </c>
       <c r="G83" t="n">
-        <v>264.79</v>
+        <v>1693.35</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.64%</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3025,28 +3025,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>Prologis, Inc.</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1234.11</v>
+        <v>1204.55</v>
       </c>
       <c r="F84" t="n">
-        <v>112.35</v>
+        <v>129.68</v>
       </c>
       <c r="G84" t="n">
-        <v>134.88</v>
+        <v>155.57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>16.55%</t>
+          <t>16.35%</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3056,28 +3056,28 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>GE HealthCare Technologies Inc.</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>360.55</v>
+        <v>767.2</v>
       </c>
       <c r="F85" t="n">
-        <v>78.97</v>
+        <v>190.91</v>
       </c>
       <c r="G85" t="n">
-        <v>94.63</v>
+        <v>228.23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16.14%</t>
+          <t>16.33%</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>769.13</v>
+        <v>1239.6</v>
       </c>
       <c r="F86" t="n">
-        <v>191.39</v>
+        <v>112.85</v>
       </c>
       <c r="G86" t="n">
-        <v>228.23</v>
+        <v>134.88</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>16.08%</t>
+          <t>16.23%</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3118,28 +3118,28 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Prologis, Inc.</t>
+          <t>Take-Two Interactive Software, Inc.</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1212.73</v>
+        <v>409.86</v>
       </c>
       <c r="F87" t="n">
-        <v>130.56</v>
+        <v>221.81</v>
       </c>
       <c r="G87" t="n">
-        <v>155.57</v>
+        <v>264.79</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>15.68%</t>
+          <t>16.11%</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3149,28 +3149,28 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Capital One Financial Corporation</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1391.81</v>
+        <v>1742.47</v>
       </c>
       <c r="F88" t="n">
-        <v>218.93</v>
+        <v>138.37</v>
       </c>
       <c r="G88" t="n">
-        <v>259.64</v>
+        <v>164.94</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>15.67%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Boston Scientific Corporation</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1880.38</v>
+        <v>1362.45</v>
       </c>
       <c r="F89" t="n">
-        <v>1427.94</v>
+        <v>91.87</v>
       </c>
       <c r="G89" t="n">
-        <v>1693.35</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.44%</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IBN</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3211,28 +3211,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1047.55</v>
+        <v>15828.13</v>
       </c>
       <c r="F90" t="n">
-        <v>29.29</v>
+        <v>421.81</v>
       </c>
       <c r="G90" t="n">
-        <v>34.3</v>
+        <v>498.83</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>14.58%</t>
+          <t>15.34%</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3242,28 +3242,28 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Boston Scientific Corporation</t>
+          <t>GE HealthCare Technologies Inc.</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1387.07</v>
+        <v>365.75</v>
       </c>
       <c r="F91" t="n">
-        <v>93.53</v>
+        <v>80.11</v>
       </c>
       <c r="G91" t="n">
-        <v>109.5</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14.42%</t>
+          <t>14.11%</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3273,28 +3273,28 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PepsiCo, Inc.</t>
+          <t>HDFC Bank Limited</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2103.31</v>
+        <v>1733.2</v>
       </c>
       <c r="F92" t="n">
-        <v>153.63</v>
+        <v>33.79</v>
       </c>
       <c r="G92" t="n">
-        <v>179.53</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14.07%</t>
+          <t>13.85%</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3304,28 +3304,28 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Capital One Financial Corporation</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1784.91</v>
+        <v>1422.01</v>
       </c>
       <c r="F93" t="n">
-        <v>141.74</v>
+        <v>223.68</v>
       </c>
       <c r="G93" t="n">
-        <v>164.94</v>
+        <v>259.64</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>14.03%</t>
+          <t>13.73%</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3335,28 +3335,28 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc.</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1621.09</v>
+        <v>1317.37</v>
       </c>
       <c r="F94" t="n">
-        <v>5001.84</v>
+        <v>102.71</v>
       </c>
       <c r="G94" t="n">
-        <v>5818.24</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13.97%</t>
+          <t>13.55%</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3366,28 +3366,28 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6205.01</v>
+        <v>2124.81</v>
       </c>
       <c r="F95" t="n">
-        <v>321.83</v>
+        <v>155.2</v>
       </c>
       <c r="G95" t="n">
-        <v>374.11</v>
+        <v>179.53</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13.76%</t>
+          <t>13.24%</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3397,28 +3397,28 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Merck &amp; Co., Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2754.31</v>
+        <v>1774.02</v>
       </c>
       <c r="F96" t="n">
-        <v>110.27</v>
+        <v>144.93</v>
       </c>
       <c r="G96" t="n">
-        <v>127.87</v>
+        <v>167.04</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>13.75%</t>
+          <t>12.55%</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3428,28 +3428,28 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1763.62</v>
+        <v>3579.64</v>
       </c>
       <c r="F97" t="n">
-        <v>144.08</v>
+        <v>153.19</v>
       </c>
       <c r="G97" t="n">
-        <v>167.04</v>
+        <v>175.18</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>13.72%</t>
+          <t>12.52%</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3459,28 +3459,28 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>16150.84</v>
+        <v>45190.47</v>
       </c>
       <c r="F98" t="n">
-        <v>430.41</v>
+        <v>185.61</v>
       </c>
       <c r="G98" t="n">
-        <v>498.83</v>
+        <v>212.18</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>13.52%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3490,28 +3490,28 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1320.58</v>
+        <v>2185.76</v>
       </c>
       <c r="F99" t="n">
-        <v>102.96</v>
+        <v>581.77</v>
       </c>
       <c r="G99" t="n">
-        <v>119.06</v>
+        <v>664.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>13.44%</t>
+          <t>11.96%</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3521,28 +3521,28 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Booking Holdings Inc.</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>497.8</v>
+        <v>1660.12</v>
       </c>
       <c r="F100" t="n">
-        <v>43.36</v>
+        <v>5122.25</v>
       </c>
       <c r="G100" t="n">
-        <v>50.09</v>
+        <v>5818.24</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>13.36%</t>
+          <t>11.89%</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SCCO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3552,28 +3552,28 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>Southern Copper Corporation</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3552.15</v>
+        <v>1579.22</v>
       </c>
       <c r="F101" t="n">
-        <v>151.77</v>
+        <v>192.8</v>
       </c>
       <c r="G101" t="n">
-        <v>175.18</v>
+        <v>218.81</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>13.02%</t>
+          <t>11.34%</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SCCO</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3583,28 +3583,28 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Southern Copper Corporation</t>
+          <t>Merck &amp; Co., Inc.</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1558.91</v>
+        <v>2831.74</v>
       </c>
       <c r="F102" t="n">
-        <v>190.32</v>
+        <v>113.37</v>
       </c>
       <c r="G102" t="n">
-        <v>218.81</v>
+        <v>127.87</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12.98%</t>
+          <t>11.33%</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3614,28 +3614,28 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>The Home Depot, Inc.</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2173.88</v>
+        <v>3764.23</v>
       </c>
       <c r="F103" t="n">
-        <v>578.61</v>
+        <v>378.12</v>
       </c>
       <c r="G103" t="n">
-        <v>664.9</v>
+        <v>426.44</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>12.93%</t>
+          <t>11.15%</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3645,59 +3645,59 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>536.4</v>
+        <v>17869.03</v>
       </c>
       <c r="F104" t="n">
-        <v>670.46</v>
+        <v>706.41</v>
       </c>
       <c r="G104" t="n">
-        <v>769.98</v>
+        <v>795.0599999999999</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>12.33%</t>
+          <t>10.76%</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>848.37</v>
+        <v>6436.57</v>
       </c>
       <c r="F105" t="n">
-        <v>250.23</v>
+        <v>333.84</v>
       </c>
       <c r="G105" t="n">
-        <v>285.42</v>
+        <v>374.11</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12.32%</t>
+          <t>10.56%</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3707,28 +3707,28 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4174.31</v>
+        <v>514.33</v>
       </c>
       <c r="F106" t="n">
-        <v>940.25</v>
+        <v>44.8</v>
       </c>
       <c r="G106" t="n">
-        <v>1072.35</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>12.16%</t>
+          <t>10.35%</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>IBN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3738,28 +3738,28 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>The Home Depot, Inc.</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3729.09</v>
+        <v>1108.64</v>
       </c>
       <c r="F107" t="n">
-        <v>374.59</v>
+        <v>30.75</v>
       </c>
       <c r="G107" t="n">
-        <v>426.44</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>11.79%</t>
+          <t>10.34%</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3769,28 +3769,28 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Eaton Corporation plc</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1368.08</v>
+        <v>1286.38</v>
       </c>
       <c r="F108" t="n">
-        <v>351.42</v>
+        <v>187.43</v>
       </c>
       <c r="G108" t="n">
-        <v>398.4</v>
+        <v>209.05</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>11.36%</t>
+          <t>9.85%</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3800,59 +3800,59 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>O'Reilly Automotive, Inc.</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3854.06</v>
+        <v>829.2</v>
       </c>
       <c r="F109" t="n">
-        <v>236.73</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="G109" t="n">
-        <v>267.08</v>
+        <v>108.72</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10.95%</t>
+          <t>9.78%</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings plc</t>
+          <t>Eaton Corporation plc</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>888.24</v>
+        <v>1399.3</v>
       </c>
       <c r="F110" t="n">
-        <v>407.69</v>
+        <v>359.44</v>
       </c>
       <c r="G110" t="n">
-        <v>457.84</v>
+        <v>398.4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10.21%</t>
+          <t>9.72%</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3862,28 +3862,28 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>AT&amp;T Inc.</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4813.75</v>
+        <v>1864.53</v>
       </c>
       <c r="F111" t="n">
-        <v>538.79</v>
+        <v>26.3</v>
       </c>
       <c r="G111" t="n">
-        <v>600.08</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3893,28 +3893,28 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>38138.18</v>
+        <v>4299.11</v>
       </c>
       <c r="F112" t="n">
-        <v>259.48</v>
+        <v>968.36</v>
       </c>
       <c r="G112" t="n">
-        <v>288.62</v>
+        <v>1072.35</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>10.03%</t>
+          <t>9.56%</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3924,28 +3924,28 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc.</t>
+          <t>Xcel Energy Inc.</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1858.14</v>
+        <v>440.7</v>
       </c>
       <c r="F113" t="n">
-        <v>26.21</v>
+        <v>74.5</v>
       </c>
       <c r="G113" t="n">
-        <v>29.13</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9.92%</t>
+          <t>9.21%</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3955,28 +3955,28 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>46534.42</v>
+        <v>1210.19</v>
       </c>
       <c r="F114" t="n">
-        <v>191.13</v>
+        <v>472.01</v>
       </c>
       <c r="G114" t="n">
-        <v>212.18</v>
+        <v>519.88</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.74%</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3986,28 +3986,28 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>American Express Company</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1292.77</v>
+        <v>2430.48</v>
       </c>
       <c r="F115" t="n">
-        <v>188.36</v>
+        <v>352.83</v>
       </c>
       <c r="G115" t="n">
-        <v>209.05</v>
+        <v>386.63</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9.88%</t>
+          <t>8.69%</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4017,28 +4017,28 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Exelon Corporation</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>18124.27</v>
+        <v>443.49</v>
       </c>
       <c r="F116" t="n">
-        <v>716.5</v>
+        <v>43.91</v>
       </c>
       <c r="G116" t="n">
-        <v>795.0599999999999</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>9.61%</t>
+          <t>8.64%</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4048,28 +4048,28 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals Incorporated</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1204.78</v>
+        <v>1407.85</v>
       </c>
       <c r="F117" t="n">
-        <v>469.9</v>
+        <v>368.14</v>
       </c>
       <c r="G117" t="n">
-        <v>519.88</v>
+        <v>402.95</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>9.48%</t>
+          <t>8.54%</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4079,23 +4079,23 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>O'Reilly Automotive, Inc.</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>832.58</v>
+        <v>1610.95</v>
       </c>
       <c r="F118" t="n">
-        <v>98.41</v>
+        <v>527.66</v>
       </c>
       <c r="G118" t="n">
-        <v>108.72</v>
+        <v>576.91</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>8.26%</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8327.129999999999</v>
+        <v>8388.379999999999</v>
       </c>
       <c r="F119" t="n">
-        <v>305.89</v>
+        <v>308.14</v>
       </c>
       <c r="G119" t="n">
         <v>335.87</v>
@@ -4126,12 +4126,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>8.92%</t>
+          <t>7.92%</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4141,28 +4141,28 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4669.51</v>
+        <v>9360.17</v>
       </c>
       <c r="F120" t="n">
-        <v>414.88</v>
+        <v>1044.13</v>
       </c>
       <c r="G120" t="n">
-        <v>455.5</v>
+        <v>1133.95</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8.91%</t>
+          <t>7.91%</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4172,28 +4172,28 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>American Express Company</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2425.93</v>
+        <v>1395.29</v>
       </c>
       <c r="F121" t="n">
-        <v>352.17</v>
+        <v>235.23</v>
       </c>
       <c r="G121" t="n">
-        <v>386.63</v>
+        <v>255.44</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8.54%</t>
+          <t>7.79%</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4203,28 +4203,28 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>9297.6</v>
+        <v>4009.38</v>
       </c>
       <c r="F122" t="n">
-        <v>1037.15</v>
+        <v>246.27</v>
       </c>
       <c r="G122" t="n">
-        <v>1133.95</v>
+        <v>267.08</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8.51%</t>
+          <t>7.77%</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4234,23 +4234,23 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc.</t>
+          <t>BlackRock, Inc.</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1611.34</v>
+        <v>1737.16</v>
       </c>
       <c r="F123" t="n">
-        <v>527.79</v>
+        <v>1119.66</v>
       </c>
       <c r="G123" t="n">
-        <v>576.91</v>
+        <v>1214.03</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>7.46%</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1765.58</v>
+        <v>1782.53</v>
       </c>
       <c r="F124" t="n">
-        <v>68.73</v>
+        <v>69.39</v>
       </c>
       <c r="G124" t="n">
         <v>74.98</v>
@@ -4281,12 +4281,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8.29%</t>
+          <t>7.45%</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4296,28 +4296,28 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1413.28</v>
+        <v>4961.88</v>
       </c>
       <c r="F125" t="n">
-        <v>369.56</v>
+        <v>555.37</v>
       </c>
       <c r="G125" t="n">
-        <v>402.95</v>
+        <v>600.08</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8.18%</t>
+          <t>7.24%</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4327,28 +4327,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>400.78</v>
+        <v>3256.32</v>
       </c>
       <c r="F126" t="n">
-        <v>82.06</v>
+        <v>308.71</v>
       </c>
       <c r="G126" t="n">
-        <v>89.37</v>
+        <v>332.79</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8.11%</t>
+          <t>7.23%</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4358,28 +4358,28 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Brookfield Corporation</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1023.62</v>
+        <v>404.93</v>
       </c>
       <c r="F127" t="n">
-        <v>45.55</v>
+        <v>82.91</v>
       </c>
       <c r="G127" t="n">
-        <v>49.57</v>
+        <v>89.37</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7.96%</t>
+          <t>7.22%</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>SATA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4389,28 +4389,28 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Strive Asset Management, LLC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1394.52</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>235.1</v>
+        <v>93.03</v>
       </c>
       <c r="G128" t="n">
-        <v>255.44</v>
+        <v>100.27</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7.83%</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4420,28 +4420,28 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>BlackRock, Inc.</t>
+          <t>Coca-Cola Europacific Partners PLC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1736.05</v>
+        <v>420.7</v>
       </c>
       <c r="F129" t="n">
-        <v>1118.94</v>
+        <v>92.2</v>
       </c>
       <c r="G129" t="n">
-        <v>1214.03</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7.81%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4451,28 +4451,28 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3236.06</v>
+        <v>39685.87</v>
       </c>
       <c r="F130" t="n">
-        <v>306.79</v>
+        <v>270.01</v>
       </c>
       <c r="G130" t="n">
-        <v>332.79</v>
+        <v>288.62</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>6.42%</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4482,28 +4482,28 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Toyota Motor Corporation</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2970.71</v>
+        <v>3987.93</v>
       </c>
       <c r="F131" t="n">
-        <v>226.86</v>
+        <v>225.64</v>
       </c>
       <c r="G131" t="n">
-        <v>245.75</v>
+        <v>241.12</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7.67%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4513,23 +4513,23 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Xcel Energy Inc.</t>
+          <t>Altria Group, Inc.</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>449.93</v>
+        <v>1044.64</v>
       </c>
       <c r="F132" t="n">
-        <v>76.06</v>
+        <v>62.23</v>
       </c>
       <c r="G132" t="n">
-        <v>82.37</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7.56%</t>
+          <t>6.12%</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3884.93</v>
+        <v>3945.54</v>
       </c>
       <c r="F133" t="n">
-        <v>53.2</v>
+        <v>54.03</v>
       </c>
       <c r="G133" t="n">
         <v>57.55</v>
@@ -4560,12 +4560,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>6.05%</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4575,28 +4575,28 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3941.44</v>
+        <v>25972.95</v>
       </c>
       <c r="F134" t="n">
-        <v>223.01</v>
+        <v>242.96</v>
       </c>
       <c r="G134" t="n">
-        <v>241.12</v>
+        <v>258.6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>7.47%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>BN</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4606,28 +4606,28 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Coca-Cola Europacific Partners PLC</t>
+          <t>Brookfield Corporation</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>418.42</v>
+        <v>1046.99</v>
       </c>
       <c r="F135" t="n">
-        <v>91.7</v>
+        <v>46.59</v>
       </c>
       <c r="G135" t="n">
-        <v>99.09999999999999</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>7.46%</t>
+          <t>5.84%</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4637,23 +4637,23 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>The TJX Companies, Inc.</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>25581.69</v>
+        <v>1671.3</v>
       </c>
       <c r="F136" t="n">
-        <v>239.3</v>
+        <v>150.17</v>
       </c>
       <c r="G136" t="n">
-        <v>258.6</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>7.45%</t>
+          <t>5.82%</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1142.52</v>
+        <v>1162.6</v>
       </c>
       <c r="F137" t="n">
-        <v>488.27</v>
+        <v>496.85</v>
       </c>
       <c r="G137" t="n">
         <v>527.55</v>
@@ -4684,12 +4684,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>7.44%</t>
+          <t>5.76%</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4699,23 +4699,23 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>Toyota Motor Corporation</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2840.56</v>
+        <v>3032.52</v>
       </c>
       <c r="F138" t="n">
-        <v>90.48999999999999</v>
+        <v>231.58</v>
       </c>
       <c r="G138" t="n">
-        <v>97.76000000000001</v>
+        <v>245.75</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>5.71%</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2932.33</v>
+        <v>2983.07</v>
       </c>
       <c r="F139" t="n">
-        <v>233.46</v>
+        <v>237.5</v>
       </c>
       <c r="G139" t="n">
         <v>251.87</v>
@@ -4746,12 +4746,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>5.62%</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4761,59 +4761,59 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1033.9</v>
+        <v>2896.43</v>
       </c>
       <c r="F140" t="n">
-        <v>831.21</v>
+        <v>92.27</v>
       </c>
       <c r="G140" t="n">
-        <v>894.75</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>5.44%</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Exelon Corporation</t>
+          <t>Seagate Technology Holdings plc</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>452.27</v>
+        <v>943.28</v>
       </c>
       <c r="F141" t="n">
-        <v>44.78</v>
+        <v>432.95</v>
       </c>
       <c r="G141" t="n">
-        <v>48.09</v>
+        <v>457.84</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6.49%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4823,59 +4823,59 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Altria Group, Inc.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1040.61</v>
+        <v>1052.93</v>
       </c>
       <c r="F142" t="n">
-        <v>61.99</v>
+        <v>846.51</v>
       </c>
       <c r="G142" t="n">
-        <v>66.3</v>
+        <v>894.75</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>6.47%</t>
+          <t>5.32%</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2558.32</v>
+        <v>916.1799999999999</v>
       </c>
       <c r="F143" t="n">
-        <v>322.32</v>
+        <v>270.23</v>
       </c>
       <c r="G143" t="n">
-        <v>344.6</v>
+        <v>285.42</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>6.26%</t>
+          <t>5.25%</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4885,28 +4885,28 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Rio Tinto Group</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1816.81</v>
+        <v>1500.51</v>
       </c>
       <c r="F144" t="n">
-        <v>91.03</v>
+        <v>68.77</v>
       </c>
       <c r="G144" t="n">
-        <v>97.11</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6.06%</t>
+          <t>5.18%</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>The TJX Companies, Inc.</t>
+          <t>American Electric Power Company, Inc.</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1667.29</v>
+        <v>633.38</v>
       </c>
       <c r="F145" t="n">
-        <v>149.81</v>
+        <v>118.33</v>
       </c>
       <c r="G145" t="n">
-        <v>159.48</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4947,28 +4947,28 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>17144.51</v>
+        <v>2157.73</v>
       </c>
       <c r="F146" t="n">
-        <v>330.56</v>
+        <v>460.16</v>
       </c>
       <c r="G146" t="n">
-        <v>351.33</v>
+        <v>483.05</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>4.73%</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4978,28 +4978,28 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Rio Tinto Group</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1491.57</v>
+        <v>1846.55</v>
       </c>
       <c r="F147" t="n">
-        <v>68.36</v>
+        <v>92.52</v>
       </c>
       <c r="G147" t="n">
-        <v>72.58</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5009,59 +5009,59 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2866.83</v>
+        <v>2606.58</v>
       </c>
       <c r="F148" t="n">
-        <v>306.7</v>
+        <v>328.4</v>
       </c>
       <c r="G148" t="n">
-        <v>324.9</v>
+        <v>344.6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>4.47%</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>ENB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>Enbridge Inc.</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>538.55</v>
+        <v>1053.95</v>
       </c>
       <c r="F149" t="n">
-        <v>1124.15</v>
+        <v>48.28</v>
       </c>
       <c r="G149" t="n">
-        <v>1188.66</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>4.37%</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5071,28 +5071,28 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Strive Asset Management, LLC</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>1509.3</v>
       </c>
       <c r="F150" t="n">
-        <v>94.84</v>
+        <v>269.06</v>
       </c>
       <c r="G150" t="n">
-        <v>100.27</v>
+        <v>281.36</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>TBB</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5102,28 +5102,28 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2142.78</v>
+        <v>1380.22</v>
       </c>
       <c r="F151" t="n">
-        <v>456.97</v>
+        <v>22.48</v>
       </c>
       <c r="G151" t="n">
-        <v>483.05</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5133,28 +5133,28 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1498.08</v>
+        <v>2864.74</v>
       </c>
       <c r="F152" t="n">
-        <v>267.06</v>
+        <v>946.33</v>
       </c>
       <c r="G152" t="n">
-        <v>281.36</v>
+        <v>984.7</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5164,28 +5164,28 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc.</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2831.68</v>
+        <v>4927.48</v>
       </c>
       <c r="F153" t="n">
-        <v>935.41</v>
+        <v>437.8</v>
       </c>
       <c r="G153" t="n">
-        <v>984.7</v>
+        <v>455.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5195,28 +5195,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Marriott International, Inc.</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2335.43</v>
+        <v>866.74</v>
       </c>
       <c r="F154" t="n">
-        <v>166.23</v>
+        <v>319.29</v>
       </c>
       <c r="G154" t="n">
-        <v>174.61</v>
+        <v>331.09</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4.77%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5226,28 +5226,28 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Marriott International, Inc.</t>
+          <t>Baker Hughes Company</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>855.91</v>
+        <v>557.03</v>
       </c>
       <c r="F155" t="n">
-        <v>315.3</v>
+        <v>56.45</v>
       </c>
       <c r="G155" t="n">
-        <v>331.09</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5257,28 +5257,28 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Mitsubishi UFJ Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5523.34</v>
+        <v>2089.08</v>
       </c>
       <c r="F156" t="n">
-        <v>1423</v>
+        <v>18.24</v>
       </c>
       <c r="G156" t="n">
-        <v>1493.48</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5288,28 +5288,28 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2905.26</v>
+        <v>5594.72</v>
       </c>
       <c r="F157" t="n">
-        <v>182.8</v>
+        <v>1441.39</v>
       </c>
       <c r="G157" t="n">
-        <v>191.62</v>
+        <v>1493.48</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5319,28 +5319,28 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Mitsubishi UFJ Financial Group, Inc.</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2067.32</v>
+        <v>2368.86</v>
       </c>
       <c r="F158" t="n">
-        <v>18.05</v>
+        <v>168.61</v>
       </c>
       <c r="G158" t="n">
-        <v>18.9</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5350,28 +5350,28 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>UBS Group AG</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1485.79</v>
+        <v>2941.81</v>
       </c>
       <c r="F159" t="n">
-        <v>47.15</v>
+        <v>185.1</v>
       </c>
       <c r="G159" t="n">
-        <v>49.36</v>
+        <v>191.62</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5381,28 +5381,28 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Baker Hughes Company</t>
+          <t>UBS Group AG</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>552.99</v>
+        <v>1505.01</v>
       </c>
       <c r="F160" t="n">
-        <v>56.04</v>
+        <v>47.76</v>
       </c>
       <c r="G160" t="n">
-        <v>58.5</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TBB</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5412,28 +5412,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
+          <t>NextEra Energy, Inc.</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1378.99</v>
+        <v>1797.92</v>
       </c>
       <c r="F161" t="n">
-        <v>22.46</v>
+        <v>86.33</v>
       </c>
       <c r="G161" t="n">
-        <v>23.41</v>
+        <v>89.19</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5443,28 +5443,28 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>American Electric Power Company, Inc.</t>
+          <t>International Business Machines Corporation</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>641.11</v>
+        <v>2941.89</v>
       </c>
       <c r="F162" t="n">
-        <v>119.78</v>
+        <v>314.73</v>
       </c>
       <c r="G162" t="n">
-        <v>124.8</v>
+        <v>324.9</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5474,28 +5474,28 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>AstraZeneca PLC</t>
+          <t>Shell plc</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2876.4</v>
+        <v>2142.2</v>
       </c>
       <c r="F163" t="n">
-        <v>92.77</v>
+        <v>75.73</v>
       </c>
       <c r="G163" t="n">
-        <v>96.51000000000001</v>
+        <v>78.17</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5505,28 +5505,28 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1970.79</v>
+        <v>17704.65</v>
       </c>
       <c r="F164" t="n">
-        <v>726.37</v>
+        <v>341.36</v>
       </c>
       <c r="G164" t="n">
-        <v>752.02</v>
+        <v>351.33</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ENB</t>
+          <t>CCZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5536,28 +5536,28 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Enbridge Inc.</t>
+          <t>Comcast Holdings Corp.</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1066.18</v>
+        <v>615.7</v>
       </c>
       <c r="F165" t="n">
-        <v>48.84</v>
+        <v>65</v>
       </c>
       <c r="G165" t="n">
-        <v>50.54</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5567,28 +5567,28 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Exxon Mobil Corporation</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3079.59</v>
+        <v>5836.56</v>
       </c>
       <c r="F166" t="n">
-        <v>657.36</v>
+        <v>138.4</v>
       </c>
       <c r="G166" t="n">
-        <v>679.99</v>
+        <v>142.34</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5598,28 +5598,28 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1840.96</v>
+        <v>792.36</v>
       </c>
       <c r="F167" t="n">
-        <v>341.88</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G167" t="n">
-        <v>353.25</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5629,28 +5629,28 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Ross Stores, Inc.</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>613.54</v>
+        <v>1540.03</v>
       </c>
       <c r="F168" t="n">
-        <v>188.65</v>
+        <v>71.88</v>
       </c>
       <c r="G168" t="n">
-        <v>194.92</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5660,28 +5660,28 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Ross Stores, Inc.</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>703.95</v>
+        <v>618.29</v>
       </c>
       <c r="F169" t="n">
-        <v>37.76</v>
+        <v>190.11</v>
       </c>
       <c r="G169" t="n">
-        <v>38.95</v>
+        <v>194.92</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5691,28 +5691,28 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1574.76</v>
+        <v>1856.04</v>
       </c>
       <c r="F170" t="n">
-        <v>93.48999999999999</v>
+        <v>344.68</v>
       </c>
       <c r="G170" t="n">
-        <v>96.44</v>
+        <v>353.25</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5722,59 +5722,59 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Parker-Hannifin Corporation</t>
+          <t>AstraZeneca PLC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1181.18</v>
+        <v>5841.78</v>
       </c>
       <c r="F171" t="n">
-        <v>935.84</v>
+        <v>188.41</v>
       </c>
       <c r="G171" t="n">
-        <v>965</v>
+        <v>192.79</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>FER</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Ferrovial SE</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>789.04</v>
+        <v>488.04</v>
       </c>
       <c r="F172" t="n">
-        <v>80.76000000000001</v>
+        <v>68.28</v>
       </c>
       <c r="G172" t="n">
-        <v>83.23999999999999</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CCZ</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5784,28 +5784,28 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Comcast Holdings Corp.</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>615.7</v>
+        <v>2696.16</v>
       </c>
       <c r="F173" t="n">
-        <v>65</v>
+        <v>201.09</v>
       </c>
       <c r="G173" t="n">
-        <v>66.90000000000001</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5815,28 +5815,28 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1444.93</v>
+        <v>1592.11</v>
       </c>
       <c r="F174" t="n">
-        <v>25.42</v>
+        <v>94.52</v>
       </c>
       <c r="G174" t="n">
-        <v>26.14</v>
+        <v>96.44</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5846,59 +5846,59 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Verizon Communications Inc.</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1522.24</v>
+        <v>1881.2</v>
       </c>
       <c r="F175" t="n">
-        <v>310.88</v>
+        <v>44.61</v>
       </c>
       <c r="G175" t="n">
-        <v>319.26</v>
+        <v>45.48</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FER</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Ferrovial SE</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>485.96</v>
+        <v>3479.47</v>
       </c>
       <c r="F176" t="n">
-        <v>67.98999999999999</v>
+        <v>174.03</v>
       </c>
       <c r="G176" t="n">
-        <v>69.81999999999999</v>
+        <v>177.3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5908,28 +5908,28 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc.</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3094.5</v>
+        <v>1240.92</v>
       </c>
       <c r="F177" t="n">
-        <v>78.31999999999999</v>
+        <v>311.25</v>
       </c>
       <c r="G177" t="n">
-        <v>80.39</v>
+        <v>316.94</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5939,28 +5939,28 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Novartis AG</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2852.86</v>
+        <v>1471.69</v>
       </c>
       <c r="F178" t="n">
-        <v>148.68</v>
+        <v>636</v>
       </c>
       <c r="G178" t="n">
-        <v>152.48</v>
+        <v>645.67</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5970,28 +5970,28 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1234.19</v>
+        <v>715.7</v>
       </c>
       <c r="F179" t="n">
-        <v>309.56</v>
+        <v>38.39</v>
       </c>
       <c r="G179" t="n">
-        <v>316.94</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6001,59 +6001,59 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Banco Santander, S.A.</t>
+          <t>Parker-Hannifin Corporation</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1885.41</v>
+        <v>1201.58</v>
       </c>
       <c r="F180" t="n">
-        <v>12.75</v>
+        <v>952</v>
       </c>
       <c r="G180" t="n">
-        <v>13.05</v>
+        <v>965</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1958.54</v>
+        <v>562.05</v>
       </c>
       <c r="F181" t="n">
-        <v>215.55</v>
+        <v>1173.22</v>
       </c>
       <c r="G181" t="n">
-        <v>220.56</v>
+        <v>1188.66</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6063,28 +6063,28 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Philip Morris International Inc.</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2694.01</v>
+        <v>2801.02</v>
       </c>
       <c r="F182" t="n">
-        <v>200.93</v>
+        <v>179.94</v>
       </c>
       <c r="G182" t="n">
-        <v>205.36</v>
+        <v>181.91</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6094,28 +6094,28 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>McDonald's Corporation</t>
+          <t>CME Group Inc.</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2247.85</v>
+        <v>1045.35</v>
       </c>
       <c r="F183" t="n">
-        <v>315</v>
+        <v>290.77</v>
       </c>
       <c r="G183" t="n">
-        <v>321.79</v>
+        <v>293.78</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6125,28 +6125,28 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>McDonald's Corporation</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>9498.85</v>
+        <v>2273.04</v>
       </c>
       <c r="F184" t="n">
-        <v>119.14</v>
+        <v>318.53</v>
       </c>
       <c r="G184" t="n">
-        <v>121.62</v>
+        <v>321.79</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6156,28 +6156,28 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>PACCAR Inc</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>645.77</v>
+        <v>2048.39</v>
       </c>
       <c r="F185" t="n">
-        <v>122.91</v>
+        <v>754.97</v>
       </c>
       <c r="G185" t="n">
-        <v>125.36</v>
+        <v>762.34</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6187,28 +6187,28 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Novartis AG</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1551.18</v>
+        <v>2898.14</v>
       </c>
       <c r="F186" t="n">
-        <v>72.40000000000001</v>
+        <v>151.04</v>
       </c>
       <c r="G186" t="n">
-        <v>73.75</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6218,28 +6218,28 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1886.38</v>
+        <v>1442.79</v>
       </c>
       <c r="F187" t="n">
-        <v>103.92</v>
+        <v>532.25</v>
       </c>
       <c r="G187" t="n">
-        <v>105.81</v>
+        <v>537.26</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6249,28 +6249,28 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>Honeywell International Inc.</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1467.57</v>
+        <v>1533.46</v>
       </c>
       <c r="F188" t="n">
-        <v>634.22</v>
+        <v>227.56</v>
       </c>
       <c r="G188" t="n">
-        <v>645.67</v>
+        <v>229.59</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6280,28 +6280,28 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1431.27</v>
+        <v>1473.92</v>
       </c>
       <c r="F189" t="n">
-        <v>528</v>
+        <v>25.93</v>
       </c>
       <c r="G189" t="n">
-        <v>537.26</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6311,28 +6311,28 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Shell plc</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2178.98</v>
+        <v>1551.52</v>
       </c>
       <c r="F190" t="n">
-        <v>77.03</v>
+        <v>316.86</v>
       </c>
       <c r="G190" t="n">
-        <v>78.17</v>
+        <v>319.26</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6342,28 +6342,28 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NextEra Energy, Inc.</t>
+          <t>Cisco Systems, Inc.</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1830.61</v>
+        <v>3186.16</v>
       </c>
       <c r="F191" t="n">
-        <v>87.90000000000001</v>
+        <v>80.64</v>
       </c>
       <c r="G191" t="n">
-        <v>89.19</v>
+        <v>81.15000000000001</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6373,28 +6373,28 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc.</t>
+          <t>Electronic Arts Inc.</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2793.23</v>
+        <v>509.22</v>
       </c>
       <c r="F192" t="n">
-        <v>179.44</v>
+        <v>203.6</v>
       </c>
       <c r="G192" t="n">
-        <v>181.91</v>
+        <v>204.89</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6404,28 +6404,28 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc.</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1877.41</v>
+        <v>1772.99</v>
       </c>
       <c r="F193" t="n">
-        <v>44.52</v>
+        <v>142.89</v>
       </c>
       <c r="G193" t="n">
-        <v>45.13</v>
+        <v>143.79</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6435,28 +6435,28 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>The Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>40967.19</v>
+        <v>1909.07</v>
       </c>
       <c r="F194" t="n">
-        <v>338</v>
+        <v>105.17</v>
       </c>
       <c r="G194" t="n">
-        <v>342.29</v>
+        <v>105.81</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6466,28 +6466,28 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>PACCAR Inc</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5475.12</v>
+        <v>654.7</v>
       </c>
       <c r="F195" t="n">
-        <v>227.25</v>
+        <v>124.61</v>
       </c>
       <c r="G195" t="n">
-        <v>230</v>
+        <v>125.36</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6497,28 +6497,28 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>3021.55</v>
+        <v>3241.95</v>
       </c>
       <c r="F196" t="n">
-        <v>88.01000000000001</v>
+        <v>75.33</v>
       </c>
       <c r="G196" t="n">
-        <v>89</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6528,28 +6528,28 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>40866.78</v>
+        <v>1060.44</v>
       </c>
       <c r="F197" t="n">
-        <v>338.53</v>
+        <v>52.47</v>
       </c>
       <c r="G197" t="n">
-        <v>342.29</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6559,28 +6559,28 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>CME Group Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1039.21</v>
+        <v>41628.15</v>
       </c>
       <c r="F198" t="n">
-        <v>289.06</v>
+        <v>343.69</v>
       </c>
       <c r="G198" t="n">
-        <v>291.76</v>
+        <v>344.83</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6590,28 +6590,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Honeywell International Inc.</t>
+          <t>British American Tobacco p.l.c.</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1533.19</v>
+        <v>1323.42</v>
       </c>
       <c r="F199" t="n">
-        <v>227.52</v>
+        <v>60.99</v>
       </c>
       <c r="G199" t="n">
-        <v>229.59</v>
+        <v>61.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6621,28 +6621,28 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corporation</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5963.07</v>
+        <v>5559.45</v>
       </c>
       <c r="F200" t="n">
-        <v>141.4</v>
+        <v>230.75</v>
       </c>
       <c r="G200" t="n">
-        <v>142.34</v>
+        <v>231.19</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6652,28 +6652,28 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Electronic Arts Inc.</t>
+          <t>Walmart Inc.</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>510.02</v>
+        <v>9891.120000000001</v>
       </c>
       <c r="F201" t="n">
-        <v>203.92</v>
+        <v>124.06</v>
       </c>
       <c r="G201" t="n">
-        <v>204.89</v>
+        <v>124.2</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6683,28 +6683,28 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>British American Tobacco p.l.c.</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1316.7</v>
+        <v>2044.49</v>
       </c>
       <c r="F202" t="n">
-        <v>60.68</v>
+        <v>225.01</v>
       </c>
       <c r="G202" t="n">
-        <v>60.82</v>
+        <v>225.26</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6714,28 +6714,28 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3536.86</v>
+        <v>41635.75</v>
       </c>
       <c r="F203" t="n">
-        <v>176.9</v>
+        <v>344.9</v>
       </c>
       <c r="G203" t="n">
-        <v>177.3</v>
+        <v>345.17</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6745,28 +6745,28 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc.</t>
+          <t>Banco Santander, S.A.</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1761.33</v>
+        <v>1931.25</v>
       </c>
       <c r="F204" t="n">
-        <v>141.95</v>
+        <v>13.06</v>
       </c>
       <c r="G204" t="n">
-        <v>142.2</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6776,28 +6776,28 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>GSK plc</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1042.86</v>
+        <v>3236.77</v>
       </c>
       <c r="F205" t="n">
-        <v>51.6</v>
+        <v>690.91</v>
       </c>
       <c r="G205" t="n">
-        <v>51.69</v>
+        <v>691.38</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6807,17 +6807,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>HSBC Holdings plc</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>3219.57</v>
+        <v>3076.14</v>
       </c>
       <c r="F206" t="n">
-        <v>74.81</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G206" t="n">
-        <v>74.90000000000001</v>
+        <v>89.62</v>
       </c>
     </row>
   </sheetData>

--- a/美股回撤分析报告.xlsx
+++ b/美股回撤分析报告.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G206"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>83.09%</t>
+          <t>86.52%</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>499.95</v>
+        <v>398.39</v>
       </c>
       <c r="F2" t="n">
-        <v>52.33</v>
+        <v>41.7</v>
       </c>
       <c r="G2" t="n">
         <v>309.44</v>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>76.47%</t>
+          <t>78.27%</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>299.29</v>
+        <v>276.39</v>
       </c>
       <c r="F3" t="n">
-        <v>113.7</v>
+        <v>105</v>
       </c>
       <c r="G3" t="n">
         <v>483.13</v>
@@ -530,7 +530,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>74.29%</t>
+          <t>75.46%</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>404.01</v>
+        <v>385.58</v>
       </c>
       <c r="F4" t="n">
-        <v>139.63</v>
+        <v>133.26</v>
       </c>
       <c r="G4" t="n">
         <v>543</v>
@@ -561,7 +561,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>74.13%</t>
+          <t>74.23%</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>276.43</v>
+        <v>275.31</v>
       </c>
       <c r="F5" t="n">
-        <v>213.61</v>
+        <v>212.74</v>
       </c>
       <c r="G5" t="n">
         <v>825.62</v>
@@ -592,7 +592,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>69.61%</t>
+          <t>69.06%</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079.66</v>
+        <v>2106.15</v>
       </c>
       <c r="F6" t="n">
-        <v>116.23</v>
+        <v>117.71</v>
       </c>
       <c r="G6" t="n">
-        <v>382.43</v>
+        <v>380.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>64.78%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>682.35</v>
+        <v>674.17</v>
       </c>
       <c r="F7" t="n">
-        <v>27.52</v>
+        <v>27.19</v>
       </c>
       <c r="G7" t="n">
         <v>78.14</v>
@@ -654,12 +654,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>63.75%</t>
+          <t>64.98%</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -669,28 +669,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Kraft Heinz Company</t>
+          <t>Novo Nordisk A/S</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>278.16</v>
+        <v>2235.07</v>
       </c>
       <c r="F8" t="n">
-        <v>23.5</v>
+        <v>50.3</v>
       </c>
       <c r="G8" t="n">
-        <v>64.84</v>
+        <v>143.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>58.97%</t>
+          <t>63.18%</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -700,23 +700,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Novo Nordisk A/S</t>
+          <t>The Kraft Heinz Company</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2618.54</v>
+        <v>282.54</v>
       </c>
       <c r="F9" t="n">
-        <v>58.93</v>
+        <v>23.87</v>
       </c>
       <c r="G9" t="n">
-        <v>143.64</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>58.06%</t>
+          <t>61.13%</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1228.09</v>
+        <v>1138.3</v>
       </c>
       <c r="F10" t="n">
-        <v>293.38</v>
+        <v>271.93</v>
       </c>
       <c r="G10" t="n">
         <v>699.54</v>
@@ -747,12 +747,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>56.01%</t>
+          <t>57.57%</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -762,28 +762,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>Thomson Reuters Corporation</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>284.43</v>
+        <v>415.64</v>
       </c>
       <c r="F11" t="n">
-        <v>72.53</v>
+        <v>91.95</v>
       </c>
       <c r="G11" t="n">
-        <v>164.86</v>
+        <v>216.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>56.55%</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -793,28 +793,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4598.73</v>
+        <v>280.9</v>
       </c>
       <c r="F12" t="n">
-        <v>160.06</v>
+        <v>71.63</v>
       </c>
       <c r="G12" t="n">
-        <v>344.21</v>
+        <v>164.86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>53.43%</t>
+          <t>55.07%</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -824,28 +824,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UnitedHealth Group Incorporated</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2586.98</v>
+        <v>4445.36</v>
       </c>
       <c r="F13" t="n">
-        <v>285.59</v>
+        <v>154.67</v>
       </c>
       <c r="G13" t="n">
-        <v>613.22</v>
+        <v>344.21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51.34%</t>
+          <t>54.19%</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -855,28 +855,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1468.62</v>
+        <v>1158.23</v>
       </c>
       <c r="F14" t="n">
-        <v>103.45</v>
+        <v>109.77</v>
       </c>
       <c r="G14" t="n">
-        <v>212.6</v>
+        <v>239.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50.75%</t>
+          <t>53.66%</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -886,28 +886,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>UnitedHealth Group Incorporated</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1245.07</v>
+        <v>2574.21</v>
       </c>
       <c r="F15" t="n">
-        <v>118</v>
+        <v>284.18</v>
       </c>
       <c r="G15" t="n">
-        <v>239.62</v>
+        <v>613.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49.69%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -917,90 +917,90 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thomson Reuters Corporation</t>
+          <t>PDD Holdings Inc.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>492.85</v>
+        <v>1466.78</v>
       </c>
       <c r="F16" t="n">
-        <v>109.03</v>
+        <v>103.32</v>
       </c>
       <c r="G16" t="n">
-        <v>216.72</v>
+        <v>212.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>48.08%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>Zscaler, Inc.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>365.4</v>
+        <v>299.89</v>
       </c>
       <c r="F17" t="n">
-        <v>459.99</v>
+        <v>188.05</v>
       </c>
       <c r="G17" t="n">
-        <v>885.92</v>
+        <v>376.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>47.34%</t>
+          <t>49.06%</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1864.73</v>
+        <v>358.49</v>
       </c>
       <c r="F18" t="n">
-        <v>104.45</v>
+        <v>451.29</v>
       </c>
       <c r="G18" t="n">
-        <v>198.35</v>
+        <v>885.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>46.66%</t>
+          <t>48.81%</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1010,28 +1010,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Zscaler, Inc.</t>
+          <t>CoStar Group, Inc.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>319.92</v>
+        <v>219.24</v>
       </c>
       <c r="F19" t="n">
-        <v>200.61</v>
+        <v>51.73</v>
       </c>
       <c r="G19" t="n">
-        <v>376.11</v>
+        <v>101.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>48.22%</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1041,23 +1041,23 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>The Boeing Company</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1824.71</v>
+        <v>430.32</v>
       </c>
       <c r="F20" t="n">
-        <v>233.02</v>
+        <v>161.17</v>
       </c>
       <c r="G20" t="n">
-        <v>435.56</v>
+        <v>311.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>46.05%</t>
+          <t>47.85%</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1515.81</v>
+        <v>1465.21</v>
       </c>
       <c r="F21" t="n">
-        <v>26.66</v>
+        <v>25.77</v>
       </c>
       <c r="G21" t="n">
         <v>49.42</v>
@@ -1088,12 +1088,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>44.47%</t>
+          <t>47.46%</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1103,28 +1103,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Limited</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4020.02</v>
+        <v>1848.22</v>
       </c>
       <c r="F22" t="n">
-        <v>168.39</v>
+        <v>104.22</v>
       </c>
       <c r="G22" t="n">
-        <v>303.26</v>
+        <v>198.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>46.47%</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1134,28 +1134,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>The Boeing Company</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>462.92</v>
+        <v>1831.04</v>
       </c>
       <c r="F23" t="n">
-        <v>173.38</v>
+        <v>233.15</v>
       </c>
       <c r="G23" t="n">
-        <v>311.28</v>
+        <v>435.56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43.35%</t>
+          <t>46.46%</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1165,23 +1165,23 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1134.53</v>
+        <v>1208.51</v>
       </c>
       <c r="F24" t="n">
-        <v>106.93</v>
+        <v>434.09</v>
       </c>
       <c r="G24" t="n">
-        <v>188.75</v>
+        <v>810.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>42.43%</t>
+          <t>46.37%</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2006.91</v>
+        <v>1869.54</v>
       </c>
       <c r="F25" t="n">
-        <v>210.81</v>
+        <v>196.38</v>
       </c>
       <c r="G25" t="n">
         <v>366.19</v>
@@ -1212,12 +1212,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>41.36%</t>
+          <t>46.04%</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1227,28 +1227,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Comcast Corporation</t>
+          <t>Alibaba Group Holding Limited</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1166.19</v>
+        <v>3906.86</v>
       </c>
       <c r="F26" t="n">
-        <v>29.59</v>
+        <v>163.65</v>
       </c>
       <c r="G26" t="n">
-        <v>50.46</v>
+        <v>303.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>44.61%</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1258,28 +1258,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Airbnb, Inc.</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>803.9299999999999</v>
+        <v>1109.27</v>
       </c>
       <c r="F27" t="n">
-        <v>131.31</v>
+        <v>104.55</v>
       </c>
       <c r="G27" t="n">
-        <v>219.94</v>
+        <v>188.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>39.92%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1289,28 +1289,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>Airbnb, Inc.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1356.14</v>
+        <v>747.39</v>
       </c>
       <c r="F28" t="n">
-        <v>487.12</v>
+        <v>122.07</v>
       </c>
       <c r="G28" t="n">
-        <v>810.72</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>39.46%</t>
+          <t>41.02%</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1320,28 +1320,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CoStar Group, Inc.</t>
+          <t>Comcast Corporation</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>259.29</v>
+        <v>1172.89</v>
       </c>
       <c r="F29" t="n">
-        <v>61.18</v>
+        <v>29.76</v>
       </c>
       <c r="G29" t="n">
-        <v>101.05</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>38.37%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1351,28 +1351,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Copart, Inc.</t>
+          <t>Roper Technologies, Inc.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>384.11</v>
+        <v>375.46</v>
       </c>
       <c r="F30" t="n">
-        <v>39.68</v>
+        <v>348.82</v>
       </c>
       <c r="G30" t="n">
-        <v>64.38</v>
+        <v>591.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>38.29%</t>
+          <t>40.67%</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1382,23 +1382,23 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3510.59</v>
+        <v>419.61</v>
       </c>
       <c r="F31" t="n">
-        <v>82.76000000000001</v>
+        <v>119.66</v>
       </c>
       <c r="G31" t="n">
-        <v>134.12</v>
+        <v>201.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>38.09%</t>
+          <t>40.55%</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>678.13</v>
+        <v>651.23</v>
       </c>
       <c r="F32" t="n">
-        <v>78.66</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>127.06</v>
@@ -1429,12 +1429,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>37.32%</t>
+          <t>40.39%</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1444,28 +1444,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>800.23</v>
+        <v>3390.97</v>
       </c>
       <c r="F33" t="n">
-        <v>755.02</v>
+        <v>79.94</v>
       </c>
       <c r="G33" t="n">
-        <v>1204.52</v>
+        <v>134.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>37.21%</t>
+          <t>40.08%</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MFG</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1475,28 +1475,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mizuho Financial Group, Inc.</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1093.85</v>
+        <v>268.94</v>
       </c>
       <c r="F34" t="n">
-        <v>8.84</v>
+        <v>192.49</v>
       </c>
       <c r="G34" t="n">
-        <v>14.08</v>
+        <v>321.24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>36.98%</t>
+          <t>39.52%</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1506,28 +1506,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Roper Technologies, Inc.</t>
+          <t>Copart, Inc.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>401.07</v>
+        <v>376.95</v>
       </c>
       <c r="F35" t="n">
-        <v>372.61</v>
+        <v>38.94</v>
       </c>
       <c r="G35" t="n">
-        <v>591.26</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36.02%</t>
+          <t>38.84%</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1537,28 +1537,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>452.54</v>
+        <v>1495.84</v>
       </c>
       <c r="F36" t="n">
-        <v>129.05</v>
+        <v>241.21</v>
       </c>
       <c r="G36" t="n">
-        <v>201.69</v>
+        <v>394.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>35.97%</t>
+          <t>38.07%</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BUD</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1568,23 +1568,23 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Anheuser-Busch InBev SA/NV</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1408.48</v>
+        <v>348.74</v>
       </c>
       <c r="F37" t="n">
-        <v>72.45</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>113.15</v>
+        <v>156.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>35.22%</t>
+          <t>38.07%</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1633.75</v>
+        <v>1562</v>
       </c>
       <c r="F38" t="n">
-        <v>483</v>
+        <v>461.79</v>
       </c>
       <c r="G38" t="n">
         <v>745.61</v>
@@ -1615,12 +1615,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>35.21%</t>
+          <t>37.02%</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1630,28 +1630,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Spotify Technology S.A.</t>
+          <t>SAP SE</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1047.14</v>
+        <v>2301.97</v>
       </c>
       <c r="F39" t="n">
-        <v>508.58</v>
+        <v>197.29</v>
       </c>
       <c r="G39" t="n">
-        <v>785</v>
+        <v>313.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34.68%</t>
+          <t>36.97%</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1661,28 +1661,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>367.83</v>
+        <v>804.64</v>
       </c>
       <c r="F40" t="n">
-        <v>102.47</v>
+        <v>759.1799999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>156.86</v>
+        <v>1204.52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34.29%</t>
+          <t>36.85%</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>MFG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1692,28 +1692,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Constellation Energy Corporation</t>
+          <t>Mizuho Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>981.37</v>
+        <v>1093.92</v>
       </c>
       <c r="F41" t="n">
-        <v>270.88</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>412.23</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>33.85%</t>
+          <t>35.69%</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1723,28 +1723,28 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2417.95</v>
+        <v>801.89</v>
       </c>
       <c r="F42" t="n">
-        <v>207.23</v>
+        <v>419.14</v>
       </c>
       <c r="G42" t="n">
-        <v>313.28</v>
+        <v>651.73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>33.34%</t>
+          <t>35.01%</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1754,28 +1754,28 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Anheuser-Busch InBev SA/NV</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>299.2</v>
+        <v>1429.47</v>
       </c>
       <c r="F43" t="n">
-        <v>214.15</v>
+        <v>73.53</v>
       </c>
       <c r="G43" t="n">
-        <v>321.24</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>32.51%</t>
+          <t>34.88%</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1785,28 +1785,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc.</t>
+          <t>Constellation Energy Corporation</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1058.88</v>
+        <v>972.5700000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>114.36</v>
+        <v>268.45</v>
       </c>
       <c r="G44" t="n">
-        <v>169.44</v>
+        <v>412.23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>32.36%</t>
+          <t>34.52%</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1816,23 +1816,23 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1654.47</v>
+        <v>1556.83</v>
       </c>
       <c r="F45" t="n">
-        <v>266.79</v>
+        <v>119.29</v>
       </c>
       <c r="G45" t="n">
-        <v>394.41</v>
+        <v>182.19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>31.64%</t>
+          <t>34.07%</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1634.56</v>
+        <v>1576.3</v>
       </c>
       <c r="F46" t="n">
-        <v>152.62</v>
+        <v>147.18</v>
       </c>
       <c r="G46" t="n">
         <v>223.25</v>
@@ -1863,43 +1863,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>31.57%</t>
+          <t>30.94%</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ALNY</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Alnylam Pharmaceuticals, Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>448.01</v>
+        <v>607.65</v>
       </c>
       <c r="F47" t="n">
-        <v>339.11</v>
+        <v>79.3</v>
       </c>
       <c r="G47" t="n">
-        <v>495.55</v>
+        <v>114.82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29.74%</t>
+          <t>30.08%</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1909,28 +1909,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>876.03</v>
+        <v>512.88</v>
       </c>
       <c r="F48" t="n">
-        <v>457.89</v>
+        <v>240.79</v>
       </c>
       <c r="G48" t="n">
-        <v>651.73</v>
+        <v>344.39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.25%</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1940,28 +1940,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>622.9</v>
+        <v>870.62</v>
       </c>
       <c r="F49" t="n">
-        <v>81.29000000000001</v>
+        <v>202</v>
       </c>
       <c r="G49" t="n">
-        <v>114.82</v>
+        <v>285.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.01%</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ALNY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1971,28 +1971,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Alnylam Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3521.77</v>
+        <v>464.78</v>
       </c>
       <c r="F50" t="n">
-        <v>147.76</v>
+        <v>351.8</v>
       </c>
       <c r="G50" t="n">
-        <v>207.52</v>
+        <v>495.55</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>28.61%</t>
+          <t>28.68%</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2002,59 +2002,59 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>T-Mobile US, Inc.</t>
+          <t>Cadence Design Systems, Inc.</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2194.45</v>
+        <v>731.64</v>
       </c>
       <c r="F51" t="n">
-        <v>194.99</v>
+        <v>268.5</v>
       </c>
       <c r="G51" t="n">
-        <v>273.15</v>
+        <v>376.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27.62%</t>
+          <t>27.72%</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>SONY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Insmed Incorporated</t>
+          <t>Sony Group Corporation</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>328.4</v>
+        <v>1317.39</v>
       </c>
       <c r="F52" t="n">
-        <v>153.98</v>
+        <v>21.93</v>
       </c>
       <c r="G52" t="n">
-        <v>212.75</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27.53%</t>
+          <t>27.63%</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2064,28 +2064,28 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>T-Mobile US, Inc.</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1785.97</v>
+        <v>2224.73</v>
       </c>
       <c r="F53" t="n">
-        <v>141.28</v>
+        <v>197.68</v>
       </c>
       <c r="G53" t="n">
-        <v>194.94</v>
+        <v>273.15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27.44%</t>
+          <t>27.56%</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2095,28 +2095,28 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Automatic Data Processing, Inc.</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1721.04</v>
+        <v>950.78</v>
       </c>
       <c r="F54" t="n">
-        <v>132.2</v>
+        <v>235.08</v>
       </c>
       <c r="G54" t="n">
-        <v>182.19</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27.26%</t>
+          <t>26.94%</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2126,59 +2126,59 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>The Progressive Corporation</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>895.05</v>
+        <v>1178.44</v>
       </c>
       <c r="F55" t="n">
-        <v>207.67</v>
+        <v>201.03</v>
       </c>
       <c r="G55" t="n">
-        <v>285.5</v>
+        <v>275.18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.09%</t>
+          <t>26.13%</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SONY</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sony Group Corporation</t>
+          <t>Insmed Incorporated</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1328.8</v>
+        <v>335.18</v>
       </c>
       <c r="F56" t="n">
-        <v>22.12</v>
+        <v>157.16</v>
       </c>
       <c r="G56" t="n">
-        <v>30.34</v>
+        <v>212.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26.92%</t>
+          <t>25.71%</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2188,28 +2188,28 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>373.2</v>
+        <v>30534.93</v>
       </c>
       <c r="F57" t="n">
-        <v>27.47</v>
+        <v>411.21</v>
       </c>
       <c r="G57" t="n">
-        <v>37.59</v>
+        <v>553.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>26.21%</t>
+          <t>25.66%</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2219,28 +2219,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>The Progressive Corporation</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1190.22</v>
+        <v>1137.05</v>
       </c>
       <c r="F58" t="n">
-        <v>203.04</v>
+        <v>166.24</v>
       </c>
       <c r="G58" t="n">
-        <v>275.18</v>
+        <v>223.61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>25.79%</t>
+          <t>25.61%</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2250,28 +2250,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>544.36</v>
+        <v>1063.17</v>
       </c>
       <c r="F59" t="n">
-        <v>255.57</v>
+        <v>421.73</v>
       </c>
       <c r="G59" t="n">
-        <v>344.39</v>
+        <v>566.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23.71%</t>
+          <t>25.59%</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2281,28 +2281,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Automatic Data Processing, Inc.</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1001.25</v>
+        <v>380</v>
       </c>
       <c r="F60" t="n">
-        <v>247.56</v>
+        <v>27.97</v>
       </c>
       <c r="G60" t="n">
-        <v>324.5</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>23.51%</t>
+          <t>25.35%</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2312,59 +2312,59 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>31437.89</v>
+        <v>1531.15</v>
       </c>
       <c r="F61" t="n">
-        <v>423.37</v>
+        <v>216.6</v>
       </c>
       <c r="G61" t="n">
-        <v>553.5</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>23.18%</t>
+          <t>23.92%</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cadence Design Systems, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>788.01</v>
+        <v>3762.97</v>
       </c>
       <c r="F62" t="n">
-        <v>289.19</v>
+        <v>157.88</v>
       </c>
       <c r="G62" t="n">
-        <v>376.45</v>
+        <v>207.52</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.59%</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2374,28 +2374,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1579.36</v>
+        <v>1625.17</v>
       </c>
       <c r="F63" t="n">
-        <v>223.42</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>290.14</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22.64%</t>
+          <t>23.39%</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Diamondback Energy, Inc.</t>
+          <t>NXP Semiconductors N.V.</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>459.24</v>
+        <v>556.3200000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>158.64</v>
+        <v>220.66</v>
       </c>
       <c r="G64" t="n">
-        <v>205.08</v>
+        <v>288.03</v>
       </c>
     </row>
     <row r="65">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2436,28 +2436,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1106.33</v>
+        <v>15187.72</v>
       </c>
       <c r="F65" t="n">
-        <v>438.85</v>
+        <v>320.33</v>
       </c>
       <c r="G65" t="n">
-        <v>566.9</v>
+        <v>413.82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21.64%</t>
+          <t>22.26%</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2467,28 +2467,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Intuitive Surgical, Inc.</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2438.15</v>
+        <v>1716.67</v>
       </c>
       <c r="F66" t="n">
-        <v>48.81</v>
+        <v>478.88</v>
       </c>
       <c r="G66" t="n">
-        <v>62.29</v>
+        <v>616</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21.55%</t>
+          <t>21.36%</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2498,28 +2498,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1222.68</v>
+        <v>1897.45</v>
       </c>
       <c r="F67" t="n">
-        <v>175.42</v>
+        <v>109.02</v>
       </c>
       <c r="G67" t="n">
-        <v>223.61</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21.08%</t>
+          <t>20.94%</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2529,28 +2529,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1904.24</v>
+        <v>2460.13</v>
       </c>
       <c r="F68" t="n">
-        <v>109.41</v>
+        <v>49.25</v>
       </c>
       <c r="G68" t="n">
-        <v>138.63</v>
+        <v>62.29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20.74%</t>
+          <t>20.62%</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2560,28 +2560,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>MercadoLibre, Inc.</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1685.85</v>
+        <v>1064.59</v>
       </c>
       <c r="F69" t="n">
-        <v>80.84</v>
+        <v>2099.9</v>
       </c>
       <c r="G69" t="n">
-        <v>101.99</v>
+        <v>2645.22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.58%</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2591,28 +2591,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Company</t>
+          <t>Diamondback Energy, Inc.</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1137.78</v>
+        <v>471.52</v>
       </c>
       <c r="F70" t="n">
-        <v>55.89</v>
+        <v>162.88</v>
       </c>
       <c r="G70" t="n">
-        <v>70.48</v>
+        <v>205.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20.48%</t>
+          <t>20.55%</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2622,28 +2622,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Bristol-Myers Squibb Company</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1271.3</v>
+        <v>1139.82</v>
       </c>
       <c r="F71" t="n">
-        <v>101.79</v>
+        <v>55.99</v>
       </c>
       <c r="G71" t="n">
-        <v>128.01</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.39%</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2653,28 +2653,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Starbucks Corporation</t>
+          <t>Microchip Technology Incorporated</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1044.62</v>
+        <v>414.31</v>
       </c>
       <c r="F72" t="n">
-        <v>91.69</v>
+        <v>76.66</v>
       </c>
       <c r="G72" t="n">
-        <v>115.04</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>19.99%</t>
+          <t>20.17%</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2684,28 +2684,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>Booking Holdings Inc.</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>15698.83</v>
+        <v>1505.32</v>
       </c>
       <c r="F73" t="n">
-        <v>331.11</v>
+        <v>4644.64</v>
       </c>
       <c r="G73" t="n">
-        <v>413.82</v>
+        <v>5818.24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>19.77%</t>
+          <t>19.95%</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2715,28 +2715,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NXP Semiconductors N.V.</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>582.59</v>
+        <v>1781.08</v>
       </c>
       <c r="F74" t="n">
-        <v>231.08</v>
+        <v>1355.54</v>
       </c>
       <c r="G74" t="n">
-        <v>288.03</v>
+        <v>1693.35</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>19.53%</t>
+          <t>19.87%</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2746,28 +2746,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Old Dominion Freight Line, Inc.</t>
+          <t>Take-Two Interactive Software, Inc.</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>391.19</v>
+        <v>392.05</v>
       </c>
       <c r="F75" t="n">
-        <v>186.13</v>
+        <v>212.17</v>
       </c>
       <c r="G75" t="n">
-        <v>231.32</v>
+        <v>264.79</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>19.49%</t>
+          <t>19.13%</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2777,28 +2777,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mondelez International, Inc.</t>
+          <t>Starbucks Corporation</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>759.42</v>
+        <v>1060</v>
       </c>
       <c r="F76" t="n">
-        <v>58.69</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>72.90000000000001</v>
+        <v>115.04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>19.36%</t>
+          <t>18.84%</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2808,28 +2808,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Intuitive Surgical, Inc.</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1780.66</v>
+        <v>1429.45</v>
       </c>
       <c r="F77" t="n">
-        <v>496.73</v>
+        <v>468.21</v>
       </c>
       <c r="G77" t="n">
-        <v>616</v>
+        <v>576.91</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>18.92%</t>
+          <t>18.42%</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2839,28 +2839,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Microchip Technology Incorporated</t>
+          <t>Mondelez International, Inc.</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>421.98</v>
+        <v>769.51</v>
       </c>
       <c r="F78" t="n">
-        <v>78.08</v>
+        <v>59.47</v>
       </c>
       <c r="G78" t="n">
-        <v>96.3</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>18.83%</t>
+          <t>18.04%</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2870,28 +2870,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>MercadoLibre, Inc.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1088.58</v>
+        <v>1310.27</v>
       </c>
       <c r="F79" t="n">
-        <v>2147.22</v>
+        <v>104.91</v>
       </c>
       <c r="G79" t="n">
-        <v>2645.22</v>
+        <v>128.01</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>18.13%</t>
+          <t>17.96%</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2901,28 +2901,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Financial Group, Inc.</t>
+          <t>Old Dominion Freight Line, Inc.</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1354.46</v>
+        <v>398.84</v>
       </c>
       <c r="F80" t="n">
-        <v>21.1</v>
+        <v>189.77</v>
       </c>
       <c r="G80" t="n">
-        <v>25.77</v>
+        <v>231.32</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>17.89%</t>
+          <t>17.85%</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2932,28 +2932,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>IDEXX Laboratories, Inc.</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1148.14</v>
+        <v>506.08</v>
       </c>
       <c r="F81" t="n">
-        <v>47.27</v>
+        <v>632.5599999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>57.57</v>
+        <v>769.98</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>16.93%</t>
+          <t>17.51%</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2963,28 +2963,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories, Inc.</t>
+          <t>Sanofi</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>511.71</v>
+        <v>1153.48</v>
       </c>
       <c r="F82" t="n">
-        <v>639.6</v>
+        <v>47.49</v>
       </c>
       <c r="G82" t="n">
-        <v>769.98</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>16.71%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2994,28 +2994,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Sumitomo Mitsui Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1857.34</v>
+        <v>1357.51</v>
       </c>
       <c r="F83" t="n">
-        <v>1410.45</v>
+        <v>21.34</v>
       </c>
       <c r="G83" t="n">
-        <v>1693.35</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>16.64%</t>
+          <t>16.75%</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3025,28 +3025,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Prologis, Inc.</t>
+          <t>GE HealthCare Technologies Inc.</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1204.55</v>
+        <v>359.68</v>
       </c>
       <c r="F84" t="n">
-        <v>129.68</v>
+        <v>78.78</v>
       </c>
       <c r="G84" t="n">
-        <v>155.57</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>16.35%</t>
+          <t>16.64%</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3056,28 +3056,28 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>767.2</v>
+        <v>363.85</v>
       </c>
       <c r="F85" t="n">
-        <v>190.91</v>
+        <v>74.5</v>
       </c>
       <c r="G85" t="n">
-        <v>228.23</v>
+        <v>89.37</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16.33%</t>
+          <t>16.43%</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1239.6</v>
+        <v>766.48</v>
       </c>
       <c r="F86" t="n">
-        <v>112.85</v>
+        <v>190.73</v>
       </c>
       <c r="G86" t="n">
-        <v>134.88</v>
+        <v>228.23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>16.23%</t>
+          <t>16.33%</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3118,23 +3118,23 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software, Inc.</t>
+          <t>Boston Scientific Corporation</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>409.86</v>
+        <v>1358.74</v>
       </c>
       <c r="F87" t="n">
-        <v>221.81</v>
+        <v>91.62</v>
       </c>
       <c r="G87" t="n">
-        <v>264.79</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>16.11%</t>
+          <t>15.49%</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1742.47</v>
+        <v>1755.32</v>
       </c>
       <c r="F88" t="n">
-        <v>138.37</v>
+        <v>139.39</v>
       </c>
       <c r="G88" t="n">
         <v>164.94</v>
@@ -3165,12 +3165,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.41%</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3180,28 +3180,28 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Boston Scientific Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1362.45</v>
+        <v>15833.76</v>
       </c>
       <c r="F89" t="n">
-        <v>91.87</v>
+        <v>421.96</v>
       </c>
       <c r="G89" t="n">
-        <v>109.5</v>
+        <v>498.83</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>15.44%</t>
+          <t>15.23%</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3211,28 +3211,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Prologis, Inc.</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>15828.13</v>
+        <v>1224.99</v>
       </c>
       <c r="F90" t="n">
-        <v>421.81</v>
+        <v>131.88</v>
       </c>
       <c r="G90" t="n">
-        <v>498.83</v>
+        <v>155.57</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15.34%</t>
+          <t>15.01%</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3242,23 +3242,23 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GE HealthCare Technologies Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>365.75</v>
+        <v>43907.38</v>
       </c>
       <c r="F91" t="n">
-        <v>80.11</v>
+        <v>180.34</v>
       </c>
       <c r="G91" t="n">
-        <v>94.63</v>
+        <v>212.18</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14.11%</t>
+          <t>14.67%</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1733.2</v>
+        <v>1721.92</v>
       </c>
       <c r="F92" t="n">
-        <v>33.79</v>
+        <v>33.57</v>
       </c>
       <c r="G92" t="n">
         <v>39.34</v>
@@ -3289,12 +3289,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>13.85%</t>
+          <t>14.26%</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3304,28 +3304,28 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Capital One Financial Corporation</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1422.01</v>
+        <v>2141.87</v>
       </c>
       <c r="F93" t="n">
-        <v>223.68</v>
+        <v>570.09</v>
       </c>
       <c r="G93" t="n">
-        <v>259.64</v>
+        <v>664.9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>13.73%</t>
+          <t>13.98%</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3335,28 +3335,28 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>Capital One Financial Corporation</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1317.37</v>
+        <v>1419.85</v>
       </c>
       <c r="F94" t="n">
-        <v>102.71</v>
+        <v>223.34</v>
       </c>
       <c r="G94" t="n">
-        <v>119.06</v>
+        <v>259.64</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13.55%</t>
+          <t>13.34%</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3366,28 +3366,28 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PepsiCo, Inc.</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2124.81</v>
+        <v>1323.4</v>
       </c>
       <c r="F95" t="n">
-        <v>155.2</v>
+        <v>103.18</v>
       </c>
       <c r="G95" t="n">
-        <v>179.53</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13.24%</t>
+          <t>13.15%</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3397,28 +3397,28 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1774.02</v>
+        <v>1286.72</v>
       </c>
       <c r="F96" t="n">
-        <v>144.93</v>
+        <v>117.14</v>
       </c>
       <c r="G96" t="n">
-        <v>167.04</v>
+        <v>134.88</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12.55%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3428,28 +3428,28 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>The Procter &amp; Gamble Company</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3579.64</v>
+        <v>17496.93</v>
       </c>
       <c r="F97" t="n">
-        <v>153.19</v>
+        <v>691.7</v>
       </c>
       <c r="G97" t="n">
-        <v>175.18</v>
+        <v>795.0599999999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>12.52%</t>
+          <t>12.08%</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3459,28 +3459,28 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>45190.47</v>
+        <v>6326.06</v>
       </c>
       <c r="F98" t="n">
-        <v>185.61</v>
+        <v>328.93</v>
       </c>
       <c r="G98" t="n">
-        <v>212.18</v>
+        <v>374.11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.96%</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3490,28 +3490,28 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2185.76</v>
+        <v>1800.1</v>
       </c>
       <c r="F99" t="n">
-        <v>581.77</v>
+        <v>147.06</v>
       </c>
       <c r="G99" t="n">
-        <v>664.9</v>
+        <v>167.04</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>11.96%</t>
+          <t>11.86%</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3521,28 +3521,28 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc.</t>
+          <t>BlackRock, Inc.</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1660.12</v>
+        <v>1660.24</v>
       </c>
       <c r="F100" t="n">
-        <v>5122.25</v>
+        <v>1070.08</v>
       </c>
       <c r="G100" t="n">
-        <v>5818.24</v>
+        <v>1214.03</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>11.89%</t>
+          <t>11.51%</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SCCO</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Southern Copper Corporation</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1579.22</v>
+        <v>8995.59</v>
       </c>
       <c r="F101" t="n">
-        <v>192.8</v>
+        <v>1003.46</v>
       </c>
       <c r="G101" t="n">
-        <v>218.81</v>
+        <v>1133.95</v>
       </c>
     </row>
     <row r="102">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3583,28 +3583,28 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Merck &amp; Co., Inc.</t>
+          <t>The Procter &amp; Gamble Company</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2831.74</v>
+        <v>3635.24</v>
       </c>
       <c r="F102" t="n">
-        <v>113.37</v>
+        <v>155.32</v>
       </c>
       <c r="G102" t="n">
-        <v>127.87</v>
+        <v>175.18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>11.33%</t>
+          <t>11.19%</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>IBN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3614,28 +3614,28 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>The Home Depot, Inc.</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3764.23</v>
+        <v>1098.19</v>
       </c>
       <c r="F103" t="n">
-        <v>378.12</v>
+        <v>30.46</v>
       </c>
       <c r="G103" t="n">
-        <v>426.44</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>11.15%</t>
+          <t>10.69%</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3645,28 +3645,28 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>O'Reilly Automotive, Inc.</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>17869.03</v>
+        <v>821.5</v>
       </c>
       <c r="F104" t="n">
-        <v>706.41</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G104" t="n">
-        <v>795.0599999999999</v>
+        <v>108.72</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10.76%</t>
+          <t>10.63%</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3676,28 +3676,28 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>The Home Depot, Inc.</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6436.57</v>
+        <v>3793.89</v>
       </c>
       <c r="F105" t="n">
-        <v>333.84</v>
+        <v>381.1</v>
       </c>
       <c r="G105" t="n">
-        <v>374.11</v>
+        <v>426.44</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10.56%</t>
+          <t>10.45%</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3707,28 +3707,28 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>514.33</v>
+        <v>1379.86</v>
       </c>
       <c r="F106" t="n">
-        <v>44.8</v>
+        <v>360.82</v>
       </c>
       <c r="G106" t="n">
-        <v>50.09</v>
+        <v>402.95</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10.35%</t>
+          <t>10.44%</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IBN</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3738,23 +3738,23 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108.64</v>
+        <v>1193.78</v>
       </c>
       <c r="F107" t="n">
-        <v>30.75</v>
+        <v>465.61</v>
       </c>
       <c r="G107" t="n">
-        <v>34.3</v>
+        <v>519.88</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10.34%</t>
+          <t>10.31%</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1286.38</v>
+        <v>1286.87</v>
       </c>
       <c r="F108" t="n">
-        <v>187.43</v>
+        <v>187.5</v>
       </c>
       <c r="G108" t="n">
         <v>209.05</v>
@@ -3785,12 +3785,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9.85%</t>
+          <t>9.97%</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>BN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3800,28 +3800,28 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>O'Reilly Automotive, Inc.</t>
+          <t>Brookfield Corporation</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>829.2</v>
+        <v>1002.95</v>
       </c>
       <c r="F109" t="n">
-        <v>98.01000000000001</v>
+        <v>44.63</v>
       </c>
       <c r="G109" t="n">
-        <v>108.72</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9.78%</t>
+          <t>9.57%</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3831,28 +3831,28 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Eaton Corporation plc</t>
+          <t>American Express Company</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1399.3</v>
+        <v>2408.43</v>
       </c>
       <c r="F110" t="n">
-        <v>359.44</v>
+        <v>349.63</v>
       </c>
       <c r="G110" t="n">
-        <v>398.4</v>
+        <v>386.63</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>9.72%</t>
+          <t>9.42%</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3862,28 +3862,28 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc.</t>
+          <t>International Business Machines Corporation</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1864.53</v>
+        <v>2751.02</v>
       </c>
       <c r="F111" t="n">
-        <v>26.3</v>
+        <v>294.31</v>
       </c>
       <c r="G111" t="n">
-        <v>29.13</v>
+        <v>324.9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.41%</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3893,28 +3893,28 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>Merck &amp; Co., Inc.</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4299.11</v>
+        <v>2893.43</v>
       </c>
       <c r="F112" t="n">
-        <v>968.36</v>
+        <v>115.84</v>
       </c>
       <c r="G112" t="n">
-        <v>1072.35</v>
+        <v>127.87</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>9.56%</t>
+          <t>9.35%</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3924,28 +3924,28 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Xcel Energy Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>440.7</v>
+        <v>3941.65</v>
       </c>
       <c r="F113" t="n">
-        <v>74.5</v>
+        <v>242.11</v>
       </c>
       <c r="G113" t="n">
-        <v>82.37</v>
+        <v>267.08</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9.21%</t>
+          <t>9.29%</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3955,28 +3955,28 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals Incorporated</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1210.19</v>
+        <v>2229.54</v>
       </c>
       <c r="F114" t="n">
-        <v>472.01</v>
+        <v>162.85</v>
       </c>
       <c r="G114" t="n">
-        <v>519.88</v>
+        <v>179.53</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8.74%</t>
+          <t>9.18%</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SATA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3986,28 +3986,28 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>American Express Company</t>
+          <t>Strive Asset Management, LLC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2430.48</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>352.83</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="G115" t="n">
-        <v>386.63</v>
+        <v>100.27</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8.69%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4017,28 +4017,28 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Exelon Corporation</t>
+          <t>Eaton Corporation plc</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>443.49</v>
+        <v>1411.33</v>
       </c>
       <c r="F116" t="n">
-        <v>43.91</v>
+        <v>362.53</v>
       </c>
       <c r="G116" t="n">
-        <v>48.09</v>
+        <v>398.4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8.64%</t>
+          <t>8.81%</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4048,28 +4048,28 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1407.85</v>
+        <v>4341.55</v>
       </c>
       <c r="F117" t="n">
-        <v>368.14</v>
+        <v>977.92</v>
       </c>
       <c r="G117" t="n">
-        <v>402.95</v>
+        <v>1072.35</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8.54%</t>
+          <t>8.64%</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4079,28 +4079,28 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc.</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1610.95</v>
+        <v>2890.13</v>
       </c>
       <c r="F118" t="n">
-        <v>527.66</v>
+        <v>230.1</v>
       </c>
       <c r="G118" t="n">
-        <v>576.91</v>
+        <v>251.87</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8.26%</t>
+          <t>8.48%</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4110,28 +4110,28 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Exelon Corporation</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8388.379999999999</v>
+        <v>444.5</v>
       </c>
       <c r="F119" t="n">
-        <v>308.14</v>
+        <v>44.01</v>
       </c>
       <c r="G119" t="n">
-        <v>335.87</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7.92%</t>
+          <t>8.22%</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4141,28 +4141,28 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9360.17</v>
+        <v>4920.34</v>
       </c>
       <c r="F120" t="n">
-        <v>1044.13</v>
+        <v>550.72</v>
       </c>
       <c r="G120" t="n">
-        <v>1133.95</v>
+        <v>600.08</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>7.91%</t>
+          <t>7.92%</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4172,28 +4172,28 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1395.29</v>
+        <v>4720.84</v>
       </c>
       <c r="F121" t="n">
-        <v>235.23</v>
+        <v>419.44</v>
       </c>
       <c r="G121" t="n">
-        <v>255.44</v>
+        <v>455.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7.79%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4203,28 +4203,28 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>AT&amp;T Inc.</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4009.38</v>
+        <v>1902.1</v>
       </c>
       <c r="F122" t="n">
-        <v>246.27</v>
+        <v>26.83</v>
       </c>
       <c r="G122" t="n">
-        <v>267.08</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7.77%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4234,28 +4234,28 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>BlackRock, Inc.</t>
+          <t>Xcel Energy Inc.</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1737.16</v>
+        <v>449.27</v>
       </c>
       <c r="F123" t="n">
-        <v>1119.66</v>
+        <v>75.95</v>
       </c>
       <c r="G123" t="n">
-        <v>1214.03</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7.46%</t>
+          <t>7.73%</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4265,28 +4265,28 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1782.53</v>
+        <v>25508.99</v>
       </c>
       <c r="F124" t="n">
-        <v>69.39</v>
+        <v>238.62</v>
       </c>
       <c r="G124" t="n">
-        <v>74.98</v>
+        <v>258.6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7.45%</t>
+          <t>7.52%</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4296,28 +4296,28 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4961.88</v>
+        <v>2529.35</v>
       </c>
       <c r="F125" t="n">
-        <v>555.37</v>
+        <v>318.67</v>
       </c>
       <c r="G125" t="n">
-        <v>600.08</v>
+        <v>344.6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>7.24%</t>
+          <t>7.49%</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4327,28 +4327,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3256.32</v>
+        <v>532.01</v>
       </c>
       <c r="F126" t="n">
-        <v>308.71</v>
+        <v>46.34</v>
       </c>
       <c r="G126" t="n">
-        <v>332.79</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>7.23%</t>
+          <t>6.87%</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4358,28 +4358,28 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>404.93</v>
+        <v>3269.18</v>
       </c>
       <c r="F127" t="n">
-        <v>82.91</v>
+        <v>309.93</v>
       </c>
       <c r="G127" t="n">
-        <v>89.37</v>
+        <v>332.79</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7.22%</t>
+          <t>6.78%</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4389,28 +4389,28 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Strive Asset Management, LLC</t>
+          <t>Coca-Cola Europacific Partners PLC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>421.52</v>
       </c>
       <c r="F128" t="n">
-        <v>93.03</v>
+        <v>92.38</v>
       </c>
       <c r="G128" t="n">
-        <v>100.27</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.71%</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4420,23 +4420,23 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Coca-Cola Europacific Partners PLC</t>
+          <t>Banco Santander, S.A.</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>420.7</v>
+        <v>1808.51</v>
       </c>
       <c r="F129" t="n">
-        <v>92.2</v>
+        <v>12.23</v>
       </c>
       <c r="G129" t="n">
-        <v>99.09999999999999</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>6.63%</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>39685.87</v>
+        <v>39607.97</v>
       </c>
       <c r="F130" t="n">
-        <v>270.01</v>
+        <v>269.48</v>
       </c>
       <c r="G130" t="n">
         <v>288.62</v>
@@ -4467,12 +4467,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.54%</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4482,28 +4482,28 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3987.93</v>
+        <v>5418.08</v>
       </c>
       <c r="F131" t="n">
-        <v>225.64</v>
+        <v>1395.88</v>
       </c>
       <c r="G131" t="n">
-        <v>241.12</v>
+        <v>1493.48</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.41%</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4513,28 +4513,28 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Altria Group, Inc.</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1044.64</v>
+        <v>3988.28</v>
       </c>
       <c r="F132" t="n">
-        <v>62.23</v>
+        <v>225.66</v>
       </c>
       <c r="G132" t="n">
-        <v>66.3</v>
+        <v>241.12</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4544,28 +4544,28 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3945.54</v>
+        <v>8571.040000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>54.03</v>
+        <v>314.85</v>
       </c>
       <c r="G133" t="n">
-        <v>57.55</v>
+        <v>335.87</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>5.83%</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4575,28 +4575,28 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Toyota Motor Corporation</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>25972.95</v>
+        <v>3030.42</v>
       </c>
       <c r="F134" t="n">
-        <v>242.96</v>
+        <v>231.42</v>
       </c>
       <c r="G134" t="n">
-        <v>258.6</v>
+        <v>245.75</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>5.57%</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4606,28 +4606,28 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Brookfield Corporation</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1046.99</v>
+        <v>2897.69</v>
       </c>
       <c r="F135" t="n">
-        <v>46.59</v>
+        <v>92.31</v>
       </c>
       <c r="G135" t="n">
-        <v>49.57</v>
+        <v>97.76000000000001</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5.84%</t>
+          <t>5.48%</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4637,28 +4637,28 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>The TJX Companies, Inc.</t>
+          <t>AstraZeneca PLC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1671.3</v>
+        <v>5714.97</v>
       </c>
       <c r="F136" t="n">
-        <v>150.17</v>
+        <v>184.32</v>
       </c>
       <c r="G136" t="n">
-        <v>159.48</v>
+        <v>195</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5.82%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4668,28 +4668,28 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>HCA Healthcare, Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1162.6</v>
+        <v>1432.42</v>
       </c>
       <c r="F137" t="n">
-        <v>496.85</v>
+        <v>241.49</v>
       </c>
       <c r="G137" t="n">
-        <v>527.55</v>
+        <v>255.44</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5.76%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4699,28 +4699,28 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Toyota Motor Corporation</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3032.52</v>
+        <v>3976.21</v>
       </c>
       <c r="F138" t="n">
-        <v>231.58</v>
+        <v>54.45</v>
       </c>
       <c r="G138" t="n">
-        <v>245.75</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4730,28 +4730,28 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>HCA Healthcare, Inc.</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2983.07</v>
+        <v>1168.12</v>
       </c>
       <c r="F139" t="n">
-        <v>237.5</v>
+        <v>499.21</v>
       </c>
       <c r="G139" t="n">
-        <v>251.87</v>
+        <v>527.55</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5.62%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4761,59 +4761,59 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2896.43</v>
+        <v>1058.66</v>
       </c>
       <c r="F140" t="n">
-        <v>92.27</v>
+        <v>851.12</v>
       </c>
       <c r="G140" t="n">
-        <v>97.76000000000001</v>
+        <v>894.75</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings plc</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>943.28</v>
+        <v>1508.81</v>
       </c>
       <c r="F141" t="n">
-        <v>432.95</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G141" t="n">
-        <v>457.84</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4823,59 +4823,59 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>The TJX Companies, Inc.</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1052.93</v>
+        <v>1692.45</v>
       </c>
       <c r="F142" t="n">
-        <v>846.51</v>
+        <v>152.07</v>
       </c>
       <c r="G142" t="n">
-        <v>894.75</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5.32%</t>
+          <t>4.64%</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>916.1799999999999</v>
+        <v>2842.52</v>
       </c>
       <c r="F143" t="n">
-        <v>270.23</v>
+        <v>938.99</v>
       </c>
       <c r="G143" t="n">
-        <v>285.42</v>
+        <v>984.7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4885,28 +4885,28 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1500.51</v>
+        <v>2907.01</v>
       </c>
       <c r="F144" t="n">
-        <v>68.77</v>
+        <v>182.91</v>
       </c>
       <c r="G144" t="n">
-        <v>72.58</v>
+        <v>191.62</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>4.43%</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>American Electric Power Company, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>633.38</v>
+        <v>17413.69</v>
       </c>
       <c r="F145" t="n">
-        <v>118.33</v>
+        <v>335.75</v>
       </c>
       <c r="G145" t="n">
-        <v>124.8</v>
+        <v>351.33</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.39%</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>TBB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4947,28 +4947,28 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2157.73</v>
+        <v>1374.08</v>
       </c>
       <c r="F146" t="n">
-        <v>460.16</v>
+        <v>22.38</v>
       </c>
       <c r="G146" t="n">
-        <v>483.05</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4978,28 +4978,28 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Rio Tinto Group</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1846.55</v>
+        <v>1823.24</v>
       </c>
       <c r="F147" t="n">
-        <v>92.52</v>
+        <v>338.59</v>
       </c>
       <c r="G147" t="n">
-        <v>97.11</v>
+        <v>353.25</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5009,28 +5009,28 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>Sandisk Corporation</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2606.58</v>
+        <v>1026.34</v>
       </c>
       <c r="F148" t="n">
-        <v>328.4</v>
+        <v>695.51</v>
       </c>
       <c r="G148" t="n">
-        <v>344.6</v>
+        <v>725</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ENB</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5040,28 +5040,28 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Enbridge Inc.</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1053.95</v>
+        <v>2173.72</v>
       </c>
       <c r="F149" t="n">
-        <v>48.28</v>
+        <v>463.57</v>
       </c>
       <c r="G149" t="n">
-        <v>50.54</v>
+        <v>483.05</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5071,28 +5071,28 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>Marriott International, Inc.</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1509.3</v>
+        <v>864.38</v>
       </c>
       <c r="F150" t="n">
-        <v>269.06</v>
+        <v>318.42</v>
       </c>
       <c r="G150" t="n">
-        <v>281.36</v>
+        <v>331.09</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TBB</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5102,28 +5102,28 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc. 5.35% GLB NTS 66</t>
+          <t>UBS Group AG</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1380.22</v>
+        <v>1502.18</v>
       </c>
       <c r="F151" t="n">
-        <v>22.48</v>
+        <v>47.67</v>
       </c>
       <c r="G151" t="n">
-        <v>23.41</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5133,59 +5133,59 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc.</t>
+          <t>American Electric Power Company, Inc.</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2864.74</v>
+        <v>645.9</v>
       </c>
       <c r="F152" t="n">
-        <v>946.33</v>
+        <v>120.67</v>
       </c>
       <c r="G152" t="n">
-        <v>984.7</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Seagate Technology Holdings plc</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4927.48</v>
+        <v>969.23</v>
       </c>
       <c r="F153" t="n">
-        <v>437.8</v>
+        <v>444.45</v>
       </c>
       <c r="G153" t="n">
-        <v>455.5</v>
+        <v>459.41</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5195,28 +5195,28 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Marriott International, Inc.</t>
+          <t>Altria Group, Inc.</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>866.74</v>
+        <v>1077.04</v>
       </c>
       <c r="F154" t="n">
-        <v>319.29</v>
+        <v>64.16</v>
       </c>
       <c r="G154" t="n">
-        <v>331.09</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5226,28 +5226,28 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Baker Hughes Company</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>557.03</v>
+        <v>1524.24</v>
       </c>
       <c r="F155" t="n">
-        <v>56.45</v>
+        <v>311.29</v>
       </c>
       <c r="G155" t="n">
-        <v>58.5</v>
+        <v>321.23</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5257,59 +5257,59 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mitsubishi UFJ Financial Group, Inc.</t>
+          <t>BHP Group Limited</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2089.08</v>
+        <v>1868.59</v>
       </c>
       <c r="F156" t="n">
-        <v>18.24</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="G156" t="n">
-        <v>18.9</v>
+        <v>74.98</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5594.72</v>
+        <v>558.04</v>
       </c>
       <c r="F157" t="n">
-        <v>1441.39</v>
+        <v>1164.83</v>
       </c>
       <c r="G157" t="n">
-        <v>1493.48</v>
+        <v>1199.76</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>CCZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5319,28 +5319,28 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Comcast Holdings Corp.</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2368.86</v>
+        <v>615.7</v>
       </c>
       <c r="F158" t="n">
-        <v>168.61</v>
+        <v>65</v>
       </c>
       <c r="G158" t="n">
-        <v>174.61</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5350,28 +5350,28 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2941.81</v>
+        <v>1453.78</v>
       </c>
       <c r="F159" t="n">
-        <v>185.1</v>
+        <v>628.26</v>
       </c>
       <c r="G159" t="n">
-        <v>191.62</v>
+        <v>646.59</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5381,28 +5381,28 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>UBS Group AG</t>
+          <t>Philip Morris International Inc.</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1505.01</v>
+        <v>2755.25</v>
       </c>
       <c r="F160" t="n">
-        <v>47.76</v>
+        <v>177</v>
       </c>
       <c r="G160" t="n">
-        <v>49.36</v>
+        <v>181.91</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5412,28 +5412,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NextEra Energy, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1797.92</v>
+        <v>41128.74</v>
       </c>
       <c r="F161" t="n">
-        <v>86.33</v>
+        <v>340.7</v>
       </c>
       <c r="G161" t="n">
-        <v>89.19</v>
+        <v>350.15</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5443,28 +5443,28 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2941.89</v>
+        <v>41146.09</v>
       </c>
       <c r="F162" t="n">
-        <v>314.73</v>
+        <v>339.71</v>
       </c>
       <c r="G162" t="n">
-        <v>324.9</v>
+        <v>349</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>ENB</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5474,28 +5474,28 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Shell plc</t>
+          <t>Enbridge Inc.</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2142.2</v>
+        <v>1076.87</v>
       </c>
       <c r="F163" t="n">
-        <v>75.73</v>
+        <v>49.33</v>
       </c>
       <c r="G163" t="n">
-        <v>78.17</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5505,28 +5505,28 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>17704.65</v>
+        <v>2396.26</v>
       </c>
       <c r="F164" t="n">
-        <v>341.36</v>
+        <v>170.56</v>
       </c>
       <c r="G164" t="n">
-        <v>351.33</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CCZ</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5536,90 +5536,90 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Comcast Holdings Corp.</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>615.7</v>
+        <v>1541.78</v>
       </c>
       <c r="F165" t="n">
-        <v>65</v>
+        <v>274.85</v>
       </c>
       <c r="G165" t="n">
-        <v>66.90000000000001</v>
+        <v>281.36</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>FER</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corporation</t>
+          <t>Ferrovial SE</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5836.56</v>
+        <v>487.47</v>
       </c>
       <c r="F166" t="n">
-        <v>138.4</v>
+        <v>68.2</v>
       </c>
       <c r="G166" t="n">
-        <v>142.34</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>新纳入</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>792.36</v>
+        <v>984.02</v>
       </c>
       <c r="F167" t="n">
-        <v>81.09999999999999</v>
+        <v>290.24</v>
       </c>
       <c r="G167" t="n">
-        <v>83.23999999999999</v>
+        <v>296.5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5629,28 +5629,28 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Mitsubishi UFJ Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1540.03</v>
+        <v>2094.97</v>
       </c>
       <c r="F168" t="n">
-        <v>71.88</v>
+        <v>18.52</v>
       </c>
       <c r="G168" t="n">
-        <v>73.75</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5660,28 +5660,28 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Ross Stores, Inc.</t>
+          <t>The Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>618.29</v>
+        <v>1882.93</v>
       </c>
       <c r="F169" t="n">
-        <v>190.11</v>
+        <v>103.73</v>
       </c>
       <c r="G169" t="n">
-        <v>194.92</v>
+        <v>105.81</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5691,28 +5691,28 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>Ross Stores, Inc.</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1856.04</v>
+        <v>621.5700000000001</v>
       </c>
       <c r="F170" t="n">
-        <v>344.68</v>
+        <v>191.12</v>
       </c>
       <c r="G170" t="n">
-        <v>353.25</v>
+        <v>194.92</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5722,59 +5722,59 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>AstraZeneca PLC</t>
+          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5841.78</v>
+        <v>1458.01</v>
       </c>
       <c r="F171" t="n">
-        <v>188.41</v>
+        <v>25.65</v>
       </c>
       <c r="G171" t="n">
-        <v>192.79</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FER</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Ferrovial SE</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>488.04</v>
+        <v>1777.83</v>
       </c>
       <c r="F172" t="n">
-        <v>68.28</v>
+        <v>143.28</v>
       </c>
       <c r="G172" t="n">
-        <v>69.81999999999999</v>
+        <v>145.94</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5784,28 +5784,28 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Novartis AG</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2696.16</v>
+        <v>2875.5</v>
       </c>
       <c r="F173" t="n">
-        <v>201.09</v>
+        <v>149.86</v>
       </c>
       <c r="G173" t="n">
-        <v>205.36</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5815,28 +5815,28 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Electronic Arts Inc.</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1592.11</v>
+        <v>503.69</v>
       </c>
       <c r="F174" t="n">
-        <v>94.52</v>
+        <v>201.39</v>
       </c>
       <c r="G174" t="n">
-        <v>96.44</v>
+        <v>204.89</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5846,28 +5846,28 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc.</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1881.2</v>
+        <v>2046.31</v>
       </c>
       <c r="F175" t="n">
-        <v>44.61</v>
+        <v>225.21</v>
       </c>
       <c r="G175" t="n">
-        <v>45.48</v>
+        <v>228.83</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>SCCO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5877,28 +5877,28 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Southern Copper Corporation</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3479.47</v>
+        <v>1764.67</v>
       </c>
       <c r="F176" t="n">
-        <v>174.03</v>
+        <v>215.44</v>
       </c>
       <c r="G176" t="n">
-        <v>177.3</v>
+        <v>218.81</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5908,28 +5908,28 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1240.92</v>
+        <v>800.86</v>
       </c>
       <c r="F177" t="n">
-        <v>311.25</v>
+        <v>81.97</v>
       </c>
       <c r="G177" t="n">
-        <v>316.94</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5939,28 +5939,28 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1471.69</v>
+        <v>2116.98</v>
       </c>
       <c r="F178" t="n">
-        <v>636</v>
+        <v>780.25</v>
       </c>
       <c r="G178" t="n">
-        <v>645.67</v>
+        <v>791.95</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5970,28 +5970,28 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>715.7</v>
+        <v>1249.42</v>
       </c>
       <c r="F179" t="n">
-        <v>38.39</v>
+        <v>313.38</v>
       </c>
       <c r="G179" t="n">
-        <v>38.95</v>
+        <v>316.94</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6001,59 +6001,59 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Parker-Hannifin Corporation</t>
+          <t>Verizon Communications Inc.</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1201.58</v>
+        <v>1950.36</v>
       </c>
       <c r="F180" t="n">
-        <v>952</v>
+        <v>46.25</v>
       </c>
       <c r="G180" t="n">
-        <v>965</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>新纳入</t>
+          <t>常规</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>McDonald's Corporation</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>562.05</v>
+        <v>2279.82</v>
       </c>
       <c r="F181" t="n">
-        <v>1173.22</v>
+        <v>319.48</v>
       </c>
       <c r="G181" t="n">
-        <v>1188.66</v>
+        <v>322.89</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6063,28 +6063,28 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc.</t>
+          <t>CME Group Inc.</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2801.02</v>
+        <v>1053.62</v>
       </c>
       <c r="F182" t="n">
-        <v>179.94</v>
+        <v>293.07</v>
       </c>
       <c r="G182" t="n">
-        <v>181.91</v>
+        <v>296.16</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6094,28 +6094,28 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>CME Group Inc.</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1045.35</v>
+        <v>3292.89</v>
       </c>
       <c r="F183" t="n">
-        <v>290.77</v>
+        <v>702.89</v>
       </c>
       <c r="G183" t="n">
-        <v>293.78</v>
+        <v>710.03</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6125,28 +6125,28 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>McDonald's Corporation</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2273.04</v>
+        <v>1608.45</v>
       </c>
       <c r="F184" t="n">
-        <v>318.53</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="G184" t="n">
-        <v>321.79</v>
+        <v>96.44</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6156,28 +6156,28 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2048.39</v>
+        <v>2728.47</v>
       </c>
       <c r="F185" t="n">
-        <v>754.97</v>
+        <v>203.5</v>
       </c>
       <c r="G185" t="n">
-        <v>762.34</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6187,28 +6187,28 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Novartis AG</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2898.14</v>
+        <v>5616.07</v>
       </c>
       <c r="F186" t="n">
-        <v>151.04</v>
+        <v>233.1</v>
       </c>
       <c r="G186" t="n">
-        <v>152.48</v>
+        <v>235.2</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6218,28 +6218,28 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Exxon Mobil Corporation</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1442.79</v>
+        <v>6061.33</v>
       </c>
       <c r="F187" t="n">
-        <v>532.25</v>
+        <v>143.73</v>
       </c>
       <c r="G187" t="n">
-        <v>537.26</v>
+        <v>145.01</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6249,28 +6249,28 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Honeywell International Inc.</t>
+          <t>Parker-Hannifin Corporation</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1533.46</v>
+        <v>1217.14</v>
       </c>
       <c r="F188" t="n">
-        <v>227.56</v>
+        <v>964.33</v>
       </c>
       <c r="G188" t="n">
-        <v>229.59</v>
+        <v>972.8</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6280,28 +6280,28 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria, S.A.</t>
+          <t>Baker Hughes Company</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1473.92</v>
+        <v>572.33</v>
       </c>
       <c r="F189" t="n">
-        <v>25.93</v>
+        <v>58</v>
       </c>
       <c r="G189" t="n">
-        <v>26.14</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6311,28 +6311,28 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1551.52</v>
+        <v>3309.09</v>
       </c>
       <c r="F190" t="n">
-        <v>316.86</v>
+        <v>76.89</v>
       </c>
       <c r="G190" t="n">
-        <v>319.26</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6342,28 +6342,28 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cisco Systems, Inc.</t>
+          <t>Rio Tinto Group</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3186.16</v>
+        <v>1923.39</v>
       </c>
       <c r="F191" t="n">
-        <v>80.64</v>
+        <v>96.37</v>
       </c>
       <c r="G191" t="n">
-        <v>81.15000000000001</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6373,28 +6373,28 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Electronic Arts Inc.</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>509.22</v>
+        <v>729.86</v>
       </c>
       <c r="F192" t="n">
-        <v>203.6</v>
+        <v>39.15</v>
       </c>
       <c r="G192" t="n">
-        <v>204.89</v>
+        <v>39.45</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6404,28 +6404,28 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc.</t>
+          <t>HSBC Holdings plc</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1772.99</v>
+        <v>3054.85</v>
       </c>
       <c r="F193" t="n">
-        <v>142.89</v>
+        <v>88.98</v>
       </c>
       <c r="G193" t="n">
-        <v>143.79</v>
+        <v>89.63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6435,28 +6435,28 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation</t>
+          <t>Shell plc</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1909.07</v>
+        <v>2198.69</v>
       </c>
       <c r="F194" t="n">
-        <v>105.17</v>
+        <v>77.63</v>
       </c>
       <c r="G194" t="n">
-        <v>105.81</v>
+        <v>78.17</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>BMO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6466,28 +6466,28 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>PACCAR Inc</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>654.7</v>
+        <v>1015.34</v>
       </c>
       <c r="F195" t="n">
-        <v>124.61</v>
+        <v>141.26</v>
       </c>
       <c r="G195" t="n">
-        <v>125.36</v>
+        <v>141.92</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6497,28 +6497,28 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>3241.95</v>
+        <v>3559.65</v>
       </c>
       <c r="F196" t="n">
-        <v>75.33</v>
+        <v>178.04</v>
       </c>
       <c r="G196" t="n">
-        <v>75.69</v>
+        <v>178.82</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6528,28 +6528,28 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>GSK plc</t>
+          <t>NextEra Energy, Inc.</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1060.44</v>
+        <v>1849.77</v>
       </c>
       <c r="F197" t="n">
-        <v>52.47</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="G197" t="n">
-        <v>52.67</v>
+        <v>89.19</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6559,28 +6559,28 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>PACCAR Inc</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>41628.15</v>
+        <v>671.99</v>
       </c>
       <c r="F198" t="n">
-        <v>343.69</v>
+        <v>127.9</v>
       </c>
       <c r="G198" t="n">
-        <v>344.83</v>
+        <v>128.42</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6590,28 +6590,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>British American Tobacco p.l.c.</t>
+          <t>Northrop Grumman Corporation</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1323.42</v>
+        <v>1000.52</v>
       </c>
       <c r="F199" t="n">
-        <v>60.99</v>
+        <v>704.98</v>
       </c>
       <c r="G199" t="n">
-        <v>61.15</v>
+        <v>707.66</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6621,28 +6621,28 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Walmart Inc.</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5559.45</v>
+        <v>10182.13</v>
       </c>
       <c r="F200" t="n">
-        <v>230.75</v>
+        <v>127.71</v>
       </c>
       <c r="G200" t="n">
-        <v>231.19</v>
+        <v>128.16</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6652,28 +6652,28 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>Honeywell International Inc.</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>9891.120000000001</v>
+        <v>1556.03</v>
       </c>
       <c r="F201" t="n">
-        <v>124.06</v>
+        <v>230.91</v>
       </c>
       <c r="G201" t="n">
-        <v>124.2</v>
+        <v>231.7</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6683,28 +6683,28 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>British American Tobacco p.l.c.</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2044.49</v>
+        <v>1342.6</v>
       </c>
       <c r="F202" t="n">
-        <v>225.01</v>
+        <v>61.87</v>
       </c>
       <c r="G202" t="n">
-        <v>225.26</v>
+        <v>62.03</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6714,28 +6714,28 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>BP p.l.c.</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>41635.75</v>
+        <v>1014.58</v>
       </c>
       <c r="F203" t="n">
-        <v>344.9</v>
+        <v>38.82</v>
       </c>
       <c r="G203" t="n">
-        <v>345.17</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6745,17 +6745,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Banco Santander, S.A.</t>
+          <t>Cisco Systems, Inc.</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1931.25</v>
+        <v>3283.75</v>
       </c>
       <c r="F204" t="n">
-        <v>13.06</v>
+        <v>83.11</v>
       </c>
       <c r="G204" t="n">
-        <v>13.07</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="205">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6776,28 +6776,28 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>3236.77</v>
+        <v>1078.03</v>
       </c>
       <c r="F205" t="n">
-        <v>690.91</v>
+        <v>53.34</v>
       </c>
       <c r="G205" t="n">
-        <v>691.38</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6807,17 +6807,48 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>HSBC Holdings plc</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>3076.14</v>
+        <v>1477.36</v>
       </c>
       <c r="F206" t="n">
-        <v>89.59999999999999</v>
+        <v>545</v>
       </c>
       <c r="G206" t="n">
-        <v>89.62</v>
+        <v>545.23</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>TotalEnergies SE</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>1594.45</v>
+      </c>
+      <c r="F207" t="n">
+        <v>74.42</v>
+      </c>
+      <c r="G207" t="n">
+        <v>74.42</v>
       </c>
     </row>
   </sheetData>
